--- a/tpl_diario.xlsx
+++ b/tpl_diario.xlsx
@@ -8,7 +8,11 @@
     <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16776" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="DIA" sheetId="1" r:id="rId1"/>
+    <sheet name="06-Jun" sheetId="1" r:id="rId1"/>
+    <sheet name="07-Jun" sheetId="2" r:id="rId2"/>
+    <sheet name="08-Jun" sheetId="3" r:id="rId3"/>
+    <sheet name="09-Jun" sheetId="4" r:id="rId4"/>
+    <sheet name="10-Jun" sheetId="5" r:id="rId5"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm.Print_Area" localSheetId="0">'06-Jun'!$A$1:$Q$47</definedName>
@@ -1258,6 +1262,202 @@
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
               <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E8328D6C-EE35-4C9B-AE6A-C22561E29519}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="14639925" cy="1019175"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>16</xdr:col>
+      <xdr:colOff>9525</xdr:colOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>9525</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="Imagen 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{69F16509-BB29-4696-80DF-B9497470067F}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="14639925" cy="1019175"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>16</xdr:col>
+      <xdr:colOff>9525</xdr:colOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>9525</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="Imagen 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{DE10E466-5F5D-43D3-A41E-874741888B11}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="14639925" cy="1019175"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing4.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>16</xdr:col>
+      <xdr:colOff>9525</xdr:colOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>9525</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="Imagen 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{8B07692C-2217-4A78-A371-B6A406B298A4}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="14639925" cy="1019175"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing5.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>16</xdr:col>
+      <xdr:colOff>9525</xdr:colOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>9525</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="Imagen 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{AFE0467E-9680-4EF6-895F-D7C1848274DF}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1570,9 +1770,7 @@
         <v>0</v>
       </c>
       <c r="C3" s="39"/>
-      <c r="D3" s="34" t="s">
-        <v/>
-      </c>
+      <c r="D3" s="34"/>
       <c r="E3" s="40"/>
       <c r="F3" s="40"/>
       <c r="G3" s="40"/>
@@ -1580,9 +1778,7 @@
       <c r="I3" s="23" t="s">
         <v>2</v>
       </c>
-      <c r="J3" s="34" t="s">
-        <v/>
-      </c>
+      <c r="J3" s="34"/>
       <c r="K3" s="40"/>
       <c r="L3" s="40"/>
       <c r="M3" s="40"/>
@@ -1590,9 +1786,7 @@
       <c r="O3" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="P3" s="2" t="s">
-        <v/>
-      </c>
+      <c r="P3" s="2"/>
     </row>
     <row r="4" spans="2:16" ht="15" customHeight="1" thickBot="1">
       <c r="B4" s="5"/>
@@ -2434,4 +2628,3529 @@
   </colBreaks>
   <drawing r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+  <sheetPr>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="B1:P49"/>
+  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="14.45"/>
+  <cols>
+    <col min="1" max="1" width="0.85546875" customWidth="1"/>
+    <col min="2" max="2" width="5.7109375" style="1" customWidth="1"/>
+    <col min="3" max="13" width="14.85546875" customWidth="1"/>
+    <col min="14" max="15" width="12.7109375" customWidth="1"/>
+    <col min="16" max="16" width="24" customWidth="1"/>
+    <col min="17" max="17" width="0.42578125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="2:16" ht="47.45" customHeight="1"/>
+    <row r="2" spans="2:16" ht="32.25" customHeight="1"/>
+    <row r="3" spans="2:16" ht="33.6" customHeight="1">
+      <c r="B3" s="29" t="s">
+        <v>0</v>
+      </c>
+      <c r="C3" s="39"/>
+      <c r="D3" s="34"/>
+      <c r="E3" s="40"/>
+      <c r="F3" s="40"/>
+      <c r="G3" s="40"/>
+      <c r="H3" s="40"/>
+      <c r="I3" s="23" t="s">
+        <v>2</v>
+      </c>
+      <c r="J3" s="34"/>
+      <c r="K3" s="40"/>
+      <c r="L3" s="40"/>
+      <c r="M3" s="40"/>
+      <c r="N3" s="40"/>
+      <c r="O3" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="P3" s="2"/>
+    </row>
+    <row r="4" spans="2:16" ht="15" customHeight="1" thickBot="1">
+      <c r="B4" s="5"/>
+      <c r="C4" s="3"/>
+      <c r="D4" s="3"/>
+      <c r="E4" s="3"/>
+      <c r="F4" s="3"/>
+      <c r="G4" s="3"/>
+      <c r="H4" s="3"/>
+      <c r="I4" s="3"/>
+      <c r="J4" s="3"/>
+      <c r="K4" s="3"/>
+      <c r="L4" s="3"/>
+      <c r="M4" s="3"/>
+      <c r="N4" s="3"/>
+      <c r="O4" s="3"/>
+      <c r="P4" s="3"/>
+    </row>
+    <row r="5" spans="2:16" ht="16.149999999999999" customHeight="1" thickBot="1">
+      <c r="B5" s="31" t="s">
+        <v>6</v>
+      </c>
+      <c r="C5" s="41"/>
+      <c r="D5" s="41"/>
+      <c r="E5" s="41"/>
+      <c r="F5" s="41"/>
+      <c r="G5" s="41"/>
+      <c r="H5" s="41"/>
+      <c r="I5" s="41"/>
+      <c r="J5" s="41"/>
+      <c r="K5" s="41"/>
+      <c r="L5" s="41"/>
+      <c r="M5" s="41"/>
+      <c r="N5" s="41"/>
+      <c r="O5" s="41"/>
+      <c r="P5" s="42"/>
+    </row>
+    <row r="6" spans="2:16" ht="66" customHeight="1">
+      <c r="B6" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="C6" s="26" t="s">
+        <v>8</v>
+      </c>
+      <c r="D6" s="26" t="s">
+        <v>9</v>
+      </c>
+      <c r="E6" s="26" t="s">
+        <v>10</v>
+      </c>
+      <c r="F6" s="26" t="s">
+        <v>11</v>
+      </c>
+      <c r="G6" s="26" t="s">
+        <v>12</v>
+      </c>
+      <c r="H6" s="26" t="s">
+        <v>13</v>
+      </c>
+      <c r="I6" s="26" t="s">
+        <v>14</v>
+      </c>
+      <c r="J6" s="26" t="s">
+        <v>15</v>
+      </c>
+      <c r="K6" s="26" t="s">
+        <v>16</v>
+      </c>
+      <c r="L6" s="26" t="s">
+        <v>17</v>
+      </c>
+      <c r="M6" s="26" t="s">
+        <v>18</v>
+      </c>
+      <c r="N6" s="32" t="s">
+        <v>19</v>
+      </c>
+      <c r="O6" s="43"/>
+      <c r="P6" s="44"/>
+    </row>
+    <row r="7" spans="2:16" ht="21.2" customHeight="1">
+      <c r="B7" s="8"/>
+      <c r="C7" s="6"/>
+      <c r="D7" s="6"/>
+      <c r="E7" s="35"/>
+      <c r="F7" s="45"/>
+      <c r="G7" s="45"/>
+      <c r="H7" s="45"/>
+      <c r="I7" s="45"/>
+      <c r="J7" s="45"/>
+      <c r="K7" s="45"/>
+      <c r="L7" s="45"/>
+      <c r="M7" s="46"/>
+      <c r="N7" s="30"/>
+      <c r="O7" s="45"/>
+      <c r="P7" s="46"/>
+    </row>
+    <row r="8" spans="2:16" ht="21.2" customHeight="1">
+      <c r="B8" s="8"/>
+      <c r="C8" s="6"/>
+      <c r="D8" s="6"/>
+      <c r="E8" s="6"/>
+      <c r="F8" s="6"/>
+      <c r="G8" s="6"/>
+      <c r="H8" s="6"/>
+      <c r="I8" s="6"/>
+      <c r="J8" s="6"/>
+      <c r="K8" s="6"/>
+      <c r="L8" s="6"/>
+      <c r="M8" s="6"/>
+      <c r="N8" s="30"/>
+      <c r="O8" s="45"/>
+      <c r="P8" s="46"/>
+    </row>
+    <row r="9" spans="2:16" ht="21.2" customHeight="1">
+      <c r="B9" s="8"/>
+      <c r="C9" s="6"/>
+      <c r="D9" s="6"/>
+      <c r="E9" s="6"/>
+      <c r="F9" s="6"/>
+      <c r="G9" s="6"/>
+      <c r="H9" s="6"/>
+      <c r="I9" s="6"/>
+      <c r="J9" s="6"/>
+      <c r="K9" s="6"/>
+      <c r="L9" s="6"/>
+      <c r="M9" s="6"/>
+      <c r="N9" s="30"/>
+      <c r="O9" s="45"/>
+      <c r="P9" s="46"/>
+    </row>
+    <row r="10" spans="2:16" ht="21.2" customHeight="1">
+      <c r="B10" s="8"/>
+      <c r="C10" s="6"/>
+      <c r="D10" s="6"/>
+      <c r="E10" s="6"/>
+      <c r="F10" s="6"/>
+      <c r="G10" s="6"/>
+      <c r="H10" s="6"/>
+      <c r="I10" s="6"/>
+      <c r="J10" s="6"/>
+      <c r="K10" s="6"/>
+      <c r="L10" s="6"/>
+      <c r="M10" s="6"/>
+      <c r="N10" s="30"/>
+      <c r="O10" s="45"/>
+      <c r="P10" s="46"/>
+    </row>
+    <row r="11" spans="2:16" ht="21.2" customHeight="1">
+      <c r="B11" s="8"/>
+      <c r="C11" s="6"/>
+      <c r="D11" s="6"/>
+      <c r="E11" s="6"/>
+      <c r="F11" s="6"/>
+      <c r="G11" s="6"/>
+      <c r="H11" s="6"/>
+      <c r="I11" s="6"/>
+      <c r="J11" s="6"/>
+      <c r="K11" s="6"/>
+      <c r="L11" s="6"/>
+      <c r="M11" s="6"/>
+      <c r="N11" s="30"/>
+      <c r="O11" s="45"/>
+      <c r="P11" s="46"/>
+    </row>
+    <row r="12" spans="2:16" ht="21.2" customHeight="1">
+      <c r="B12" s="8"/>
+      <c r="C12" s="6"/>
+      <c r="D12" s="6"/>
+      <c r="E12" s="6"/>
+      <c r="F12" s="6"/>
+      <c r="G12" s="6"/>
+      <c r="H12" s="6"/>
+      <c r="I12" s="6"/>
+      <c r="J12" s="6"/>
+      <c r="K12" s="6"/>
+      <c r="L12" s="6"/>
+      <c r="M12" s="6"/>
+      <c r="N12" s="30"/>
+      <c r="O12" s="45"/>
+      <c r="P12" s="46"/>
+    </row>
+    <row r="13" spans="2:16" ht="21.2" customHeight="1">
+      <c r="B13" s="8"/>
+      <c r="C13" s="6"/>
+      <c r="D13" s="6"/>
+      <c r="E13" s="6"/>
+      <c r="F13" s="6"/>
+      <c r="G13" s="6"/>
+      <c r="H13" s="6"/>
+      <c r="I13" s="6"/>
+      <c r="J13" s="6"/>
+      <c r="K13" s="6"/>
+      <c r="L13" s="6"/>
+      <c r="M13" s="6"/>
+      <c r="N13" s="30"/>
+      <c r="O13" s="45"/>
+      <c r="P13" s="46"/>
+    </row>
+    <row r="14" spans="2:16" ht="21.2" customHeight="1">
+      <c r="B14" s="8"/>
+      <c r="C14" s="6"/>
+      <c r="D14" s="6"/>
+      <c r="E14" s="6"/>
+      <c r="F14" s="6"/>
+      <c r="G14" s="6"/>
+      <c r="H14" s="6"/>
+      <c r="I14" s="6"/>
+      <c r="J14" s="6"/>
+      <c r="K14" s="6"/>
+      <c r="L14" s="6"/>
+      <c r="M14" s="6"/>
+      <c r="N14" s="30"/>
+      <c r="O14" s="45"/>
+      <c r="P14" s="46"/>
+    </row>
+    <row r="15" spans="2:16" ht="21.2" customHeight="1">
+      <c r="B15" s="8"/>
+      <c r="C15" s="6"/>
+      <c r="D15" s="6"/>
+      <c r="E15" s="6"/>
+      <c r="F15" s="6"/>
+      <c r="G15" s="6"/>
+      <c r="H15" s="6"/>
+      <c r="I15" s="6"/>
+      <c r="J15" s="6"/>
+      <c r="K15" s="6"/>
+      <c r="L15" s="6"/>
+      <c r="M15" s="6"/>
+      <c r="N15" s="30"/>
+      <c r="O15" s="45"/>
+      <c r="P15" s="46"/>
+    </row>
+    <row r="16" spans="2:16" ht="21.2" customHeight="1">
+      <c r="B16" s="8"/>
+      <c r="C16" s="6"/>
+      <c r="D16" s="6"/>
+      <c r="E16" s="6"/>
+      <c r="F16" s="6"/>
+      <c r="G16" s="6"/>
+      <c r="H16" s="6"/>
+      <c r="I16" s="6"/>
+      <c r="J16" s="6"/>
+      <c r="K16" s="6"/>
+      <c r="L16" s="6"/>
+      <c r="M16" s="6"/>
+      <c r="N16" s="30"/>
+      <c r="O16" s="45"/>
+      <c r="P16" s="46"/>
+    </row>
+    <row r="17" spans="2:16" ht="21.2" customHeight="1">
+      <c r="B17" s="8"/>
+      <c r="C17" s="6"/>
+      <c r="D17" s="6"/>
+      <c r="E17" s="6"/>
+      <c r="F17" s="6"/>
+      <c r="G17" s="6"/>
+      <c r="H17" s="6"/>
+      <c r="I17" s="6"/>
+      <c r="J17" s="6"/>
+      <c r="K17" s="6"/>
+      <c r="L17" s="6"/>
+      <c r="M17" s="6"/>
+      <c r="N17" s="30"/>
+      <c r="O17" s="45"/>
+      <c r="P17" s="46"/>
+    </row>
+    <row r="18" spans="2:16" ht="21.2" customHeight="1">
+      <c r="B18" s="8"/>
+      <c r="C18" s="6"/>
+      <c r="D18" s="6"/>
+      <c r="E18" s="6"/>
+      <c r="F18" s="6"/>
+      <c r="G18" s="6"/>
+      <c r="H18" s="6"/>
+      <c r="I18" s="6"/>
+      <c r="J18" s="6"/>
+      <c r="K18" s="6"/>
+      <c r="L18" s="6"/>
+      <c r="M18" s="6"/>
+      <c r="N18" s="30"/>
+      <c r="O18" s="45"/>
+      <c r="P18" s="46"/>
+    </row>
+    <row r="19" spans="2:16" ht="21.2" customHeight="1">
+      <c r="B19" s="8"/>
+      <c r="C19" s="6"/>
+      <c r="D19" s="6"/>
+      <c r="E19" s="6"/>
+      <c r="F19" s="6"/>
+      <c r="G19" s="6"/>
+      <c r="H19" s="6"/>
+      <c r="I19" s="6"/>
+      <c r="J19" s="6"/>
+      <c r="K19" s="6"/>
+      <c r="L19" s="6"/>
+      <c r="M19" s="6"/>
+      <c r="N19" s="30"/>
+      <c r="O19" s="45"/>
+      <c r="P19" s="46"/>
+    </row>
+    <row r="20" spans="2:16" ht="21.2" customHeight="1">
+      <c r="B20" s="8"/>
+      <c r="C20" s="6"/>
+      <c r="D20" s="6"/>
+      <c r="E20" s="6"/>
+      <c r="F20" s="6"/>
+      <c r="G20" s="6"/>
+      <c r="H20" s="6"/>
+      <c r="I20" s="6"/>
+      <c r="J20" s="6"/>
+      <c r="K20" s="6"/>
+      <c r="L20" s="6"/>
+      <c r="M20" s="6"/>
+      <c r="N20" s="30"/>
+      <c r="O20" s="45"/>
+      <c r="P20" s="46"/>
+    </row>
+    <row r="21" spans="2:16" ht="21.2" customHeight="1">
+      <c r="B21" s="8"/>
+      <c r="C21" s="6"/>
+      <c r="D21" s="6"/>
+      <c r="E21" s="6"/>
+      <c r="F21" s="6"/>
+      <c r="G21" s="6"/>
+      <c r="H21" s="6"/>
+      <c r="I21" s="6"/>
+      <c r="J21" s="6"/>
+      <c r="K21" s="6"/>
+      <c r="L21" s="6"/>
+      <c r="M21" s="6"/>
+      <c r="N21" s="30"/>
+      <c r="O21" s="45"/>
+      <c r="P21" s="46"/>
+    </row>
+    <row r="22" spans="2:16" ht="21.2" customHeight="1">
+      <c r="B22" s="8"/>
+      <c r="C22" s="6"/>
+      <c r="D22" s="6"/>
+      <c r="E22" s="6"/>
+      <c r="F22" s="6"/>
+      <c r="G22" s="6"/>
+      <c r="H22" s="6"/>
+      <c r="I22" s="6"/>
+      <c r="J22" s="6"/>
+      <c r="K22" s="6"/>
+      <c r="L22" s="6"/>
+      <c r="M22" s="6"/>
+      <c r="N22" s="30"/>
+      <c r="O22" s="45"/>
+      <c r="P22" s="46"/>
+    </row>
+    <row r="23" spans="2:16" ht="21.2" customHeight="1">
+      <c r="B23" s="8"/>
+      <c r="C23" s="6"/>
+      <c r="D23" s="6"/>
+      <c r="E23" s="6"/>
+      <c r="F23" s="6"/>
+      <c r="G23" s="6"/>
+      <c r="H23" s="6"/>
+      <c r="I23" s="6"/>
+      <c r="J23" s="6"/>
+      <c r="K23" s="6"/>
+      <c r="L23" s="6"/>
+      <c r="M23" s="6"/>
+      <c r="N23" s="30"/>
+      <c r="O23" s="45"/>
+      <c r="P23" s="46"/>
+    </row>
+    <row r="24" spans="2:16" ht="21.2" customHeight="1">
+      <c r="B24" s="8"/>
+      <c r="C24" s="6"/>
+      <c r="D24" s="6"/>
+      <c r="E24" s="6"/>
+      <c r="F24" s="6"/>
+      <c r="G24" s="6"/>
+      <c r="H24" s="6"/>
+      <c r="I24" s="6"/>
+      <c r="J24" s="6"/>
+      <c r="K24" s="6"/>
+      <c r="L24" s="6"/>
+      <c r="M24" s="6"/>
+      <c r="N24" s="30"/>
+      <c r="O24" s="45"/>
+      <c r="P24" s="46"/>
+    </row>
+    <row r="25" spans="2:16" ht="21.2" customHeight="1">
+      <c r="B25" s="8"/>
+      <c r="C25" s="6"/>
+      <c r="D25" s="6"/>
+      <c r="E25" s="6"/>
+      <c r="F25" s="6"/>
+      <c r="G25" s="6"/>
+      <c r="H25" s="6"/>
+      <c r="I25" s="6"/>
+      <c r="J25" s="6"/>
+      <c r="K25" s="6"/>
+      <c r="L25" s="6"/>
+      <c r="M25" s="6"/>
+      <c r="N25" s="30"/>
+      <c r="O25" s="45"/>
+      <c r="P25" s="46"/>
+    </row>
+    <row r="26" spans="2:16" ht="21.2" customHeight="1">
+      <c r="B26" s="8"/>
+      <c r="C26" s="6"/>
+      <c r="D26" s="6"/>
+      <c r="E26" s="6"/>
+      <c r="F26" s="6"/>
+      <c r="G26" s="6"/>
+      <c r="H26" s="6"/>
+      <c r="I26" s="6"/>
+      <c r="J26" s="6"/>
+      <c r="K26" s="6"/>
+      <c r="L26" s="6"/>
+      <c r="M26" s="6"/>
+      <c r="N26" s="30"/>
+      <c r="O26" s="45"/>
+      <c r="P26" s="46"/>
+    </row>
+    <row r="27" spans="2:16" ht="21.2" customHeight="1" thickBot="1">
+      <c r="B27" s="9"/>
+      <c r="C27" s="10"/>
+      <c r="D27" s="10"/>
+      <c r="E27" s="10"/>
+      <c r="F27" s="10"/>
+      <c r="G27" s="10"/>
+      <c r="H27" s="10"/>
+      <c r="I27" s="10"/>
+      <c r="J27" s="10"/>
+      <c r="K27" s="10"/>
+      <c r="L27" s="10"/>
+      <c r="M27" s="10"/>
+      <c r="N27" s="33"/>
+      <c r="O27" s="47"/>
+      <c r="P27" s="48"/>
+    </row>
+    <row r="28" spans="2:16" ht="16.899999999999999" customHeight="1" thickBot="1">
+      <c r="B28" s="5"/>
+      <c r="C28" s="3"/>
+      <c r="D28" s="3"/>
+      <c r="E28" s="3"/>
+      <c r="F28" s="3"/>
+      <c r="G28" s="3"/>
+      <c r="H28" s="3"/>
+      <c r="I28" s="3"/>
+      <c r="J28" s="3"/>
+      <c r="K28" s="3"/>
+      <c r="L28" s="3"/>
+      <c r="M28" s="3"/>
+      <c r="N28" s="25"/>
+      <c r="O28" s="25"/>
+      <c r="P28" s="13" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="29" spans="2:16" ht="16.149999999999999" customHeight="1" thickBot="1">
+      <c r="B29" s="31" t="s">
+        <v>49</v>
+      </c>
+      <c r="C29" s="41"/>
+      <c r="D29" s="41"/>
+      <c r="E29" s="41"/>
+      <c r="F29" s="41"/>
+      <c r="G29" s="41"/>
+      <c r="H29" s="41"/>
+      <c r="I29" s="41"/>
+      <c r="J29" s="41"/>
+      <c r="K29" s="41"/>
+      <c r="L29" s="41"/>
+      <c r="M29" s="41"/>
+      <c r="N29" s="41"/>
+      <c r="O29" s="42"/>
+      <c r="P29" s="25"/>
+    </row>
+    <row r="30" spans="2:16" ht="16.149999999999999" customHeight="1" thickBot="1">
+      <c r="B30" s="31" t="s">
+        <v>50</v>
+      </c>
+      <c r="C30" s="41"/>
+      <c r="D30" s="41"/>
+      <c r="E30" s="42"/>
+      <c r="F30" s="19"/>
+      <c r="G30" s="31" t="s">
+        <v>51</v>
+      </c>
+      <c r="H30" s="41"/>
+      <c r="I30" s="41"/>
+      <c r="J30" s="42"/>
+      <c r="K30" s="19"/>
+      <c r="L30" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="M30" s="41"/>
+      <c r="N30" s="41"/>
+      <c r="O30" s="42"/>
+      <c r="P30" s="25"/>
+    </row>
+    <row r="31" spans="2:16">
+      <c r="B31" s="16" t="s">
+        <v>7</v>
+      </c>
+      <c r="C31" s="17" t="s">
+        <v>53</v>
+      </c>
+      <c r="D31" s="17" t="s">
+        <v>9</v>
+      </c>
+      <c r="E31" s="20" t="s">
+        <v>54</v>
+      </c>
+      <c r="G31" s="16" t="s">
+        <v>7</v>
+      </c>
+      <c r="H31" s="17" t="s">
+        <v>53</v>
+      </c>
+      <c r="I31" s="17" t="s">
+        <v>9</v>
+      </c>
+      <c r="J31" s="20" t="s">
+        <v>54</v>
+      </c>
+      <c r="L31" s="16" t="s">
+        <v>7</v>
+      </c>
+      <c r="M31" s="17" t="s">
+        <v>53</v>
+      </c>
+      <c r="N31" s="18" t="s">
+        <v>9</v>
+      </c>
+      <c r="O31" s="20" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="32" spans="2:16" ht="21.2" customHeight="1">
+      <c r="B32" s="8"/>
+      <c r="C32" s="6"/>
+      <c r="D32" s="6"/>
+      <c r="E32" s="24"/>
+      <c r="G32" s="8"/>
+      <c r="H32" s="6"/>
+      <c r="I32" s="6"/>
+      <c r="J32" s="24"/>
+      <c r="L32" s="8"/>
+      <c r="M32" s="6"/>
+      <c r="N32" s="11"/>
+      <c r="O32" s="21"/>
+    </row>
+    <row r="33" spans="2:16" ht="21.2" customHeight="1">
+      <c r="B33" s="8"/>
+      <c r="C33" s="6"/>
+      <c r="D33" s="6"/>
+      <c r="E33" s="24"/>
+      <c r="G33" s="8"/>
+      <c r="H33" s="6"/>
+      <c r="I33" s="6"/>
+      <c r="J33" s="24"/>
+      <c r="L33" s="8"/>
+      <c r="M33" s="6"/>
+      <c r="N33" s="11"/>
+      <c r="O33" s="21"/>
+    </row>
+    <row r="34" spans="2:16" ht="21.2" customHeight="1">
+      <c r="B34" s="8"/>
+      <c r="C34" s="6"/>
+      <c r="D34" s="6"/>
+      <c r="E34" s="24"/>
+      <c r="G34" s="8"/>
+      <c r="H34" s="6"/>
+      <c r="I34" s="6"/>
+      <c r="J34" s="24"/>
+      <c r="L34" s="8"/>
+      <c r="M34" s="6"/>
+      <c r="N34" s="11"/>
+      <c r="O34" s="21"/>
+    </row>
+    <row r="35" spans="2:16" ht="21.2" customHeight="1">
+      <c r="B35" s="8"/>
+      <c r="C35" s="6"/>
+      <c r="D35" s="6"/>
+      <c r="E35" s="24"/>
+      <c r="G35" s="8"/>
+      <c r="H35" s="6"/>
+      <c r="I35" s="6"/>
+      <c r="J35" s="24"/>
+      <c r="L35" s="8"/>
+      <c r="M35" s="6"/>
+      <c r="N35" s="11"/>
+      <c r="O35" s="21"/>
+    </row>
+    <row r="36" spans="2:16" ht="21.2" customHeight="1">
+      <c r="B36" s="8"/>
+      <c r="C36" s="6"/>
+      <c r="D36" s="6"/>
+      <c r="E36" s="24"/>
+      <c r="G36" s="8"/>
+      <c r="H36" s="6"/>
+      <c r="I36" s="6"/>
+      <c r="J36" s="24"/>
+      <c r="L36" s="8"/>
+      <c r="M36" s="6"/>
+      <c r="N36" s="11"/>
+      <c r="O36" s="21"/>
+    </row>
+    <row r="37" spans="2:16" ht="21.2" customHeight="1">
+      <c r="B37" s="8"/>
+      <c r="C37" s="6"/>
+      <c r="D37" s="6"/>
+      <c r="E37" s="24"/>
+      <c r="G37" s="8"/>
+      <c r="H37" s="6"/>
+      <c r="I37" s="6"/>
+      <c r="J37" s="21"/>
+      <c r="L37" s="8"/>
+      <c r="M37" s="6"/>
+      <c r="N37" s="11"/>
+      <c r="O37" s="21"/>
+    </row>
+    <row r="38" spans="2:16" ht="21.2" customHeight="1">
+      <c r="B38" s="8"/>
+      <c r="C38" s="6"/>
+      <c r="D38" s="6"/>
+      <c r="E38" s="24"/>
+      <c r="G38" s="8"/>
+      <c r="H38" s="6"/>
+      <c r="I38" s="6"/>
+      <c r="J38" s="21"/>
+      <c r="L38" s="8"/>
+      <c r="M38" s="6"/>
+      <c r="N38" s="11"/>
+      <c r="O38" s="21"/>
+    </row>
+    <row r="39" spans="2:16" ht="21.2" customHeight="1">
+      <c r="B39" s="8"/>
+      <c r="C39" s="6"/>
+      <c r="D39" s="6"/>
+      <c r="E39" s="24"/>
+      <c r="G39" s="8"/>
+      <c r="H39" s="6"/>
+      <c r="I39" s="6"/>
+      <c r="J39" s="21"/>
+      <c r="L39" s="8"/>
+      <c r="M39" s="6"/>
+      <c r="N39" s="11"/>
+      <c r="O39" s="21"/>
+    </row>
+    <row r="40" spans="2:16" ht="21.2" customHeight="1">
+      <c r="B40" s="8"/>
+      <c r="C40" s="6"/>
+      <c r="D40" s="6"/>
+      <c r="E40" s="24"/>
+      <c r="G40" s="8"/>
+      <c r="H40" s="6"/>
+      <c r="I40" s="6"/>
+      <c r="J40" s="21"/>
+      <c r="L40" s="8"/>
+      <c r="M40" s="6"/>
+      <c r="N40" s="11"/>
+      <c r="O40" s="21"/>
+    </row>
+    <row r="41" spans="2:16" ht="21.2" customHeight="1">
+      <c r="B41" s="8"/>
+      <c r="C41" s="6"/>
+      <c r="D41" s="6"/>
+      <c r="E41" s="24"/>
+      <c r="G41" s="8"/>
+      <c r="H41" s="6"/>
+      <c r="I41" s="6"/>
+      <c r="J41" s="21"/>
+      <c r="L41" s="8"/>
+      <c r="M41" s="6"/>
+      <c r="N41" s="11"/>
+      <c r="O41" s="21"/>
+    </row>
+    <row r="42" spans="2:16" ht="21.2" customHeight="1">
+      <c r="B42" s="8"/>
+      <c r="C42" s="6"/>
+      <c r="D42" s="6"/>
+      <c r="E42" s="21"/>
+      <c r="G42" s="8"/>
+      <c r="H42" s="6"/>
+      <c r="I42" s="6"/>
+      <c r="J42" s="21"/>
+      <c r="L42" s="8"/>
+      <c r="M42" s="6"/>
+      <c r="N42" s="11"/>
+      <c r="O42" s="21"/>
+    </row>
+    <row r="43" spans="2:16" ht="21.2" customHeight="1">
+      <c r="B43" s="8"/>
+      <c r="C43" s="6"/>
+      <c r="D43" s="6"/>
+      <c r="E43" s="21"/>
+      <c r="G43" s="8"/>
+      <c r="H43" s="6"/>
+      <c r="I43" s="6"/>
+      <c r="J43" s="21"/>
+      <c r="L43" s="8"/>
+      <c r="M43" s="6"/>
+      <c r="N43" s="11"/>
+      <c r="O43" s="21"/>
+    </row>
+    <row r="44" spans="2:16" ht="21.2" customHeight="1">
+      <c r="B44" s="8"/>
+      <c r="C44" s="6"/>
+      <c r="D44" s="6"/>
+      <c r="E44" s="21"/>
+      <c r="G44" s="8"/>
+      <c r="H44" s="6"/>
+      <c r="I44" s="6"/>
+      <c r="J44" s="21"/>
+      <c r="L44" s="8"/>
+      <c r="M44" s="6"/>
+      <c r="N44" s="11"/>
+      <c r="O44" s="21"/>
+    </row>
+    <row r="45" spans="2:16" ht="21.2" customHeight="1">
+      <c r="B45" s="8"/>
+      <c r="C45" s="6"/>
+      <c r="D45" s="6"/>
+      <c r="E45" s="21"/>
+      <c r="G45" s="8"/>
+      <c r="H45" s="6"/>
+      <c r="I45" s="6"/>
+      <c r="J45" s="21"/>
+      <c r="L45" s="8"/>
+      <c r="M45" s="6"/>
+      <c r="N45" s="11"/>
+      <c r="O45" s="21"/>
+    </row>
+    <row r="46" spans="2:16" ht="21.2" customHeight="1" thickBot="1">
+      <c r="B46" s="9"/>
+      <c r="C46" s="10"/>
+      <c r="D46" s="10"/>
+      <c r="E46" s="22"/>
+      <c r="G46" s="9"/>
+      <c r="H46" s="10"/>
+      <c r="I46" s="10"/>
+      <c r="J46" s="22"/>
+      <c r="L46" s="9"/>
+      <c r="M46" s="10"/>
+      <c r="N46" s="12"/>
+      <c r="O46" s="22"/>
+    </row>
+    <row r="47" spans="2:16" ht="7.15" customHeight="1">
+      <c r="B47" s="14"/>
+      <c r="C47" s="15"/>
+      <c r="D47" s="15"/>
+      <c r="E47" s="15"/>
+      <c r="F47" s="15"/>
+      <c r="G47" s="15"/>
+      <c r="H47" s="15"/>
+      <c r="I47" s="15"/>
+      <c r="J47" s="15"/>
+      <c r="K47" s="15"/>
+      <c r="L47" s="15"/>
+      <c r="M47" s="15"/>
+      <c r="N47" s="15"/>
+      <c r="O47" s="15"/>
+    </row>
+    <row r="48" spans="2:16">
+      <c r="B48" s="5"/>
+      <c r="C48" s="28"/>
+      <c r="D48" s="39"/>
+      <c r="E48" s="39"/>
+      <c r="F48" s="39"/>
+      <c r="G48" s="3"/>
+      <c r="H48" s="3"/>
+      <c r="I48" s="3"/>
+      <c r="J48" s="3"/>
+      <c r="K48" s="3"/>
+      <c r="L48" s="3"/>
+      <c r="M48" s="28"/>
+      <c r="N48" s="39"/>
+      <c r="O48" s="39"/>
+      <c r="P48" s="39"/>
+    </row>
+    <row r="49" spans="2:16">
+      <c r="B49" s="5"/>
+      <c r="C49" s="28"/>
+      <c r="D49" s="39"/>
+      <c r="E49" s="39"/>
+      <c r="F49" s="39"/>
+      <c r="G49" s="3"/>
+      <c r="H49" s="3"/>
+      <c r="I49" s="3"/>
+      <c r="J49" s="3"/>
+      <c r="K49" s="3"/>
+      <c r="L49" s="3"/>
+      <c r="M49" s="28"/>
+      <c r="N49" s="39"/>
+      <c r="O49" s="39"/>
+      <c r="P49" s="39"/>
+    </row>
+  </sheetData>
+  <mergeCells count="35">
+    <mergeCell ref="G30:J30"/>
+    <mergeCell ref="N12:P12"/>
+    <mergeCell ref="N21:P21"/>
+    <mergeCell ref="C49:F49"/>
+    <mergeCell ref="N10:P10"/>
+    <mergeCell ref="N13:P13"/>
+    <mergeCell ref="N9:P9"/>
+    <mergeCell ref="N6:P6"/>
+    <mergeCell ref="M49:P49"/>
+    <mergeCell ref="N15:P15"/>
+    <mergeCell ref="E7:M7"/>
+    <mergeCell ref="N24:P24"/>
+    <mergeCell ref="M48:P48"/>
+    <mergeCell ref="B29:O29"/>
+    <mergeCell ref="N27:P27"/>
+    <mergeCell ref="N20:P20"/>
+    <mergeCell ref="N26:P26"/>
+    <mergeCell ref="N11:P11"/>
+    <mergeCell ref="N7:P7"/>
+    <mergeCell ref="C48:F48"/>
+    <mergeCell ref="B3:C3"/>
+    <mergeCell ref="N18:P18"/>
+    <mergeCell ref="B30:E30"/>
+    <mergeCell ref="N14:P14"/>
+    <mergeCell ref="N23:P23"/>
+    <mergeCell ref="N17:P17"/>
+    <mergeCell ref="N8:P8"/>
+    <mergeCell ref="N19:P19"/>
+    <mergeCell ref="B5:P5"/>
+    <mergeCell ref="D3:H3"/>
+    <mergeCell ref="N25:P25"/>
+    <mergeCell ref="J3:N3"/>
+    <mergeCell ref="N16:P16"/>
+    <mergeCell ref="L30:O30"/>
+    <mergeCell ref="N22:P22"/>
+  </mergeCells>
+  <printOptions horizontalCentered="1" verticalCentered="1"/>
+  <pageMargins left="0.19685039370078741" right="0.19685039370078741" top="0.19685039370078741" bottom="0.19685039370078741" header="0" footer="0"/>
+  <pageSetup scale="56" orientation="landscape" verticalDpi="598"/>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
+  <sheetPr>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="B1:P49"/>
+  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="14.45"/>
+  <cols>
+    <col min="1" max="1" width="0.85546875" customWidth="1"/>
+    <col min="2" max="2" width="5.7109375" style="1" customWidth="1"/>
+    <col min="3" max="13" width="14.85546875" customWidth="1"/>
+    <col min="14" max="15" width="12.7109375" customWidth="1"/>
+    <col min="16" max="16" width="24" customWidth="1"/>
+    <col min="17" max="17" width="0.42578125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="2:16" ht="47.45" customHeight="1"/>
+    <row r="2" spans="2:16" ht="32.25" customHeight="1"/>
+    <row r="3" spans="2:16" ht="33.6" customHeight="1">
+      <c r="B3" s="29" t="s">
+        <v>0</v>
+      </c>
+      <c r="C3" s="39"/>
+      <c r="D3" s="34"/>
+      <c r="E3" s="40"/>
+      <c r="F3" s="40"/>
+      <c r="G3" s="40"/>
+      <c r="H3" s="40"/>
+      <c r="I3" s="23" t="s">
+        <v>2</v>
+      </c>
+      <c r="J3" s="34"/>
+      <c r="K3" s="40"/>
+      <c r="L3" s="40"/>
+      <c r="M3" s="40"/>
+      <c r="N3" s="40"/>
+      <c r="O3" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="P3" s="2"/>
+    </row>
+    <row r="4" spans="2:16" ht="15" customHeight="1" thickBot="1">
+      <c r="B4" s="5"/>
+      <c r="C4" s="3"/>
+      <c r="D4" s="3"/>
+      <c r="E4" s="3"/>
+      <c r="F4" s="3"/>
+      <c r="G4" s="3"/>
+      <c r="H4" s="3"/>
+      <c r="I4" s="3"/>
+      <c r="J4" s="3"/>
+      <c r="K4" s="3"/>
+      <c r="L4" s="3"/>
+      <c r="M4" s="3"/>
+      <c r="N4" s="3"/>
+      <c r="O4" s="3"/>
+      <c r="P4" s="3"/>
+    </row>
+    <row r="5" spans="2:16" ht="16.149999999999999" customHeight="1" thickBot="1">
+      <c r="B5" s="31" t="s">
+        <v>6</v>
+      </c>
+      <c r="C5" s="41"/>
+      <c r="D5" s="41"/>
+      <c r="E5" s="41"/>
+      <c r="F5" s="41"/>
+      <c r="G5" s="41"/>
+      <c r="H5" s="41"/>
+      <c r="I5" s="41"/>
+      <c r="J5" s="41"/>
+      <c r="K5" s="41"/>
+      <c r="L5" s="41"/>
+      <c r="M5" s="41"/>
+      <c r="N5" s="41"/>
+      <c r="O5" s="41"/>
+      <c r="P5" s="42"/>
+    </row>
+    <row r="6" spans="2:16" ht="66" customHeight="1">
+      <c r="B6" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="C6" s="26" t="s">
+        <v>8</v>
+      </c>
+      <c r="D6" s="26" t="s">
+        <v>9</v>
+      </c>
+      <c r="E6" s="26" t="s">
+        <v>10</v>
+      </c>
+      <c r="F6" s="26" t="s">
+        <v>11</v>
+      </c>
+      <c r="G6" s="26" t="s">
+        <v>12</v>
+      </c>
+      <c r="H6" s="26" t="s">
+        <v>13</v>
+      </c>
+      <c r="I6" s="26" t="s">
+        <v>14</v>
+      </c>
+      <c r="J6" s="26" t="s">
+        <v>15</v>
+      </c>
+      <c r="K6" s="26" t="s">
+        <v>16</v>
+      </c>
+      <c r="L6" s="26" t="s">
+        <v>17</v>
+      </c>
+      <c r="M6" s="26" t="s">
+        <v>18</v>
+      </c>
+      <c r="N6" s="32" t="s">
+        <v>19</v>
+      </c>
+      <c r="O6" s="43"/>
+      <c r="P6" s="44"/>
+    </row>
+    <row r="7" spans="2:16" ht="21.2" customHeight="1">
+      <c r="B7" s="8"/>
+      <c r="C7" s="6"/>
+      <c r="D7" s="6"/>
+      <c r="E7" s="6"/>
+      <c r="F7" s="6"/>
+      <c r="G7" s="6"/>
+      <c r="H7" s="6"/>
+      <c r="I7" s="6"/>
+      <c r="J7" s="6"/>
+      <c r="K7" s="6"/>
+      <c r="L7" s="6"/>
+      <c r="M7" s="6"/>
+      <c r="N7" s="30"/>
+      <c r="O7" s="45"/>
+      <c r="P7" s="46"/>
+    </row>
+    <row r="8" spans="2:16" ht="21.2" customHeight="1">
+      <c r="B8" s="8"/>
+      <c r="C8" s="6"/>
+      <c r="D8" s="6"/>
+      <c r="E8" s="6"/>
+      <c r="F8" s="6"/>
+      <c r="G8" s="6"/>
+      <c r="H8" s="6"/>
+      <c r="I8" s="6"/>
+      <c r="J8" s="6"/>
+      <c r="K8" s="6"/>
+      <c r="L8" s="6"/>
+      <c r="M8" s="6"/>
+      <c r="N8" s="30"/>
+      <c r="O8" s="45"/>
+      <c r="P8" s="46"/>
+    </row>
+    <row r="9" spans="2:16" ht="21.2" customHeight="1">
+      <c r="B9" s="8"/>
+      <c r="C9" s="6"/>
+      <c r="D9" s="6"/>
+      <c r="E9" s="6"/>
+      <c r="F9" s="6"/>
+      <c r="G9" s="6"/>
+      <c r="H9" s="6"/>
+      <c r="I9" s="6"/>
+      <c r="J9" s="6"/>
+      <c r="K9" s="6"/>
+      <c r="L9" s="6"/>
+      <c r="M9" s="6"/>
+      <c r="N9" s="30"/>
+      <c r="O9" s="45"/>
+      <c r="P9" s="46"/>
+    </row>
+    <row r="10" spans="2:16" ht="21.2" customHeight="1">
+      <c r="B10" s="8"/>
+      <c r="C10" s="6"/>
+      <c r="D10" s="6"/>
+      <c r="E10" s="6"/>
+      <c r="F10" s="6"/>
+      <c r="G10" s="6"/>
+      <c r="H10" s="6"/>
+      <c r="I10" s="6"/>
+      <c r="J10" s="6"/>
+      <c r="K10" s="6"/>
+      <c r="L10" s="6"/>
+      <c r="M10" s="6"/>
+      <c r="N10" s="30"/>
+      <c r="O10" s="45"/>
+      <c r="P10" s="46"/>
+    </row>
+    <row r="11" spans="2:16" ht="21.2" customHeight="1">
+      <c r="B11" s="8"/>
+      <c r="C11" s="6"/>
+      <c r="D11" s="6"/>
+      <c r="E11" s="6"/>
+      <c r="F11" s="6"/>
+      <c r="G11" s="6"/>
+      <c r="H11" s="6"/>
+      <c r="I11" s="6"/>
+      <c r="J11" s="6"/>
+      <c r="K11" s="6"/>
+      <c r="L11" s="6"/>
+      <c r="M11" s="6"/>
+      <c r="N11" s="30"/>
+      <c r="O11" s="45"/>
+      <c r="P11" s="46"/>
+    </row>
+    <row r="12" spans="2:16" ht="21.2" customHeight="1">
+      <c r="B12" s="8"/>
+      <c r="C12" s="6"/>
+      <c r="D12" s="6"/>
+      <c r="E12" s="6"/>
+      <c r="F12" s="6"/>
+      <c r="G12" s="6"/>
+      <c r="H12" s="6"/>
+      <c r="I12" s="6"/>
+      <c r="J12" s="6"/>
+      <c r="K12" s="6"/>
+      <c r="L12" s="6"/>
+      <c r="M12" s="6"/>
+      <c r="N12" s="30"/>
+      <c r="O12" s="45"/>
+      <c r="P12" s="46"/>
+    </row>
+    <row r="13" spans="2:16" ht="21.2" customHeight="1">
+      <c r="B13" s="8"/>
+      <c r="C13" s="6"/>
+      <c r="D13" s="6"/>
+      <c r="E13" s="6"/>
+      <c r="F13" s="6"/>
+      <c r="G13" s="6"/>
+      <c r="H13" s="6"/>
+      <c r="I13" s="6"/>
+      <c r="J13" s="6"/>
+      <c r="K13" s="6"/>
+      <c r="L13" s="6"/>
+      <c r="M13" s="6"/>
+      <c r="N13" s="30"/>
+      <c r="O13" s="45"/>
+      <c r="P13" s="46"/>
+    </row>
+    <row r="14" spans="2:16" ht="21.2" customHeight="1">
+      <c r="B14" s="8"/>
+      <c r="C14" s="6"/>
+      <c r="D14" s="6"/>
+      <c r="E14" s="6"/>
+      <c r="F14" s="6"/>
+      <c r="G14" s="6"/>
+      <c r="H14" s="6"/>
+      <c r="I14" s="6"/>
+      <c r="J14" s="6"/>
+      <c r="K14" s="6"/>
+      <c r="L14" s="6"/>
+      <c r="M14" s="6"/>
+      <c r="N14" s="30"/>
+      <c r="O14" s="45"/>
+      <c r="P14" s="46"/>
+    </row>
+    <row r="15" spans="2:16" ht="21.2" customHeight="1">
+      <c r="B15" s="8"/>
+      <c r="C15" s="6"/>
+      <c r="D15" s="6"/>
+      <c r="E15" s="6"/>
+      <c r="F15" s="6"/>
+      <c r="G15" s="6"/>
+      <c r="H15" s="6"/>
+      <c r="I15" s="6"/>
+      <c r="J15" s="6"/>
+      <c r="K15" s="6"/>
+      <c r="L15" s="6"/>
+      <c r="M15" s="6"/>
+      <c r="N15" s="30"/>
+      <c r="O15" s="45"/>
+      <c r="P15" s="46"/>
+    </row>
+    <row r="16" spans="2:16" ht="21.2" customHeight="1">
+      <c r="B16" s="8"/>
+      <c r="C16" s="6"/>
+      <c r="D16" s="6"/>
+      <c r="E16" s="6"/>
+      <c r="F16" s="6"/>
+      <c r="G16" s="6"/>
+      <c r="H16" s="6"/>
+      <c r="I16" s="6"/>
+      <c r="J16" s="6"/>
+      <c r="K16" s="6"/>
+      <c r="L16" s="6"/>
+      <c r="M16" s="6"/>
+      <c r="N16" s="30"/>
+      <c r="O16" s="45"/>
+      <c r="P16" s="46"/>
+    </row>
+    <row r="17" spans="2:16" ht="21.2" customHeight="1">
+      <c r="B17" s="8"/>
+      <c r="C17" s="6"/>
+      <c r="D17" s="6"/>
+      <c r="E17" s="6"/>
+      <c r="F17" s="6"/>
+      <c r="G17" s="6"/>
+      <c r="H17" s="6"/>
+      <c r="I17" s="6"/>
+      <c r="J17" s="6"/>
+      <c r="K17" s="6"/>
+      <c r="L17" s="6"/>
+      <c r="M17" s="6"/>
+      <c r="N17" s="30"/>
+      <c r="O17" s="45"/>
+      <c r="P17" s="46"/>
+    </row>
+    <row r="18" spans="2:16" ht="21.2" customHeight="1">
+      <c r="B18" s="8"/>
+      <c r="C18" s="6"/>
+      <c r="D18" s="6"/>
+      <c r="E18" s="6"/>
+      <c r="F18" s="6"/>
+      <c r="G18" s="6"/>
+      <c r="H18" s="6"/>
+      <c r="I18" s="6"/>
+      <c r="J18" s="6"/>
+      <c r="K18" s="6"/>
+      <c r="L18" s="6"/>
+      <c r="M18" s="6"/>
+      <c r="N18" s="30"/>
+      <c r="O18" s="45"/>
+      <c r="P18" s="46"/>
+    </row>
+    <row r="19" spans="2:16" ht="21.2" customHeight="1">
+      <c r="B19" s="8"/>
+      <c r="C19" s="6"/>
+      <c r="D19" s="6"/>
+      <c r="E19" s="6"/>
+      <c r="F19" s="6"/>
+      <c r="G19" s="6"/>
+      <c r="H19" s="6"/>
+      <c r="I19" s="6"/>
+      <c r="J19" s="6"/>
+      <c r="K19" s="6"/>
+      <c r="L19" s="6"/>
+      <c r="M19" s="6"/>
+      <c r="N19" s="30"/>
+      <c r="O19" s="45"/>
+      <c r="P19" s="46"/>
+    </row>
+    <row r="20" spans="2:16" ht="21.2" customHeight="1">
+      <c r="B20" s="8"/>
+      <c r="C20" s="6"/>
+      <c r="D20" s="6"/>
+      <c r="E20" s="6"/>
+      <c r="F20" s="6"/>
+      <c r="G20" s="6"/>
+      <c r="H20" s="6"/>
+      <c r="I20" s="6"/>
+      <c r="J20" s="6"/>
+      <c r="K20" s="6"/>
+      <c r="L20" s="6"/>
+      <c r="M20" s="6"/>
+      <c r="N20" s="30"/>
+      <c r="O20" s="45"/>
+      <c r="P20" s="46"/>
+    </row>
+    <row r="21" spans="2:16" ht="21.2" customHeight="1">
+      <c r="B21" s="8"/>
+      <c r="C21" s="6"/>
+      <c r="D21" s="6"/>
+      <c r="E21" s="6"/>
+      <c r="F21" s="6"/>
+      <c r="G21" s="6"/>
+      <c r="H21" s="6"/>
+      <c r="I21" s="6"/>
+      <c r="J21" s="6"/>
+      <c r="K21" s="6"/>
+      <c r="L21" s="6"/>
+      <c r="M21" s="6"/>
+      <c r="N21" s="30"/>
+      <c r="O21" s="45"/>
+      <c r="P21" s="46"/>
+    </row>
+    <row r="22" spans="2:16" ht="21.2" customHeight="1">
+      <c r="B22" s="8"/>
+      <c r="C22" s="6"/>
+      <c r="D22" s="6"/>
+      <c r="E22" s="6"/>
+      <c r="F22" s="6"/>
+      <c r="G22" s="6"/>
+      <c r="H22" s="6"/>
+      <c r="I22" s="6"/>
+      <c r="J22" s="6"/>
+      <c r="K22" s="6"/>
+      <c r="L22" s="6"/>
+      <c r="M22" s="6"/>
+      <c r="N22" s="30"/>
+      <c r="O22" s="45"/>
+      <c r="P22" s="46"/>
+    </row>
+    <row r="23" spans="2:16" ht="21.2" customHeight="1">
+      <c r="B23" s="8"/>
+      <c r="C23" s="6"/>
+      <c r="D23" s="6"/>
+      <c r="E23" s="6"/>
+      <c r="F23" s="6"/>
+      <c r="G23" s="6"/>
+      <c r="H23" s="6"/>
+      <c r="I23" s="6"/>
+      <c r="J23" s="6"/>
+      <c r="K23" s="6"/>
+      <c r="L23" s="6"/>
+      <c r="M23" s="6"/>
+      <c r="N23" s="30"/>
+      <c r="O23" s="45"/>
+      <c r="P23" s="46"/>
+    </row>
+    <row r="24" spans="2:16" ht="21.2" customHeight="1">
+      <c r="B24" s="8"/>
+      <c r="C24" s="6"/>
+      <c r="D24" s="6"/>
+      <c r="E24" s="6"/>
+      <c r="F24" s="6"/>
+      <c r="G24" s="6"/>
+      <c r="H24" s="6"/>
+      <c r="I24" s="6"/>
+      <c r="J24" s="6"/>
+      <c r="K24" s="6"/>
+      <c r="L24" s="6"/>
+      <c r="M24" s="6"/>
+      <c r="N24" s="30"/>
+      <c r="O24" s="45"/>
+      <c r="P24" s="46"/>
+    </row>
+    <row r="25" spans="2:16" ht="21.2" customHeight="1">
+      <c r="B25" s="8"/>
+      <c r="C25" s="6"/>
+      <c r="D25" s="6"/>
+      <c r="E25" s="6"/>
+      <c r="F25" s="6"/>
+      <c r="G25" s="6"/>
+      <c r="H25" s="6"/>
+      <c r="I25" s="6"/>
+      <c r="J25" s="6"/>
+      <c r="K25" s="6"/>
+      <c r="L25" s="6"/>
+      <c r="M25" s="6"/>
+      <c r="N25" s="30"/>
+      <c r="O25" s="45"/>
+      <c r="P25" s="46"/>
+    </row>
+    <row r="26" spans="2:16" ht="21.2" customHeight="1">
+      <c r="B26" s="8"/>
+      <c r="C26" s="6"/>
+      <c r="D26" s="6"/>
+      <c r="E26" s="6"/>
+      <c r="F26" s="6"/>
+      <c r="G26" s="6"/>
+      <c r="H26" s="6"/>
+      <c r="I26" s="6"/>
+      <c r="J26" s="6"/>
+      <c r="K26" s="6"/>
+      <c r="L26" s="6"/>
+      <c r="M26" s="6"/>
+      <c r="N26" s="30"/>
+      <c r="O26" s="45"/>
+      <c r="P26" s="46"/>
+    </row>
+    <row r="27" spans="2:16" ht="21.2" customHeight="1" thickBot="1">
+      <c r="B27" s="9"/>
+      <c r="C27" s="10"/>
+      <c r="D27" s="10"/>
+      <c r="E27" s="10"/>
+      <c r="F27" s="10"/>
+      <c r="G27" s="10"/>
+      <c r="H27" s="10"/>
+      <c r="I27" s="10"/>
+      <c r="J27" s="10"/>
+      <c r="K27" s="10"/>
+      <c r="L27" s="10"/>
+      <c r="M27" s="10"/>
+      <c r="N27" s="33"/>
+      <c r="O27" s="47"/>
+      <c r="P27" s="48"/>
+    </row>
+    <row r="28" spans="2:16" ht="16.899999999999999" customHeight="1" thickBot="1">
+      <c r="B28" s="5"/>
+      <c r="C28" s="3"/>
+      <c r="D28" s="3"/>
+      <c r="E28" s="3"/>
+      <c r="F28" s="3"/>
+      <c r="G28" s="3"/>
+      <c r="H28" s="3"/>
+      <c r="I28" s="3"/>
+      <c r="J28" s="3"/>
+      <c r="K28" s="3"/>
+      <c r="L28" s="3"/>
+      <c r="M28" s="3"/>
+      <c r="N28" s="25"/>
+      <c r="O28" s="25"/>
+      <c r="P28" s="13" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="29" spans="2:16" ht="16.149999999999999" customHeight="1" thickBot="1">
+      <c r="B29" s="31" t="s">
+        <v>49</v>
+      </c>
+      <c r="C29" s="41"/>
+      <c r="D29" s="41"/>
+      <c r="E29" s="41"/>
+      <c r="F29" s="41"/>
+      <c r="G29" s="41"/>
+      <c r="H29" s="41"/>
+      <c r="I29" s="41"/>
+      <c r="J29" s="41"/>
+      <c r="K29" s="41"/>
+      <c r="L29" s="41"/>
+      <c r="M29" s="41"/>
+      <c r="N29" s="41"/>
+      <c r="O29" s="42"/>
+      <c r="P29" s="25"/>
+    </row>
+    <row r="30" spans="2:16" ht="16.149999999999999" customHeight="1" thickBot="1">
+      <c r="B30" s="31" t="s">
+        <v>50</v>
+      </c>
+      <c r="C30" s="41"/>
+      <c r="D30" s="41"/>
+      <c r="E30" s="42"/>
+      <c r="F30" s="19"/>
+      <c r="G30" s="31" t="s">
+        <v>51</v>
+      </c>
+      <c r="H30" s="41"/>
+      <c r="I30" s="41"/>
+      <c r="J30" s="42"/>
+      <c r="K30" s="19"/>
+      <c r="L30" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="M30" s="41"/>
+      <c r="N30" s="41"/>
+      <c r="O30" s="42"/>
+      <c r="P30" s="25"/>
+    </row>
+    <row r="31" spans="2:16">
+      <c r="B31" s="16" t="s">
+        <v>7</v>
+      </c>
+      <c r="C31" s="17" t="s">
+        <v>53</v>
+      </c>
+      <c r="D31" s="17" t="s">
+        <v>9</v>
+      </c>
+      <c r="E31" s="20" t="s">
+        <v>54</v>
+      </c>
+      <c r="G31" s="16" t="s">
+        <v>7</v>
+      </c>
+      <c r="H31" s="17" t="s">
+        <v>53</v>
+      </c>
+      <c r="I31" s="17" t="s">
+        <v>9</v>
+      </c>
+      <c r="J31" s="20" t="s">
+        <v>54</v>
+      </c>
+      <c r="L31" s="16" t="s">
+        <v>7</v>
+      </c>
+      <c r="M31" s="17" t="s">
+        <v>53</v>
+      </c>
+      <c r="N31" s="18" t="s">
+        <v>9</v>
+      </c>
+      <c r="O31" s="20" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="32" spans="2:16" ht="21.2" customHeight="1">
+      <c r="B32" s="8"/>
+      <c r="C32" s="6"/>
+      <c r="D32" s="6"/>
+      <c r="E32" s="24"/>
+      <c r="G32" s="8"/>
+      <c r="H32" s="6"/>
+      <c r="I32" s="6"/>
+      <c r="J32" s="24"/>
+      <c r="L32" s="8"/>
+      <c r="M32" s="6"/>
+      <c r="N32" s="11"/>
+      <c r="O32" s="21"/>
+    </row>
+    <row r="33" spans="2:16" ht="21.2" customHeight="1">
+      <c r="B33" s="8"/>
+      <c r="C33" s="6"/>
+      <c r="D33" s="6"/>
+      <c r="E33" s="24"/>
+      <c r="G33" s="8"/>
+      <c r="H33" s="6"/>
+      <c r="I33" s="6"/>
+      <c r="J33" s="24"/>
+      <c r="L33" s="8"/>
+      <c r="M33" s="6"/>
+      <c r="N33" s="11"/>
+      <c r="O33" s="21"/>
+    </row>
+    <row r="34" spans="2:16" ht="21.2" customHeight="1">
+      <c r="B34" s="8"/>
+      <c r="C34" s="6"/>
+      <c r="D34" s="6"/>
+      <c r="E34" s="24"/>
+      <c r="G34" s="8"/>
+      <c r="H34" s="6"/>
+      <c r="I34" s="6"/>
+      <c r="J34" s="21"/>
+      <c r="L34" s="8"/>
+      <c r="M34" s="6"/>
+      <c r="N34" s="11"/>
+      <c r="O34" s="21"/>
+    </row>
+    <row r="35" spans="2:16" ht="21.2" customHeight="1">
+      <c r="B35" s="8"/>
+      <c r="C35" s="6"/>
+      <c r="D35" s="6"/>
+      <c r="E35" s="24"/>
+      <c r="G35" s="8"/>
+      <c r="H35" s="6"/>
+      <c r="I35" s="6"/>
+      <c r="J35" s="21"/>
+      <c r="L35" s="8"/>
+      <c r="M35" s="6"/>
+      <c r="N35" s="11"/>
+      <c r="O35" s="21"/>
+    </row>
+    <row r="36" spans="2:16" ht="21.2" customHeight="1">
+      <c r="B36" s="8"/>
+      <c r="C36" s="6"/>
+      <c r="D36" s="6"/>
+      <c r="E36" s="24"/>
+      <c r="G36" s="8"/>
+      <c r="H36" s="6"/>
+      <c r="I36" s="6"/>
+      <c r="J36" s="21"/>
+      <c r="L36" s="8"/>
+      <c r="M36" s="6"/>
+      <c r="N36" s="11"/>
+      <c r="O36" s="21"/>
+    </row>
+    <row r="37" spans="2:16" ht="21.2" customHeight="1">
+      <c r="B37" s="8"/>
+      <c r="C37" s="6"/>
+      <c r="D37" s="6"/>
+      <c r="E37" s="24"/>
+      <c r="G37" s="8"/>
+      <c r="H37" s="6"/>
+      <c r="I37" s="6"/>
+      <c r="J37" s="21"/>
+      <c r="L37" s="8"/>
+      <c r="M37" s="6"/>
+      <c r="N37" s="11"/>
+      <c r="O37" s="21"/>
+    </row>
+    <row r="38" spans="2:16" ht="21.2" customHeight="1">
+      <c r="B38" s="8"/>
+      <c r="C38" s="6"/>
+      <c r="D38" s="6"/>
+      <c r="E38" s="24"/>
+      <c r="G38" s="8"/>
+      <c r="H38" s="6"/>
+      <c r="I38" s="6"/>
+      <c r="J38" s="21"/>
+      <c r="L38" s="8"/>
+      <c r="M38" s="6"/>
+      <c r="N38" s="11"/>
+      <c r="O38" s="21"/>
+    </row>
+    <row r="39" spans="2:16" ht="21.2" customHeight="1">
+      <c r="B39" s="8"/>
+      <c r="C39" s="6"/>
+      <c r="D39" s="6"/>
+      <c r="E39" s="24"/>
+      <c r="G39" s="8"/>
+      <c r="H39" s="6"/>
+      <c r="I39" s="6"/>
+      <c r="J39" s="21"/>
+      <c r="L39" s="8"/>
+      <c r="M39" s="6"/>
+      <c r="N39" s="11"/>
+      <c r="O39" s="21"/>
+    </row>
+    <row r="40" spans="2:16" ht="21.2" customHeight="1">
+      <c r="B40" s="8"/>
+      <c r="C40" s="6"/>
+      <c r="D40" s="6"/>
+      <c r="E40" s="24"/>
+      <c r="G40" s="8"/>
+      <c r="H40" s="6"/>
+      <c r="I40" s="6"/>
+      <c r="J40" s="21"/>
+      <c r="L40" s="8"/>
+      <c r="M40" s="6"/>
+      <c r="N40" s="11"/>
+      <c r="O40" s="21"/>
+    </row>
+    <row r="41" spans="2:16" ht="21.2" customHeight="1">
+      <c r="B41" s="8"/>
+      <c r="C41" s="6"/>
+      <c r="D41" s="6"/>
+      <c r="E41" s="24"/>
+      <c r="G41" s="8"/>
+      <c r="H41" s="6"/>
+      <c r="I41" s="6"/>
+      <c r="J41" s="21"/>
+      <c r="L41" s="8"/>
+      <c r="M41" s="6"/>
+      <c r="N41" s="11"/>
+      <c r="O41" s="21"/>
+    </row>
+    <row r="42" spans="2:16" ht="21.2" customHeight="1">
+      <c r="B42" s="8"/>
+      <c r="C42" s="6"/>
+      <c r="D42" s="6"/>
+      <c r="E42" s="24"/>
+      <c r="G42" s="8"/>
+      <c r="H42" s="6"/>
+      <c r="I42" s="6"/>
+      <c r="J42" s="21"/>
+      <c r="L42" s="8"/>
+      <c r="M42" s="6"/>
+      <c r="N42" s="11"/>
+      <c r="O42" s="21"/>
+    </row>
+    <row r="43" spans="2:16" ht="21.2" customHeight="1">
+      <c r="B43" s="8"/>
+      <c r="C43" s="6"/>
+      <c r="D43" s="6"/>
+      <c r="E43" s="21"/>
+      <c r="G43" s="8"/>
+      <c r="H43" s="6"/>
+      <c r="I43" s="6"/>
+      <c r="J43" s="21"/>
+      <c r="L43" s="8"/>
+      <c r="M43" s="6"/>
+      <c r="N43" s="11"/>
+      <c r="O43" s="21"/>
+    </row>
+    <row r="44" spans="2:16" ht="21.2" customHeight="1">
+      <c r="B44" s="8"/>
+      <c r="C44" s="6"/>
+      <c r="D44" s="6"/>
+      <c r="E44" s="21"/>
+      <c r="G44" s="8"/>
+      <c r="H44" s="6"/>
+      <c r="I44" s="6"/>
+      <c r="J44" s="21"/>
+      <c r="L44" s="8"/>
+      <c r="M44" s="6"/>
+      <c r="N44" s="11"/>
+      <c r="O44" s="21"/>
+    </row>
+    <row r="45" spans="2:16" ht="21.2" customHeight="1">
+      <c r="B45" s="8"/>
+      <c r="C45" s="6"/>
+      <c r="D45" s="6"/>
+      <c r="E45" s="21"/>
+      <c r="G45" s="8"/>
+      <c r="H45" s="6"/>
+      <c r="I45" s="6"/>
+      <c r="J45" s="21"/>
+      <c r="L45" s="8"/>
+      <c r="M45" s="6"/>
+      <c r="N45" s="11"/>
+      <c r="O45" s="21"/>
+    </row>
+    <row r="46" spans="2:16" ht="21.2" customHeight="1" thickBot="1">
+      <c r="B46" s="9"/>
+      <c r="C46" s="10"/>
+      <c r="D46" s="10"/>
+      <c r="E46" s="22"/>
+      <c r="G46" s="9"/>
+      <c r="H46" s="10"/>
+      <c r="I46" s="10"/>
+      <c r="J46" s="22"/>
+      <c r="L46" s="9"/>
+      <c r="M46" s="10"/>
+      <c r="N46" s="12"/>
+      <c r="O46" s="22"/>
+    </row>
+    <row r="47" spans="2:16" ht="7.15" customHeight="1">
+      <c r="B47" s="14"/>
+      <c r="C47" s="15"/>
+      <c r="D47" s="15"/>
+      <c r="E47" s="15"/>
+      <c r="F47" s="15"/>
+      <c r="G47" s="15"/>
+      <c r="H47" s="15"/>
+      <c r="I47" s="15"/>
+      <c r="J47" s="15"/>
+      <c r="K47" s="15"/>
+      <c r="L47" s="15"/>
+      <c r="M47" s="15"/>
+      <c r="N47" s="15"/>
+      <c r="O47" s="15"/>
+    </row>
+    <row r="48" spans="2:16">
+      <c r="B48" s="5"/>
+      <c r="C48" s="28"/>
+      <c r="D48" s="39"/>
+      <c r="E48" s="39"/>
+      <c r="F48" s="39"/>
+      <c r="G48" s="3"/>
+      <c r="H48" s="3"/>
+      <c r="I48" s="3"/>
+      <c r="J48" s="3"/>
+      <c r="K48" s="3"/>
+      <c r="L48" s="3"/>
+      <c r="M48" s="28"/>
+      <c r="N48" s="39"/>
+      <c r="O48" s="39"/>
+      <c r="P48" s="39"/>
+    </row>
+    <row r="49" spans="2:16">
+      <c r="B49" s="5"/>
+      <c r="C49" s="28"/>
+      <c r="D49" s="39"/>
+      <c r="E49" s="39"/>
+      <c r="F49" s="39"/>
+      <c r="G49" s="3"/>
+      <c r="H49" s="3"/>
+      <c r="I49" s="3"/>
+      <c r="J49" s="3"/>
+      <c r="K49" s="3"/>
+      <c r="L49" s="3"/>
+      <c r="M49" s="28"/>
+      <c r="N49" s="39"/>
+      <c r="O49" s="39"/>
+      <c r="P49" s="39"/>
+    </row>
+  </sheetData>
+  <mergeCells count="34">
+    <mergeCell ref="N12:P12"/>
+    <mergeCell ref="N21:P21"/>
+    <mergeCell ref="C49:F49"/>
+    <mergeCell ref="N10:P10"/>
+    <mergeCell ref="N13:P13"/>
+    <mergeCell ref="N9:P9"/>
+    <mergeCell ref="N6:P6"/>
+    <mergeCell ref="M49:P49"/>
+    <mergeCell ref="N15:P15"/>
+    <mergeCell ref="N24:P24"/>
+    <mergeCell ref="M48:P48"/>
+    <mergeCell ref="B29:O29"/>
+    <mergeCell ref="N27:P27"/>
+    <mergeCell ref="N20:P20"/>
+    <mergeCell ref="N26:P26"/>
+    <mergeCell ref="N11:P11"/>
+    <mergeCell ref="N7:P7"/>
+    <mergeCell ref="N25:P25"/>
+    <mergeCell ref="C48:F48"/>
+    <mergeCell ref="B3:C3"/>
+    <mergeCell ref="N18:P18"/>
+    <mergeCell ref="B30:E30"/>
+    <mergeCell ref="N14:P14"/>
+    <mergeCell ref="N23:P23"/>
+    <mergeCell ref="N17:P17"/>
+    <mergeCell ref="N8:P8"/>
+    <mergeCell ref="N19:P19"/>
+    <mergeCell ref="B5:P5"/>
+    <mergeCell ref="D3:H3"/>
+    <mergeCell ref="J3:N3"/>
+    <mergeCell ref="N16:P16"/>
+    <mergeCell ref="L30:O30"/>
+    <mergeCell ref="N22:P22"/>
+    <mergeCell ref="G30:J30"/>
+  </mergeCells>
+  <printOptions horizontalCentered="1" verticalCentered="1"/>
+  <pageMargins left="0.19685039370078741" right="0.19685039370078741" top="0.19685039370078741" bottom="0.19685039370078741" header="0" footer="0"/>
+  <pageSetup scale="56" orientation="landscape" verticalDpi="598"/>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
+  <sheetPr>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="B1:P49"/>
+  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="14.45"/>
+  <cols>
+    <col min="1" max="1" width="0.85546875" customWidth="1"/>
+    <col min="2" max="2" width="5.7109375" style="1" customWidth="1"/>
+    <col min="3" max="13" width="14.85546875" customWidth="1"/>
+    <col min="14" max="15" width="12.7109375" customWidth="1"/>
+    <col min="16" max="16" width="24" customWidth="1"/>
+    <col min="17" max="17" width="0.42578125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="2:16" ht="47.45" customHeight="1"/>
+    <row r="2" spans="2:16" ht="32.25" customHeight="1"/>
+    <row r="3" spans="2:16" ht="33.6" customHeight="1">
+      <c r="B3" s="29" t="s">
+        <v>0</v>
+      </c>
+      <c r="C3" s="39"/>
+      <c r="D3" s="34"/>
+      <c r="E3" s="40"/>
+      <c r="F3" s="40"/>
+      <c r="G3" s="40"/>
+      <c r="H3" s="40"/>
+      <c r="I3" s="23" t="s">
+        <v>2</v>
+      </c>
+      <c r="J3" s="34"/>
+      <c r="K3" s="40"/>
+      <c r="L3" s="40"/>
+      <c r="M3" s="40"/>
+      <c r="N3" s="40"/>
+      <c r="O3" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="P3" s="2"/>
+    </row>
+    <row r="4" spans="2:16" ht="15" customHeight="1" thickBot="1">
+      <c r="B4" s="5"/>
+      <c r="C4" s="3"/>
+      <c r="D4" s="3"/>
+      <c r="E4" s="3"/>
+      <c r="F4" s="3"/>
+      <c r="G4" s="3"/>
+      <c r="H4" s="3"/>
+      <c r="I4" s="3"/>
+      <c r="J4" s="3"/>
+      <c r="K4" s="3"/>
+      <c r="L4" s="3"/>
+      <c r="M4" s="3"/>
+      <c r="N4" s="3"/>
+      <c r="O4" s="3"/>
+      <c r="P4" s="3"/>
+    </row>
+    <row r="5" spans="2:16" ht="16.149999999999999" customHeight="1" thickBot="1">
+      <c r="B5" s="31" t="s">
+        <v>6</v>
+      </c>
+      <c r="C5" s="41"/>
+      <c r="D5" s="41"/>
+      <c r="E5" s="41"/>
+      <c r="F5" s="41"/>
+      <c r="G5" s="41"/>
+      <c r="H5" s="41"/>
+      <c r="I5" s="41"/>
+      <c r="J5" s="41"/>
+      <c r="K5" s="41"/>
+      <c r="L5" s="41"/>
+      <c r="M5" s="41"/>
+      <c r="N5" s="41"/>
+      <c r="O5" s="41"/>
+      <c r="P5" s="42"/>
+    </row>
+    <row r="6" spans="2:16" ht="66" customHeight="1">
+      <c r="B6" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="C6" s="26" t="s">
+        <v>8</v>
+      </c>
+      <c r="D6" s="26" t="s">
+        <v>9</v>
+      </c>
+      <c r="E6" s="26" t="s">
+        <v>10</v>
+      </c>
+      <c r="F6" s="26" t="s">
+        <v>11</v>
+      </c>
+      <c r="G6" s="26" t="s">
+        <v>12</v>
+      </c>
+      <c r="H6" s="26" t="s">
+        <v>13</v>
+      </c>
+      <c r="I6" s="26" t="s">
+        <v>14</v>
+      </c>
+      <c r="J6" s="26" t="s">
+        <v>15</v>
+      </c>
+      <c r="K6" s="26" t="s">
+        <v>16</v>
+      </c>
+      <c r="L6" s="26" t="s">
+        <v>17</v>
+      </c>
+      <c r="M6" s="26" t="s">
+        <v>18</v>
+      </c>
+      <c r="N6" s="32" t="s">
+        <v>19</v>
+      </c>
+      <c r="O6" s="43"/>
+      <c r="P6" s="44"/>
+    </row>
+    <row r="7" spans="2:16" ht="21.2" customHeight="1">
+      <c r="B7" s="8"/>
+      <c r="C7" s="6"/>
+      <c r="D7" s="6"/>
+      <c r="E7" s="6"/>
+      <c r="F7" s="6"/>
+      <c r="G7" s="6"/>
+      <c r="H7" s="6"/>
+      <c r="I7" s="6"/>
+      <c r="J7" s="6"/>
+      <c r="K7" s="6"/>
+      <c r="L7" s="6"/>
+      <c r="M7" s="6"/>
+      <c r="N7" s="30"/>
+      <c r="O7" s="45"/>
+      <c r="P7" s="46"/>
+    </row>
+    <row r="8" spans="2:16" ht="21.2" customHeight="1">
+      <c r="B8" s="8"/>
+      <c r="C8" s="6"/>
+      <c r="D8" s="6"/>
+      <c r="E8" s="6"/>
+      <c r="F8" s="6"/>
+      <c r="G8" s="6"/>
+      <c r="H8" s="6"/>
+      <c r="I8" s="6"/>
+      <c r="J8" s="6"/>
+      <c r="K8" s="6"/>
+      <c r="L8" s="6"/>
+      <c r="M8" s="6"/>
+      <c r="N8" s="30"/>
+      <c r="O8" s="45"/>
+      <c r="P8" s="46"/>
+    </row>
+    <row r="9" spans="2:16" ht="21.2" customHeight="1">
+      <c r="B9" s="8"/>
+      <c r="C9" s="6"/>
+      <c r="D9" s="6"/>
+      <c r="E9" s="6"/>
+      <c r="F9" s="6"/>
+      <c r="G9" s="6"/>
+      <c r="H9" s="6"/>
+      <c r="I9" s="6"/>
+      <c r="J9" s="6"/>
+      <c r="K9" s="6"/>
+      <c r="L9" s="6"/>
+      <c r="M9" s="6"/>
+      <c r="N9" s="30"/>
+      <c r="O9" s="45"/>
+      <c r="P9" s="46"/>
+    </row>
+    <row r="10" spans="2:16" ht="21.2" customHeight="1">
+      <c r="B10" s="8"/>
+      <c r="C10" s="6"/>
+      <c r="D10" s="6"/>
+      <c r="E10" s="6"/>
+      <c r="F10" s="6"/>
+      <c r="G10" s="6"/>
+      <c r="H10" s="6"/>
+      <c r="I10" s="6"/>
+      <c r="J10" s="6"/>
+      <c r="K10" s="6"/>
+      <c r="L10" s="6"/>
+      <c r="M10" s="6"/>
+      <c r="N10" s="30"/>
+      <c r="O10" s="45"/>
+      <c r="P10" s="46"/>
+    </row>
+    <row r="11" spans="2:16" ht="21.2" customHeight="1">
+      <c r="B11" s="8"/>
+      <c r="C11" s="6"/>
+      <c r="D11" s="6"/>
+      <c r="E11" s="6"/>
+      <c r="F11" s="6"/>
+      <c r="G11" s="6"/>
+      <c r="H11" s="6"/>
+      <c r="I11" s="6"/>
+      <c r="J11" s="6"/>
+      <c r="K11" s="6"/>
+      <c r="L11" s="6"/>
+      <c r="M11" s="6"/>
+      <c r="N11" s="30"/>
+      <c r="O11" s="45"/>
+      <c r="P11" s="46"/>
+    </row>
+    <row r="12" spans="2:16" ht="21.2" customHeight="1">
+      <c r="B12" s="8"/>
+      <c r="C12" s="6"/>
+      <c r="D12" s="6"/>
+      <c r="E12" s="6"/>
+      <c r="F12" s="6"/>
+      <c r="G12" s="6"/>
+      <c r="H12" s="6"/>
+      <c r="I12" s="6"/>
+      <c r="J12" s="6"/>
+      <c r="K12" s="6"/>
+      <c r="L12" s="6"/>
+      <c r="M12" s="6"/>
+      <c r="N12" s="30"/>
+      <c r="O12" s="45"/>
+      <c r="P12" s="46"/>
+    </row>
+    <row r="13" spans="2:16" ht="21.2" customHeight="1">
+      <c r="B13" s="8"/>
+      <c r="C13" s="6"/>
+      <c r="D13" s="6"/>
+      <c r="E13" s="6"/>
+      <c r="F13" s="6"/>
+      <c r="G13" s="6"/>
+      <c r="H13" s="6"/>
+      <c r="I13" s="6"/>
+      <c r="J13" s="6"/>
+      <c r="K13" s="6"/>
+      <c r="L13" s="6"/>
+      <c r="M13" s="6"/>
+      <c r="N13" s="30"/>
+      <c r="O13" s="45"/>
+      <c r="P13" s="46"/>
+    </row>
+    <row r="14" spans="2:16" ht="21.2" customHeight="1">
+      <c r="B14" s="8"/>
+      <c r="C14" s="6"/>
+      <c r="D14" s="6"/>
+      <c r="E14" s="6"/>
+      <c r="F14" s="6"/>
+      <c r="G14" s="6"/>
+      <c r="H14" s="6"/>
+      <c r="I14" s="6"/>
+      <c r="J14" s="6"/>
+      <c r="K14" s="6"/>
+      <c r="L14" s="6"/>
+      <c r="M14" s="6"/>
+      <c r="N14" s="30"/>
+      <c r="O14" s="45"/>
+      <c r="P14" s="46"/>
+    </row>
+    <row r="15" spans="2:16" ht="21.2" customHeight="1">
+      <c r="B15" s="8"/>
+      <c r="C15" s="6"/>
+      <c r="D15" s="6"/>
+      <c r="E15" s="6"/>
+      <c r="F15" s="6"/>
+      <c r="G15" s="6"/>
+      <c r="H15" s="6"/>
+      <c r="I15" s="6"/>
+      <c r="J15" s="6"/>
+      <c r="K15" s="6"/>
+      <c r="L15" s="6"/>
+      <c r="M15" s="6"/>
+      <c r="N15" s="30"/>
+      <c r="O15" s="45"/>
+      <c r="P15" s="46"/>
+    </row>
+    <row r="16" spans="2:16" ht="21.2" customHeight="1">
+      <c r="B16" s="8"/>
+      <c r="C16" s="6"/>
+      <c r="D16" s="6"/>
+      <c r="E16" s="6"/>
+      <c r="F16" s="6"/>
+      <c r="G16" s="6"/>
+      <c r="H16" s="6"/>
+      <c r="I16" s="6"/>
+      <c r="J16" s="6"/>
+      <c r="K16" s="6"/>
+      <c r="L16" s="6"/>
+      <c r="M16" s="6"/>
+      <c r="N16" s="30"/>
+      <c r="O16" s="45"/>
+      <c r="P16" s="46"/>
+    </row>
+    <row r="17" spans="2:16" ht="21.2" customHeight="1">
+      <c r="B17" s="8"/>
+      <c r="C17" s="6"/>
+      <c r="D17" s="6"/>
+      <c r="E17" s="6"/>
+      <c r="F17" s="6"/>
+      <c r="G17" s="6"/>
+      <c r="H17" s="6"/>
+      <c r="I17" s="6"/>
+      <c r="J17" s="6"/>
+      <c r="K17" s="6"/>
+      <c r="L17" s="6"/>
+      <c r="M17" s="6"/>
+      <c r="N17" s="30"/>
+      <c r="O17" s="45"/>
+      <c r="P17" s="46"/>
+    </row>
+    <row r="18" spans="2:16" ht="21.2" customHeight="1">
+      <c r="B18" s="8"/>
+      <c r="C18" s="6"/>
+      <c r="D18" s="6"/>
+      <c r="E18" s="6"/>
+      <c r="F18" s="6"/>
+      <c r="G18" s="6"/>
+      <c r="H18" s="6"/>
+      <c r="I18" s="6"/>
+      <c r="J18" s="6"/>
+      <c r="K18" s="6"/>
+      <c r="L18" s="6"/>
+      <c r="M18" s="6"/>
+      <c r="N18" s="30"/>
+      <c r="O18" s="45"/>
+      <c r="P18" s="46"/>
+    </row>
+    <row r="19" spans="2:16" ht="21.2" customHeight="1">
+      <c r="B19" s="8"/>
+      <c r="C19" s="6"/>
+      <c r="D19" s="6"/>
+      <c r="E19" s="6"/>
+      <c r="F19" s="6"/>
+      <c r="G19" s="6"/>
+      <c r="H19" s="6"/>
+      <c r="I19" s="6"/>
+      <c r="J19" s="6"/>
+      <c r="K19" s="6"/>
+      <c r="L19" s="6"/>
+      <c r="M19" s="6"/>
+      <c r="N19" s="30"/>
+      <c r="O19" s="45"/>
+      <c r="P19" s="46"/>
+    </row>
+    <row r="20" spans="2:16" ht="21.2" customHeight="1">
+      <c r="B20" s="8"/>
+      <c r="C20" s="6"/>
+      <c r="D20" s="6"/>
+      <c r="E20" s="6"/>
+      <c r="F20" s="6"/>
+      <c r="G20" s="6"/>
+      <c r="H20" s="6"/>
+      <c r="I20" s="6"/>
+      <c r="J20" s="6"/>
+      <c r="K20" s="6"/>
+      <c r="L20" s="6"/>
+      <c r="M20" s="6"/>
+      <c r="N20" s="30"/>
+      <c r="O20" s="45"/>
+      <c r="P20" s="46"/>
+    </row>
+    <row r="21" spans="2:16" ht="21.2" customHeight="1">
+      <c r="B21" s="8"/>
+      <c r="C21" s="6"/>
+      <c r="D21" s="6"/>
+      <c r="E21" s="6"/>
+      <c r="F21" s="6"/>
+      <c r="G21" s="6"/>
+      <c r="H21" s="6"/>
+      <c r="I21" s="6"/>
+      <c r="J21" s="6"/>
+      <c r="K21" s="6"/>
+      <c r="L21" s="6"/>
+      <c r="M21" s="6"/>
+      <c r="N21" s="30"/>
+      <c r="O21" s="45"/>
+      <c r="P21" s="46"/>
+    </row>
+    <row r="22" spans="2:16" ht="21.2" customHeight="1">
+      <c r="B22" s="8"/>
+      <c r="C22" s="6"/>
+      <c r="D22" s="6"/>
+      <c r="E22" s="6"/>
+      <c r="F22" s="6"/>
+      <c r="G22" s="6"/>
+      <c r="H22" s="6"/>
+      <c r="I22" s="6"/>
+      <c r="J22" s="6"/>
+      <c r="K22" s="6"/>
+      <c r="L22" s="6"/>
+      <c r="M22" s="6"/>
+      <c r="N22" s="30"/>
+      <c r="O22" s="45"/>
+      <c r="P22" s="46"/>
+    </row>
+    <row r="23" spans="2:16" ht="21.2" customHeight="1">
+      <c r="B23" s="8"/>
+      <c r="C23" s="6"/>
+      <c r="D23" s="6"/>
+      <c r="E23" s="6"/>
+      <c r="F23" s="6"/>
+      <c r="G23" s="6"/>
+      <c r="H23" s="6"/>
+      <c r="I23" s="6"/>
+      <c r="J23" s="6"/>
+      <c r="K23" s="6"/>
+      <c r="L23" s="6"/>
+      <c r="M23" s="6"/>
+      <c r="N23" s="30"/>
+      <c r="O23" s="45"/>
+      <c r="P23" s="46"/>
+    </row>
+    <row r="24" spans="2:16" ht="21.2" customHeight="1">
+      <c r="B24" s="8"/>
+      <c r="C24" s="6"/>
+      <c r="D24" s="6"/>
+      <c r="E24" s="6"/>
+      <c r="F24" s="6"/>
+      <c r="G24" s="6"/>
+      <c r="H24" s="6"/>
+      <c r="I24" s="6"/>
+      <c r="J24" s="6"/>
+      <c r="K24" s="6"/>
+      <c r="L24" s="6"/>
+      <c r="M24" s="6"/>
+      <c r="N24" s="30"/>
+      <c r="O24" s="45"/>
+      <c r="P24" s="46"/>
+    </row>
+    <row r="25" spans="2:16" ht="21.2" customHeight="1">
+      <c r="B25" s="8"/>
+      <c r="C25" s="6"/>
+      <c r="D25" s="6"/>
+      <c r="E25" s="6"/>
+      <c r="F25" s="6"/>
+      <c r="G25" s="6"/>
+      <c r="H25" s="6"/>
+      <c r="I25" s="6"/>
+      <c r="J25" s="6"/>
+      <c r="K25" s="6"/>
+      <c r="L25" s="6"/>
+      <c r="M25" s="6"/>
+      <c r="N25" s="30"/>
+      <c r="O25" s="45"/>
+      <c r="P25" s="46"/>
+    </row>
+    <row r="26" spans="2:16" ht="21.2" customHeight="1">
+      <c r="B26" s="8"/>
+      <c r="C26" s="6"/>
+      <c r="D26" s="6"/>
+      <c r="E26" s="6"/>
+      <c r="F26" s="6"/>
+      <c r="G26" s="6"/>
+      <c r="H26" s="6"/>
+      <c r="I26" s="6"/>
+      <c r="J26" s="6"/>
+      <c r="K26" s="6"/>
+      <c r="L26" s="6"/>
+      <c r="M26" s="6"/>
+      <c r="N26" s="30"/>
+      <c r="O26" s="45"/>
+      <c r="P26" s="46"/>
+    </row>
+    <row r="27" spans="2:16" ht="21.2" customHeight="1" thickBot="1">
+      <c r="B27" s="9"/>
+      <c r="C27" s="10"/>
+      <c r="D27" s="10"/>
+      <c r="E27" s="10"/>
+      <c r="F27" s="10"/>
+      <c r="G27" s="10"/>
+      <c r="H27" s="10"/>
+      <c r="I27" s="10"/>
+      <c r="J27" s="10"/>
+      <c r="K27" s="10"/>
+      <c r="L27" s="10"/>
+      <c r="M27" s="10"/>
+      <c r="N27" s="33"/>
+      <c r="O27" s="47"/>
+      <c r="P27" s="48"/>
+    </row>
+    <row r="28" spans="2:16" ht="16.899999999999999" customHeight="1" thickBot="1">
+      <c r="B28" s="5"/>
+      <c r="C28" s="3"/>
+      <c r="D28" s="3"/>
+      <c r="E28" s="3"/>
+      <c r="F28" s="3"/>
+      <c r="G28" s="3"/>
+      <c r="H28" s="3"/>
+      <c r="I28" s="3"/>
+      <c r="J28" s="3"/>
+      <c r="K28" s="3"/>
+      <c r="L28" s="3"/>
+      <c r="M28" s="3"/>
+      <c r="N28" s="25"/>
+      <c r="O28" s="25"/>
+      <c r="P28" s="13" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="29" spans="2:16" ht="16.149999999999999" customHeight="1" thickBot="1">
+      <c r="B29" s="31" t="s">
+        <v>49</v>
+      </c>
+      <c r="C29" s="41"/>
+      <c r="D29" s="41"/>
+      <c r="E29" s="41"/>
+      <c r="F29" s="41"/>
+      <c r="G29" s="41"/>
+      <c r="H29" s="41"/>
+      <c r="I29" s="41"/>
+      <c r="J29" s="41"/>
+      <c r="K29" s="41"/>
+      <c r="L29" s="41"/>
+      <c r="M29" s="41"/>
+      <c r="N29" s="41"/>
+      <c r="O29" s="42"/>
+      <c r="P29" s="25"/>
+    </row>
+    <row r="30" spans="2:16" ht="16.149999999999999" customHeight="1" thickBot="1">
+      <c r="B30" s="31" t="s">
+        <v>50</v>
+      </c>
+      <c r="C30" s="41"/>
+      <c r="D30" s="41"/>
+      <c r="E30" s="42"/>
+      <c r="F30" s="19"/>
+      <c r="G30" s="31" t="s">
+        <v>51</v>
+      </c>
+      <c r="H30" s="41"/>
+      <c r="I30" s="41"/>
+      <c r="J30" s="42"/>
+      <c r="K30" s="19"/>
+      <c r="L30" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="M30" s="41"/>
+      <c r="N30" s="41"/>
+      <c r="O30" s="42"/>
+      <c r="P30" s="25"/>
+    </row>
+    <row r="31" spans="2:16">
+      <c r="B31" s="16" t="s">
+        <v>7</v>
+      </c>
+      <c r="C31" s="17" t="s">
+        <v>53</v>
+      </c>
+      <c r="D31" s="17" t="s">
+        <v>9</v>
+      </c>
+      <c r="E31" s="20" t="s">
+        <v>54</v>
+      </c>
+      <c r="G31" s="16" t="s">
+        <v>7</v>
+      </c>
+      <c r="H31" s="17" t="s">
+        <v>53</v>
+      </c>
+      <c r="I31" s="17" t="s">
+        <v>9</v>
+      </c>
+      <c r="J31" s="20" t="s">
+        <v>54</v>
+      </c>
+      <c r="L31" s="16" t="s">
+        <v>7</v>
+      </c>
+      <c r="M31" s="17" t="s">
+        <v>53</v>
+      </c>
+      <c r="N31" s="18" t="s">
+        <v>9</v>
+      </c>
+      <c r="O31" s="20" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="32" spans="2:16" ht="21.2" customHeight="1">
+      <c r="B32" s="8"/>
+      <c r="C32" s="6"/>
+      <c r="D32" s="6"/>
+      <c r="E32" s="24"/>
+      <c r="G32" s="8"/>
+      <c r="H32" s="6"/>
+      <c r="I32" s="6"/>
+      <c r="J32" s="24"/>
+      <c r="L32" s="8"/>
+      <c r="M32" s="6"/>
+      <c r="N32" s="11"/>
+      <c r="O32" s="21"/>
+    </row>
+    <row r="33" spans="2:16" ht="21.2" customHeight="1">
+      <c r="B33" s="8"/>
+      <c r="C33" s="6"/>
+      <c r="D33" s="6"/>
+      <c r="E33" s="24"/>
+      <c r="G33" s="8"/>
+      <c r="H33" s="6"/>
+      <c r="I33" s="6"/>
+      <c r="J33" s="24"/>
+      <c r="L33" s="8"/>
+      <c r="M33" s="6"/>
+      <c r="N33" s="11"/>
+      <c r="O33" s="21"/>
+    </row>
+    <row r="34" spans="2:16" ht="21.2" customHeight="1">
+      <c r="B34" s="8"/>
+      <c r="C34" s="6"/>
+      <c r="D34" s="6"/>
+      <c r="E34" s="24"/>
+      <c r="G34" s="8"/>
+      <c r="H34" s="6"/>
+      <c r="I34" s="6"/>
+      <c r="J34" s="24"/>
+      <c r="L34" s="8"/>
+      <c r="M34" s="6"/>
+      <c r="N34" s="11"/>
+      <c r="O34" s="21"/>
+    </row>
+    <row r="35" spans="2:16" ht="21.2" customHeight="1">
+      <c r="B35" s="8"/>
+      <c r="C35" s="6"/>
+      <c r="D35" s="6"/>
+      <c r="E35" s="24"/>
+      <c r="G35" s="8"/>
+      <c r="H35" s="6"/>
+      <c r="I35" s="6"/>
+      <c r="J35" s="24"/>
+      <c r="L35" s="8"/>
+      <c r="M35" s="6"/>
+      <c r="N35" s="11"/>
+      <c r="O35" s="21"/>
+    </row>
+    <row r="36" spans="2:16" ht="21.2" customHeight="1">
+      <c r="B36" s="8"/>
+      <c r="C36" s="6"/>
+      <c r="D36" s="6"/>
+      <c r="E36" s="24"/>
+      <c r="G36" s="8"/>
+      <c r="H36" s="6"/>
+      <c r="I36" s="6"/>
+      <c r="J36" s="21"/>
+      <c r="L36" s="8"/>
+      <c r="M36" s="6"/>
+      <c r="N36" s="11"/>
+      <c r="O36" s="21"/>
+    </row>
+    <row r="37" spans="2:16" ht="21.2" customHeight="1">
+      <c r="B37" s="8"/>
+      <c r="C37" s="6"/>
+      <c r="D37" s="6"/>
+      <c r="E37" s="24"/>
+      <c r="G37" s="8"/>
+      <c r="H37" s="6"/>
+      <c r="I37" s="6"/>
+      <c r="J37" s="21"/>
+      <c r="L37" s="8"/>
+      <c r="M37" s="6"/>
+      <c r="N37" s="11"/>
+      <c r="O37" s="21"/>
+    </row>
+    <row r="38" spans="2:16" ht="21.2" customHeight="1">
+      <c r="B38" s="8"/>
+      <c r="C38" s="6"/>
+      <c r="D38" s="6"/>
+      <c r="E38" s="24"/>
+      <c r="G38" s="8"/>
+      <c r="H38" s="6"/>
+      <c r="I38" s="6"/>
+      <c r="J38" s="21"/>
+      <c r="L38" s="8"/>
+      <c r="M38" s="6"/>
+      <c r="N38" s="11"/>
+      <c r="O38" s="21"/>
+    </row>
+    <row r="39" spans="2:16" ht="21.2" customHeight="1">
+      <c r="B39" s="8"/>
+      <c r="C39" s="6"/>
+      <c r="D39" s="6"/>
+      <c r="E39" s="24"/>
+      <c r="G39" s="8"/>
+      <c r="H39" s="6"/>
+      <c r="I39" s="6"/>
+      <c r="J39" s="21"/>
+      <c r="L39" s="8"/>
+      <c r="M39" s="6"/>
+      <c r="N39" s="11"/>
+      <c r="O39" s="21"/>
+    </row>
+    <row r="40" spans="2:16" ht="21.2" customHeight="1">
+      <c r="B40" s="8"/>
+      <c r="C40" s="6"/>
+      <c r="D40" s="6"/>
+      <c r="E40" s="24"/>
+      <c r="G40" s="8"/>
+      <c r="H40" s="6"/>
+      <c r="I40" s="6"/>
+      <c r="J40" s="21"/>
+      <c r="L40" s="8"/>
+      <c r="M40" s="6"/>
+      <c r="N40" s="11"/>
+      <c r="O40" s="21"/>
+    </row>
+    <row r="41" spans="2:16" ht="21.2" customHeight="1">
+      <c r="B41" s="8"/>
+      <c r="C41" s="6"/>
+      <c r="D41" s="6"/>
+      <c r="E41" s="24"/>
+      <c r="G41" s="8"/>
+      <c r="H41" s="6"/>
+      <c r="I41" s="6"/>
+      <c r="J41" s="21"/>
+      <c r="L41" s="8"/>
+      <c r="M41" s="6"/>
+      <c r="N41" s="11"/>
+      <c r="O41" s="21"/>
+    </row>
+    <row r="42" spans="2:16" ht="21.2" customHeight="1">
+      <c r="B42" s="8"/>
+      <c r="C42" s="6"/>
+      <c r="D42" s="6"/>
+      <c r="E42" s="21"/>
+      <c r="G42" s="8"/>
+      <c r="H42" s="6"/>
+      <c r="I42" s="6"/>
+      <c r="J42" s="21"/>
+      <c r="L42" s="8"/>
+      <c r="M42" s="6"/>
+      <c r="N42" s="11"/>
+      <c r="O42" s="21"/>
+    </row>
+    <row r="43" spans="2:16" ht="21.2" customHeight="1">
+      <c r="B43" s="8"/>
+      <c r="C43" s="6"/>
+      <c r="D43" s="6"/>
+      <c r="E43" s="21"/>
+      <c r="G43" s="8"/>
+      <c r="H43" s="6"/>
+      <c r="I43" s="6"/>
+      <c r="J43" s="21"/>
+      <c r="L43" s="8"/>
+      <c r="M43" s="6"/>
+      <c r="N43" s="11"/>
+      <c r="O43" s="21"/>
+    </row>
+    <row r="44" spans="2:16" ht="21.2" customHeight="1">
+      <c r="B44" s="8"/>
+      <c r="C44" s="6"/>
+      <c r="D44" s="6"/>
+      <c r="E44" s="21"/>
+      <c r="G44" s="8"/>
+      <c r="H44" s="6"/>
+      <c r="I44" s="6"/>
+      <c r="J44" s="21"/>
+      <c r="L44" s="8"/>
+      <c r="M44" s="6"/>
+      <c r="N44" s="11"/>
+      <c r="O44" s="21"/>
+    </row>
+    <row r="45" spans="2:16" ht="21.2" customHeight="1">
+      <c r="B45" s="8"/>
+      <c r="C45" s="6"/>
+      <c r="D45" s="6"/>
+      <c r="E45" s="21"/>
+      <c r="G45" s="8"/>
+      <c r="H45" s="6"/>
+      <c r="I45" s="6"/>
+      <c r="J45" s="21"/>
+      <c r="L45" s="8"/>
+      <c r="M45" s="6"/>
+      <c r="N45" s="11"/>
+      <c r="O45" s="21"/>
+    </row>
+    <row r="46" spans="2:16" ht="21.2" customHeight="1" thickBot="1">
+      <c r="B46" s="9"/>
+      <c r="C46" s="10"/>
+      <c r="D46" s="10"/>
+      <c r="E46" s="22"/>
+      <c r="G46" s="9"/>
+      <c r="H46" s="10"/>
+      <c r="I46" s="10"/>
+      <c r="J46" s="22"/>
+      <c r="L46" s="9"/>
+      <c r="M46" s="10"/>
+      <c r="N46" s="12"/>
+      <c r="O46" s="22"/>
+    </row>
+    <row r="47" spans="2:16" ht="7.15" customHeight="1">
+      <c r="B47" s="14"/>
+      <c r="C47" s="15"/>
+      <c r="D47" s="15"/>
+      <c r="E47" s="15"/>
+      <c r="F47" s="15"/>
+      <c r="G47" s="15"/>
+      <c r="H47" s="15"/>
+      <c r="I47" s="15"/>
+      <c r="J47" s="15"/>
+      <c r="K47" s="15"/>
+      <c r="L47" s="15"/>
+      <c r="M47" s="15"/>
+      <c r="N47" s="15"/>
+      <c r="O47" s="15"/>
+    </row>
+    <row r="48" spans="2:16">
+      <c r="B48" s="5"/>
+      <c r="C48" s="28"/>
+      <c r="D48" s="39"/>
+      <c r="E48" s="39"/>
+      <c r="F48" s="39"/>
+      <c r="G48" s="3"/>
+      <c r="H48" s="3"/>
+      <c r="I48" s="3"/>
+      <c r="J48" s="3"/>
+      <c r="K48" s="3"/>
+      <c r="L48" s="3"/>
+      <c r="M48" s="28"/>
+      <c r="N48" s="39"/>
+      <c r="O48" s="39"/>
+      <c r="P48" s="39"/>
+    </row>
+    <row r="49" spans="2:16">
+      <c r="B49" s="5"/>
+      <c r="C49" s="28"/>
+      <c r="D49" s="39"/>
+      <c r="E49" s="39"/>
+      <c r="F49" s="39"/>
+      <c r="G49" s="3"/>
+      <c r="H49" s="3"/>
+      <c r="I49" s="3"/>
+      <c r="J49" s="3"/>
+      <c r="K49" s="3"/>
+      <c r="L49" s="3"/>
+      <c r="M49" s="28"/>
+      <c r="N49" s="39"/>
+      <c r="O49" s="39"/>
+      <c r="P49" s="39"/>
+    </row>
+  </sheetData>
+  <mergeCells count="34">
+    <mergeCell ref="N12:P12"/>
+    <mergeCell ref="N21:P21"/>
+    <mergeCell ref="C49:F49"/>
+    <mergeCell ref="N10:P10"/>
+    <mergeCell ref="N13:P13"/>
+    <mergeCell ref="N9:P9"/>
+    <mergeCell ref="N6:P6"/>
+    <mergeCell ref="M49:P49"/>
+    <mergeCell ref="N15:P15"/>
+    <mergeCell ref="N24:P24"/>
+    <mergeCell ref="M48:P48"/>
+    <mergeCell ref="B29:O29"/>
+    <mergeCell ref="N27:P27"/>
+    <mergeCell ref="N20:P20"/>
+    <mergeCell ref="N26:P26"/>
+    <mergeCell ref="N11:P11"/>
+    <mergeCell ref="N7:P7"/>
+    <mergeCell ref="N25:P25"/>
+    <mergeCell ref="C48:F48"/>
+    <mergeCell ref="B3:C3"/>
+    <mergeCell ref="N18:P18"/>
+    <mergeCell ref="B30:E30"/>
+    <mergeCell ref="N14:P14"/>
+    <mergeCell ref="N23:P23"/>
+    <mergeCell ref="N17:P17"/>
+    <mergeCell ref="N8:P8"/>
+    <mergeCell ref="N19:P19"/>
+    <mergeCell ref="B5:P5"/>
+    <mergeCell ref="D3:H3"/>
+    <mergeCell ref="J3:N3"/>
+    <mergeCell ref="N16:P16"/>
+    <mergeCell ref="L30:O30"/>
+    <mergeCell ref="N22:P22"/>
+    <mergeCell ref="G30:J30"/>
+  </mergeCells>
+  <printOptions horizontalCentered="1" verticalCentered="1"/>
+  <pageMargins left="0.19685039370078741" right="0.19685039370078741" top="0.19685039370078741" bottom="0.19685039370078741" header="0" footer="0"/>
+  <pageSetup scale="56" orientation="landscape" verticalDpi="598"/>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
+  <sheetPr>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="B1:P49"/>
+  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="14.45"/>
+  <cols>
+    <col min="1" max="1" width="0.85546875" customWidth="1"/>
+    <col min="2" max="2" width="5.7109375" style="1" customWidth="1"/>
+    <col min="3" max="13" width="14.85546875" customWidth="1"/>
+    <col min="14" max="15" width="12.7109375" customWidth="1"/>
+    <col min="16" max="16" width="24" customWidth="1"/>
+    <col min="17" max="17" width="0.42578125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="2:16" ht="47.45" customHeight="1"/>
+    <row r="2" spans="2:16" ht="32.25" customHeight="1"/>
+    <row r="3" spans="2:16" ht="33.6" customHeight="1">
+      <c r="B3" s="29" t="s">
+        <v>0</v>
+      </c>
+      <c r="C3" s="39"/>
+      <c r="D3" s="34"/>
+      <c r="E3" s="40"/>
+      <c r="F3" s="40"/>
+      <c r="G3" s="40"/>
+      <c r="H3" s="40"/>
+      <c r="I3" s="23" t="s">
+        <v>2</v>
+      </c>
+      <c r="J3" s="34"/>
+      <c r="K3" s="40"/>
+      <c r="L3" s="40"/>
+      <c r="M3" s="40"/>
+      <c r="N3" s="40"/>
+      <c r="O3" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="P3" s="2"/>
+    </row>
+    <row r="4" spans="2:16" ht="15" customHeight="1" thickBot="1">
+      <c r="B4" s="5"/>
+      <c r="C4" s="3"/>
+      <c r="D4" s="3"/>
+      <c r="E4" s="3"/>
+      <c r="F4" s="3"/>
+      <c r="G4" s="3"/>
+      <c r="H4" s="3"/>
+      <c r="I4" s="3"/>
+      <c r="J4" s="3"/>
+      <c r="K4" s="3"/>
+      <c r="L4" s="3"/>
+      <c r="M4" s="3"/>
+      <c r="N4" s="3"/>
+      <c r="O4" s="3"/>
+      <c r="P4" s="3"/>
+    </row>
+    <row r="5" spans="2:16" ht="16.149999999999999" customHeight="1" thickBot="1">
+      <c r="B5" s="31" t="s">
+        <v>6</v>
+      </c>
+      <c r="C5" s="41"/>
+      <c r="D5" s="41"/>
+      <c r="E5" s="41"/>
+      <c r="F5" s="41"/>
+      <c r="G5" s="41"/>
+      <c r="H5" s="41"/>
+      <c r="I5" s="41"/>
+      <c r="J5" s="41"/>
+      <c r="K5" s="41"/>
+      <c r="L5" s="41"/>
+      <c r="M5" s="41"/>
+      <c r="N5" s="41"/>
+      <c r="O5" s="41"/>
+      <c r="P5" s="42"/>
+    </row>
+    <row r="6" spans="2:16" ht="66" customHeight="1">
+      <c r="B6" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="C6" s="26" t="s">
+        <v>8</v>
+      </c>
+      <c r="D6" s="26" t="s">
+        <v>9</v>
+      </c>
+      <c r="E6" s="26" t="s">
+        <v>10</v>
+      </c>
+      <c r="F6" s="26" t="s">
+        <v>11</v>
+      </c>
+      <c r="G6" s="26" t="s">
+        <v>12</v>
+      </c>
+      <c r="H6" s="26" t="s">
+        <v>13</v>
+      </c>
+      <c r="I6" s="26" t="s">
+        <v>14</v>
+      </c>
+      <c r="J6" s="26" t="s">
+        <v>15</v>
+      </c>
+      <c r="K6" s="26" t="s">
+        <v>16</v>
+      </c>
+      <c r="L6" s="26" t="s">
+        <v>17</v>
+      </c>
+      <c r="M6" s="26" t="s">
+        <v>18</v>
+      </c>
+      <c r="N6" s="32" t="s">
+        <v>19</v>
+      </c>
+      <c r="O6" s="43"/>
+      <c r="P6" s="44"/>
+    </row>
+    <row r="7" spans="2:16" ht="21.2" customHeight="1">
+      <c r="B7" s="8"/>
+      <c r="C7" s="6"/>
+      <c r="D7" s="6"/>
+      <c r="E7" s="36"/>
+      <c r="F7" s="37"/>
+      <c r="G7" s="37"/>
+      <c r="H7" s="37"/>
+      <c r="I7" s="37"/>
+      <c r="J7" s="37"/>
+      <c r="K7" s="37"/>
+      <c r="L7" s="37"/>
+      <c r="M7" s="38"/>
+      <c r="N7" s="30"/>
+      <c r="O7" s="45"/>
+      <c r="P7" s="46"/>
+    </row>
+    <row r="8" spans="2:16" ht="21.2" customHeight="1">
+      <c r="B8" s="8"/>
+      <c r="C8" s="6"/>
+      <c r="D8" s="6"/>
+      <c r="E8" s="6"/>
+      <c r="F8" s="6"/>
+      <c r="G8" s="6"/>
+      <c r="H8" s="6"/>
+      <c r="I8" s="6"/>
+      <c r="J8" s="6"/>
+      <c r="K8" s="6"/>
+      <c r="L8" s="6"/>
+      <c r="M8" s="6"/>
+      <c r="N8" s="30"/>
+      <c r="O8" s="45"/>
+      <c r="P8" s="46"/>
+    </row>
+    <row r="9" spans="2:16" ht="21.2" customHeight="1">
+      <c r="B9" s="8"/>
+      <c r="C9" s="6"/>
+      <c r="D9" s="6"/>
+      <c r="E9" s="6"/>
+      <c r="F9" s="6"/>
+      <c r="G9" s="6"/>
+      <c r="H9" s="6"/>
+      <c r="I9" s="6"/>
+      <c r="J9" s="6"/>
+      <c r="K9" s="6"/>
+      <c r="L9" s="6"/>
+      <c r="M9" s="6"/>
+      <c r="N9" s="30"/>
+      <c r="O9" s="45"/>
+      <c r="P9" s="46"/>
+    </row>
+    <row r="10" spans="2:16" ht="21.2" customHeight="1">
+      <c r="B10" s="8"/>
+      <c r="C10" s="6"/>
+      <c r="D10" s="6"/>
+      <c r="E10" s="6"/>
+      <c r="F10" s="6"/>
+      <c r="G10" s="6"/>
+      <c r="H10" s="6"/>
+      <c r="I10" s="6"/>
+      <c r="J10" s="6"/>
+      <c r="K10" s="6"/>
+      <c r="L10" s="6"/>
+      <c r="M10" s="6"/>
+      <c r="N10" s="30"/>
+      <c r="O10" s="45"/>
+      <c r="P10" s="46"/>
+    </row>
+    <row r="11" spans="2:16" ht="21.75" customHeight="1">
+      <c r="B11" s="8"/>
+      <c r="C11" s="6"/>
+      <c r="D11" s="6"/>
+      <c r="E11" s="6"/>
+      <c r="F11" s="6"/>
+      <c r="G11" s="6"/>
+      <c r="H11" s="6"/>
+      <c r="I11" s="6"/>
+      <c r="J11" s="6"/>
+      <c r="K11" s="6"/>
+      <c r="L11" s="6"/>
+      <c r="M11" s="6"/>
+      <c r="N11" s="30"/>
+      <c r="O11" s="45"/>
+      <c r="P11" s="46"/>
+    </row>
+    <row r="12" spans="2:16" ht="26.25" customHeight="1">
+      <c r="B12" s="8"/>
+      <c r="C12" s="6"/>
+      <c r="D12" s="6"/>
+      <c r="E12" s="36"/>
+      <c r="F12" s="37"/>
+      <c r="G12" s="37"/>
+      <c r="H12" s="37"/>
+      <c r="I12" s="37"/>
+      <c r="J12" s="37"/>
+      <c r="K12" s="37"/>
+      <c r="L12" s="37"/>
+      <c r="M12" s="38"/>
+      <c r="N12" s="30"/>
+      <c r="O12" s="45"/>
+      <c r="P12" s="46"/>
+    </row>
+    <row r="13" spans="2:16" ht="30" customHeight="1">
+      <c r="B13" s="8"/>
+      <c r="C13" s="6"/>
+      <c r="D13" s="6"/>
+      <c r="E13" s="36"/>
+      <c r="F13" s="37"/>
+      <c r="G13" s="37"/>
+      <c r="H13" s="37"/>
+      <c r="I13" s="37"/>
+      <c r="J13" s="37"/>
+      <c r="K13" s="37"/>
+      <c r="L13" s="37"/>
+      <c r="M13" s="38"/>
+      <c r="N13" s="30"/>
+      <c r="O13" s="45"/>
+      <c r="P13" s="46"/>
+    </row>
+    <row r="14" spans="2:16" ht="29.25" customHeight="1">
+      <c r="B14" s="8"/>
+      <c r="C14" s="6"/>
+      <c r="D14" s="6"/>
+      <c r="E14" s="36"/>
+      <c r="F14" s="37"/>
+      <c r="G14" s="37"/>
+      <c r="H14" s="37"/>
+      <c r="I14" s="37"/>
+      <c r="J14" s="37"/>
+      <c r="K14" s="37"/>
+      <c r="L14" s="37"/>
+      <c r="M14" s="38"/>
+      <c r="N14" s="30"/>
+      <c r="O14" s="45"/>
+      <c r="P14" s="46"/>
+    </row>
+    <row r="15" spans="2:16" ht="21.2" customHeight="1">
+      <c r="B15" s="8"/>
+      <c r="C15" s="6"/>
+      <c r="D15" s="6"/>
+      <c r="E15" s="6"/>
+      <c r="F15" s="6"/>
+      <c r="G15" s="6"/>
+      <c r="H15" s="6"/>
+      <c r="I15" s="6"/>
+      <c r="J15" s="6"/>
+      <c r="K15" s="6"/>
+      <c r="L15" s="6"/>
+      <c r="M15" s="6"/>
+      <c r="N15" s="30"/>
+      <c r="O15" s="45"/>
+      <c r="P15" s="46"/>
+    </row>
+    <row r="16" spans="2:16" ht="21.2" customHeight="1">
+      <c r="B16" s="8"/>
+      <c r="C16" s="6"/>
+      <c r="D16" s="6"/>
+      <c r="E16" s="6"/>
+      <c r="F16" s="6"/>
+      <c r="G16" s="6"/>
+      <c r="H16" s="6"/>
+      <c r="I16" s="6"/>
+      <c r="J16" s="6"/>
+      <c r="K16" s="6"/>
+      <c r="L16" s="6"/>
+      <c r="M16" s="6"/>
+      <c r="N16" s="30"/>
+      <c r="O16" s="45"/>
+      <c r="P16" s="46"/>
+    </row>
+    <row r="17" spans="2:16" ht="21.2" customHeight="1">
+      <c r="B17" s="8"/>
+      <c r="C17" s="6"/>
+      <c r="D17" s="6"/>
+      <c r="E17" s="6"/>
+      <c r="F17" s="6"/>
+      <c r="G17" s="6"/>
+      <c r="H17" s="6"/>
+      <c r="I17" s="6"/>
+      <c r="J17" s="6"/>
+      <c r="K17" s="6"/>
+      <c r="L17" s="6"/>
+      <c r="M17" s="6"/>
+      <c r="N17" s="30"/>
+      <c r="O17" s="45"/>
+      <c r="P17" s="46"/>
+    </row>
+    <row r="18" spans="2:16" ht="21.2" customHeight="1">
+      <c r="B18" s="8"/>
+      <c r="C18" s="6"/>
+      <c r="D18" s="6"/>
+      <c r="E18" s="6"/>
+      <c r="F18" s="6"/>
+      <c r="G18" s="6"/>
+      <c r="H18" s="6"/>
+      <c r="I18" s="6"/>
+      <c r="J18" s="6"/>
+      <c r="K18" s="6"/>
+      <c r="L18" s="6"/>
+      <c r="M18" s="6"/>
+      <c r="N18" s="30"/>
+      <c r="O18" s="45"/>
+      <c r="P18" s="46"/>
+    </row>
+    <row r="19" spans="2:16" ht="21.2" customHeight="1">
+      <c r="B19" s="8"/>
+      <c r="C19" s="6"/>
+      <c r="D19" s="6"/>
+      <c r="E19" s="6"/>
+      <c r="F19" s="6"/>
+      <c r="G19" s="6"/>
+      <c r="H19" s="6"/>
+      <c r="I19" s="6"/>
+      <c r="J19" s="6"/>
+      <c r="K19" s="6"/>
+      <c r="L19" s="6"/>
+      <c r="M19" s="6"/>
+      <c r="N19" s="30"/>
+      <c r="O19" s="45"/>
+      <c r="P19" s="46"/>
+    </row>
+    <row r="20" spans="2:16" ht="21.2" customHeight="1">
+      <c r="B20" s="8"/>
+      <c r="C20" s="6"/>
+      <c r="D20" s="6"/>
+      <c r="E20" s="6"/>
+      <c r="F20" s="6"/>
+      <c r="G20" s="6"/>
+      <c r="H20" s="6"/>
+      <c r="I20" s="6"/>
+      <c r="J20" s="6"/>
+      <c r="K20" s="6"/>
+      <c r="L20" s="6"/>
+      <c r="M20" s="6"/>
+      <c r="N20" s="30"/>
+      <c r="O20" s="45"/>
+      <c r="P20" s="46"/>
+    </row>
+    <row r="21" spans="2:16" ht="21.2" customHeight="1">
+      <c r="B21" s="8"/>
+      <c r="C21" s="6"/>
+      <c r="D21" s="6"/>
+      <c r="E21" s="6"/>
+      <c r="F21" s="6"/>
+      <c r="G21" s="6"/>
+      <c r="H21" s="6"/>
+      <c r="I21" s="6"/>
+      <c r="J21" s="6"/>
+      <c r="K21" s="6"/>
+      <c r="L21" s="6"/>
+      <c r="M21" s="6"/>
+      <c r="N21" s="30"/>
+      <c r="O21" s="45"/>
+      <c r="P21" s="46"/>
+    </row>
+    <row r="22" spans="2:16" ht="21.2" customHeight="1">
+      <c r="B22" s="8"/>
+      <c r="C22" s="6"/>
+      <c r="D22" s="6"/>
+      <c r="E22" s="6"/>
+      <c r="F22" s="6"/>
+      <c r="G22" s="6"/>
+      <c r="H22" s="6"/>
+      <c r="I22" s="6"/>
+      <c r="J22" s="6"/>
+      <c r="K22" s="6"/>
+      <c r="L22" s="6"/>
+      <c r="M22" s="6"/>
+      <c r="N22" s="30"/>
+      <c r="O22" s="45"/>
+      <c r="P22" s="46"/>
+    </row>
+    <row r="23" spans="2:16" ht="21.2" customHeight="1">
+      <c r="B23" s="8"/>
+      <c r="C23" s="6"/>
+      <c r="D23" s="6"/>
+      <c r="E23" s="6"/>
+      <c r="F23" s="6"/>
+      <c r="G23" s="6"/>
+      <c r="H23" s="6"/>
+      <c r="I23" s="6"/>
+      <c r="J23" s="6"/>
+      <c r="K23" s="6"/>
+      <c r="L23" s="6"/>
+      <c r="M23" s="6"/>
+      <c r="N23" s="30"/>
+      <c r="O23" s="45"/>
+      <c r="P23" s="46"/>
+    </row>
+    <row r="24" spans="2:16" ht="21.2" customHeight="1">
+      <c r="B24" s="8"/>
+      <c r="C24" s="6"/>
+      <c r="D24" s="6"/>
+      <c r="E24" s="6"/>
+      <c r="F24" s="6"/>
+      <c r="G24" s="6"/>
+      <c r="H24" s="6"/>
+      <c r="I24" s="6"/>
+      <c r="J24" s="6"/>
+      <c r="K24" s="6"/>
+      <c r="L24" s="6"/>
+      <c r="M24" s="6"/>
+      <c r="N24" s="30"/>
+      <c r="O24" s="45"/>
+      <c r="P24" s="46"/>
+    </row>
+    <row r="25" spans="2:16" ht="21.2" customHeight="1">
+      <c r="B25" s="8"/>
+      <c r="C25" s="6"/>
+      <c r="D25" s="6"/>
+      <c r="E25" s="6"/>
+      <c r="F25" s="6"/>
+      <c r="G25" s="6"/>
+      <c r="H25" s="6"/>
+      <c r="I25" s="6"/>
+      <c r="J25" s="6"/>
+      <c r="K25" s="6"/>
+      <c r="L25" s="6"/>
+      <c r="M25" s="6"/>
+      <c r="N25" s="30"/>
+      <c r="O25" s="45"/>
+      <c r="P25" s="46"/>
+    </row>
+    <row r="26" spans="2:16" ht="21.2" customHeight="1">
+      <c r="B26" s="8"/>
+      <c r="C26" s="6"/>
+      <c r="D26" s="6"/>
+      <c r="E26" s="6"/>
+      <c r="F26" s="6"/>
+      <c r="G26" s="6"/>
+      <c r="H26" s="6"/>
+      <c r="I26" s="6"/>
+      <c r="J26" s="6"/>
+      <c r="K26" s="6"/>
+      <c r="L26" s="6"/>
+      <c r="M26" s="6"/>
+      <c r="N26" s="30"/>
+      <c r="O26" s="45"/>
+      <c r="P26" s="46"/>
+    </row>
+    <row r="27" spans="2:16" ht="21.2" customHeight="1" thickBot="1">
+      <c r="B27" s="9"/>
+      <c r="C27" s="10"/>
+      <c r="D27" s="10"/>
+      <c r="E27" s="10"/>
+      <c r="F27" s="10"/>
+      <c r="G27" s="10"/>
+      <c r="H27" s="10"/>
+      <c r="I27" s="10"/>
+      <c r="J27" s="10"/>
+      <c r="K27" s="10"/>
+      <c r="L27" s="10"/>
+      <c r="M27" s="10"/>
+      <c r="N27" s="33"/>
+      <c r="O27" s="47"/>
+      <c r="P27" s="48"/>
+    </row>
+    <row r="28" spans="2:16" ht="16.899999999999999" customHeight="1" thickBot="1">
+      <c r="B28" s="5"/>
+      <c r="C28" s="3"/>
+      <c r="D28" s="3"/>
+      <c r="E28" s="3"/>
+      <c r="F28" s="3"/>
+      <c r="G28" s="3"/>
+      <c r="H28" s="3"/>
+      <c r="I28" s="3"/>
+      <c r="J28" s="3"/>
+      <c r="K28" s="3"/>
+      <c r="L28" s="3"/>
+      <c r="M28" s="3"/>
+      <c r="N28" s="25"/>
+      <c r="O28" s="25"/>
+      <c r="P28" s="13" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="29" spans="2:16" ht="16.149999999999999" customHeight="1" thickBot="1">
+      <c r="B29" s="31" t="s">
+        <v>49</v>
+      </c>
+      <c r="C29" s="41"/>
+      <c r="D29" s="41"/>
+      <c r="E29" s="41"/>
+      <c r="F29" s="41"/>
+      <c r="G29" s="41"/>
+      <c r="H29" s="41"/>
+      <c r="I29" s="41"/>
+      <c r="J29" s="41"/>
+      <c r="K29" s="41"/>
+      <c r="L29" s="41"/>
+      <c r="M29" s="41"/>
+      <c r="N29" s="41"/>
+      <c r="O29" s="42"/>
+      <c r="P29" s="25"/>
+    </row>
+    <row r="30" spans="2:16" ht="16.149999999999999" customHeight="1" thickBot="1">
+      <c r="B30" s="31" t="s">
+        <v>50</v>
+      </c>
+      <c r="C30" s="41"/>
+      <c r="D30" s="41"/>
+      <c r="E30" s="42"/>
+      <c r="F30" s="19"/>
+      <c r="G30" s="31" t="s">
+        <v>51</v>
+      </c>
+      <c r="H30" s="41"/>
+      <c r="I30" s="41"/>
+      <c r="J30" s="42"/>
+      <c r="K30" s="19"/>
+      <c r="L30" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="M30" s="41"/>
+      <c r="N30" s="41"/>
+      <c r="O30" s="42"/>
+      <c r="P30" s="25"/>
+    </row>
+    <row r="31" spans="2:16">
+      <c r="B31" s="16" t="s">
+        <v>7</v>
+      </c>
+      <c r="C31" s="17" t="s">
+        <v>53</v>
+      </c>
+      <c r="D31" s="17" t="s">
+        <v>9</v>
+      </c>
+      <c r="E31" s="20" t="s">
+        <v>54</v>
+      </c>
+      <c r="G31" s="16" t="s">
+        <v>7</v>
+      </c>
+      <c r="H31" s="17" t="s">
+        <v>53</v>
+      </c>
+      <c r="I31" s="17" t="s">
+        <v>9</v>
+      </c>
+      <c r="J31" s="20" t="s">
+        <v>54</v>
+      </c>
+      <c r="L31" s="16" t="s">
+        <v>7</v>
+      </c>
+      <c r="M31" s="17" t="s">
+        <v>53</v>
+      </c>
+      <c r="N31" s="18" t="s">
+        <v>9</v>
+      </c>
+      <c r="O31" s="20" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="32" spans="2:16" ht="21.2" customHeight="1">
+      <c r="B32" s="8"/>
+      <c r="C32" s="6"/>
+      <c r="D32" s="6"/>
+      <c r="E32" s="24"/>
+      <c r="G32" s="8"/>
+      <c r="H32" s="6"/>
+      <c r="I32" s="6"/>
+      <c r="J32" s="24"/>
+      <c r="L32" s="8"/>
+      <c r="M32" s="6"/>
+      <c r="N32" s="11"/>
+      <c r="O32" s="21"/>
+    </row>
+    <row r="33" spans="2:16" ht="21.2" customHeight="1">
+      <c r="B33" s="8"/>
+      <c r="C33" s="6"/>
+      <c r="D33" s="6"/>
+      <c r="E33" s="24"/>
+      <c r="G33" s="8"/>
+      <c r="H33" s="6"/>
+      <c r="I33" s="6"/>
+      <c r="J33" s="24"/>
+      <c r="L33" s="8"/>
+      <c r="M33" s="6"/>
+      <c r="N33" s="11"/>
+      <c r="O33" s="21"/>
+    </row>
+    <row r="34" spans="2:16" ht="21.2" customHeight="1">
+      <c r="B34" s="8"/>
+      <c r="C34" s="6"/>
+      <c r="D34" s="6"/>
+      <c r="E34" s="24"/>
+      <c r="G34" s="8"/>
+      <c r="H34" s="6"/>
+      <c r="I34" s="6"/>
+      <c r="J34" s="24"/>
+      <c r="L34" s="8"/>
+      <c r="M34" s="6"/>
+      <c r="N34" s="11"/>
+      <c r="O34" s="21"/>
+    </row>
+    <row r="35" spans="2:16" ht="21.2" customHeight="1">
+      <c r="B35" s="8"/>
+      <c r="C35" s="6"/>
+      <c r="D35" s="6"/>
+      <c r="E35" s="24"/>
+      <c r="G35" s="8"/>
+      <c r="H35" s="6"/>
+      <c r="I35" s="6"/>
+      <c r="J35" s="24"/>
+      <c r="L35" s="8"/>
+      <c r="M35" s="6"/>
+      <c r="N35" s="11"/>
+      <c r="O35" s="21"/>
+    </row>
+    <row r="36" spans="2:16" ht="21.2" customHeight="1">
+      <c r="B36" s="8"/>
+      <c r="C36" s="6"/>
+      <c r="D36" s="6"/>
+      <c r="E36" s="24"/>
+      <c r="G36" s="8"/>
+      <c r="H36" s="6"/>
+      <c r="I36" s="6"/>
+      <c r="J36" s="21"/>
+      <c r="L36" s="8"/>
+      <c r="M36" s="6"/>
+      <c r="N36" s="11"/>
+      <c r="O36" s="21"/>
+    </row>
+    <row r="37" spans="2:16" ht="21.2" customHeight="1">
+      <c r="B37" s="8"/>
+      <c r="C37" s="6"/>
+      <c r="D37" s="6"/>
+      <c r="E37" s="24"/>
+      <c r="G37" s="8"/>
+      <c r="H37" s="6"/>
+      <c r="I37" s="6"/>
+      <c r="J37" s="21"/>
+      <c r="L37" s="8"/>
+      <c r="M37" s="6"/>
+      <c r="N37" s="11"/>
+      <c r="O37" s="21"/>
+    </row>
+    <row r="38" spans="2:16" ht="21.2" customHeight="1">
+      <c r="B38" s="8"/>
+      <c r="C38" s="6"/>
+      <c r="D38" s="6"/>
+      <c r="E38" s="24"/>
+      <c r="G38" s="8"/>
+      <c r="H38" s="6"/>
+      <c r="I38" s="6"/>
+      <c r="J38" s="21"/>
+      <c r="L38" s="8"/>
+      <c r="M38" s="6"/>
+      <c r="N38" s="11"/>
+      <c r="O38" s="21"/>
+    </row>
+    <row r="39" spans="2:16" ht="21.2" customHeight="1">
+      <c r="B39" s="8"/>
+      <c r="C39" s="6"/>
+      <c r="D39" s="6"/>
+      <c r="E39" s="24"/>
+      <c r="G39" s="8"/>
+      <c r="H39" s="6"/>
+      <c r="I39" s="6"/>
+      <c r="J39" s="21"/>
+      <c r="L39" s="8"/>
+      <c r="M39" s="6"/>
+      <c r="N39" s="11"/>
+      <c r="O39" s="21"/>
+    </row>
+    <row r="40" spans="2:16" ht="21.2" customHeight="1">
+      <c r="B40" s="8"/>
+      <c r="C40" s="6"/>
+      <c r="D40" s="6"/>
+      <c r="E40" s="24"/>
+      <c r="G40" s="8"/>
+      <c r="H40" s="6"/>
+      <c r="I40" s="6"/>
+      <c r="J40" s="21"/>
+      <c r="L40" s="8"/>
+      <c r="M40" s="6"/>
+      <c r="N40" s="11"/>
+      <c r="O40" s="21"/>
+    </row>
+    <row r="41" spans="2:16" ht="21.2" customHeight="1">
+      <c r="B41" s="8"/>
+      <c r="C41" s="6"/>
+      <c r="D41" s="6"/>
+      <c r="E41" s="24"/>
+      <c r="G41" s="8"/>
+      <c r="H41" s="6"/>
+      <c r="I41" s="6"/>
+      <c r="J41" s="21"/>
+      <c r="L41" s="8"/>
+      <c r="M41" s="6"/>
+      <c r="N41" s="11"/>
+      <c r="O41" s="21"/>
+    </row>
+    <row r="42" spans="2:16" ht="21.2" customHeight="1">
+      <c r="B42" s="8"/>
+      <c r="C42" s="6"/>
+      <c r="D42" s="6"/>
+      <c r="E42" s="24"/>
+      <c r="G42" s="8"/>
+      <c r="H42" s="6"/>
+      <c r="I42" s="6"/>
+      <c r="J42" s="21"/>
+      <c r="L42" s="8"/>
+      <c r="M42" s="6"/>
+      <c r="N42" s="11"/>
+      <c r="O42" s="21"/>
+    </row>
+    <row r="43" spans="2:16" ht="21.2" customHeight="1">
+      <c r="B43" s="8"/>
+      <c r="C43" s="6"/>
+      <c r="D43" s="6"/>
+      <c r="E43" s="24"/>
+      <c r="G43" s="8"/>
+      <c r="H43" s="6"/>
+      <c r="I43" s="6"/>
+      <c r="J43" s="21"/>
+      <c r="L43" s="8"/>
+      <c r="M43" s="6"/>
+      <c r="N43" s="11"/>
+      <c r="O43" s="21"/>
+    </row>
+    <row r="44" spans="2:16" ht="21.2" customHeight="1">
+      <c r="B44" s="8"/>
+      <c r="C44" s="6"/>
+      <c r="D44" s="6"/>
+      <c r="E44" s="24"/>
+      <c r="G44" s="8"/>
+      <c r="H44" s="6"/>
+      <c r="I44" s="6"/>
+      <c r="J44" s="21"/>
+      <c r="L44" s="8"/>
+      <c r="M44" s="6"/>
+      <c r="N44" s="11"/>
+      <c r="O44" s="21"/>
+    </row>
+    <row r="45" spans="2:16" ht="21.2" customHeight="1">
+      <c r="B45" s="8"/>
+      <c r="C45" s="6"/>
+      <c r="D45" s="6"/>
+      <c r="E45" s="24"/>
+      <c r="G45" s="8"/>
+      <c r="H45" s="6"/>
+      <c r="I45" s="6"/>
+      <c r="J45" s="21"/>
+      <c r="L45" s="8"/>
+      <c r="M45" s="6"/>
+      <c r="N45" s="11"/>
+      <c r="O45" s="21"/>
+    </row>
+    <row r="46" spans="2:16" ht="21.2" customHeight="1" thickBot="1">
+      <c r="B46" s="9"/>
+      <c r="C46" s="10"/>
+      <c r="D46" s="10"/>
+      <c r="E46" s="27"/>
+      <c r="G46" s="9"/>
+      <c r="H46" s="10"/>
+      <c r="I46" s="10"/>
+      <c r="J46" s="22"/>
+      <c r="L46" s="9"/>
+      <c r="M46" s="10"/>
+      <c r="N46" s="12"/>
+      <c r="O46" s="22"/>
+    </row>
+    <row r="47" spans="2:16" ht="7.15" customHeight="1">
+      <c r="B47" s="14"/>
+      <c r="C47" s="15"/>
+      <c r="D47" s="15"/>
+      <c r="E47" s="15"/>
+      <c r="F47" s="15"/>
+      <c r="G47" s="15"/>
+      <c r="H47" s="15"/>
+      <c r="I47" s="15"/>
+      <c r="J47" s="15"/>
+      <c r="K47" s="15"/>
+      <c r="L47" s="15"/>
+      <c r="M47" s="15"/>
+      <c r="N47" s="15"/>
+      <c r="O47" s="15"/>
+    </row>
+    <row r="48" spans="2:16">
+      <c r="B48" s="5"/>
+      <c r="C48" s="28"/>
+      <c r="D48" s="39"/>
+      <c r="E48" s="39"/>
+      <c r="F48" s="39"/>
+      <c r="G48" s="3"/>
+      <c r="H48" s="3"/>
+      <c r="I48" s="3"/>
+      <c r="J48" s="3"/>
+      <c r="K48" s="3"/>
+      <c r="L48" s="3"/>
+      <c r="M48" s="28"/>
+      <c r="N48" s="39"/>
+      <c r="O48" s="39"/>
+      <c r="P48" s="39"/>
+    </row>
+    <row r="49" spans="2:16">
+      <c r="B49" s="5"/>
+      <c r="C49" s="28"/>
+      <c r="D49" s="39"/>
+      <c r="E49" s="39"/>
+      <c r="F49" s="39"/>
+      <c r="G49" s="3"/>
+      <c r="H49" s="3"/>
+      <c r="I49" s="3"/>
+      <c r="J49" s="3"/>
+      <c r="K49" s="3"/>
+      <c r="L49" s="3"/>
+      <c r="M49" s="28"/>
+      <c r="N49" s="39"/>
+      <c r="O49" s="39"/>
+      <c r="P49" s="39"/>
+    </row>
+  </sheetData>
+  <mergeCells count="38">
+    <mergeCell ref="L30:O30"/>
+    <mergeCell ref="N22:P22"/>
+    <mergeCell ref="E14:M14"/>
+    <mergeCell ref="G30:J30"/>
+    <mergeCell ref="N12:P12"/>
+    <mergeCell ref="N21:P21"/>
+    <mergeCell ref="C49:F49"/>
+    <mergeCell ref="N10:P10"/>
+    <mergeCell ref="N13:P13"/>
+    <mergeCell ref="N9:P9"/>
+    <mergeCell ref="N6:P6"/>
+    <mergeCell ref="M49:P49"/>
+    <mergeCell ref="N15:P15"/>
+    <mergeCell ref="E7:M7"/>
+    <mergeCell ref="N24:P24"/>
+    <mergeCell ref="M48:P48"/>
+    <mergeCell ref="B29:O29"/>
+    <mergeCell ref="N27:P27"/>
+    <mergeCell ref="N20:P20"/>
+    <mergeCell ref="N26:P26"/>
+    <mergeCell ref="E12:M12"/>
+    <mergeCell ref="N11:P11"/>
+    <mergeCell ref="C48:F48"/>
+    <mergeCell ref="B3:C3"/>
+    <mergeCell ref="N18:P18"/>
+    <mergeCell ref="B30:E30"/>
+    <mergeCell ref="N14:P14"/>
+    <mergeCell ref="E13:M13"/>
+    <mergeCell ref="N23:P23"/>
+    <mergeCell ref="N17:P17"/>
+    <mergeCell ref="N8:P8"/>
+    <mergeCell ref="N19:P19"/>
+    <mergeCell ref="B5:P5"/>
+    <mergeCell ref="D3:H3"/>
+    <mergeCell ref="N7:P7"/>
+    <mergeCell ref="N25:P25"/>
+    <mergeCell ref="J3:N3"/>
+    <mergeCell ref="N16:P16"/>
+  </mergeCells>
+  <printOptions horizontalCentered="1" verticalCentered="1"/>
+  <pageMargins left="0.19685039370078741" right="0.19685039370078741" top="0.19685039370078741" bottom="0.19685039370078741" header="0" footer="0"/>
+  <pageSetup scale="56" orientation="landscape" verticalDpi="598"/>
+  <drawing r:id="rId1"/>
+</worksheet>
 </file>
--- a/tpl_diario.xlsx
+++ b/tpl_diario.xlsx
@@ -1770,7 +1770,9 @@
         <v>0</v>
       </c>
       <c r="C3" s="39"/>
-      <c r="D3" s="34"/>
+      <c r="D3" s="34" t="s">
+        <v>1</v>
+      </c>
       <c r="E3" s="40"/>
       <c r="F3" s="40"/>
       <c r="G3" s="40"/>
@@ -1778,7 +1780,9 @@
       <c r="I3" s="23" t="s">
         <v>2</v>
       </c>
-      <c r="J3" s="34"/>
+      <c r="J3" s="34" t="s">
+        <v>3</v>
+      </c>
       <c r="K3" s="40"/>
       <c r="L3" s="40"/>
       <c r="M3" s="40"/>
@@ -1786,7 +1790,9 @@
       <c r="O3" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="P3" s="2"/>
+      <c r="P3" s="2" t="s">
+        <v>5</v>
+      </c>
     </row>
     <row r="4" spans="2:16" ht="15" customHeight="1" thickBot="1">
       <c r="B4" s="5"/>
@@ -1868,33 +1874,71 @@
       <c r="P6" s="44"/>
     </row>
     <row r="7" spans="2:16" ht="21.2" customHeight="1">
-      <c r="B7" s="8"/>
-      <c r="C7" s="6"/>
-      <c r="D7" s="6"/>
-      <c r="E7" s="6"/>
-      <c r="F7" s="6"/>
-      <c r="G7" s="6"/>
-      <c r="H7" s="6"/>
-      <c r="I7" s="6"/>
+      <c r="B7" s="8">
+        <v>1</v>
+      </c>
+      <c r="C7" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="D7" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="E7" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="F7" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="G7" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="H7" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="I7" s="6">
+        <v>7</v>
+      </c>
       <c r="J7" s="6"/>
-      <c r="K7" s="6"/>
+      <c r="K7" s="6">
+        <v>25</v>
+      </c>
       <c r="L7" s="6"/>
       <c r="M7" s="6"/>
-      <c r="N7" s="30"/>
+      <c r="N7" s="30" t="s">
+        <v>26</v>
+      </c>
       <c r="O7" s="45"/>
       <c r="P7" s="46"/>
     </row>
     <row r="8" spans="2:16" ht="21.2" customHeight="1">
-      <c r="B8" s="8"/>
-      <c r="C8" s="6"/>
-      <c r="D8" s="6"/>
-      <c r="E8" s="6"/>
-      <c r="F8" s="6"/>
-      <c r="G8" s="6"/>
-      <c r="H8" s="6"/>
-      <c r="I8" s="6"/>
+      <c r="B8" s="8">
+        <v>2</v>
+      </c>
+      <c r="C8" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="D8" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="E8" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="F8" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="G8" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="H8" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="I8" s="6">
+        <v>11</v>
+      </c>
       <c r="J8" s="6"/>
-      <c r="K8" s="6"/>
+      <c r="K8" s="6">
+        <v>44</v>
+      </c>
       <c r="L8" s="6"/>
       <c r="M8" s="6"/>
       <c r="N8" s="30"/>
@@ -1902,32 +1946,68 @@
       <c r="P8" s="46"/>
     </row>
     <row r="9" spans="2:16" ht="21.2" customHeight="1">
-      <c r="B9" s="8"/>
-      <c r="C9" s="6"/>
-      <c r="D9" s="6"/>
-      <c r="E9" s="6"/>
-      <c r="F9" s="6"/>
-      <c r="G9" s="6"/>
-      <c r="H9" s="6"/>
-      <c r="I9" s="6"/>
+      <c r="B9" s="8">
+        <v>3</v>
+      </c>
+      <c r="C9" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="D9" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="E9" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="F9" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="G9" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="H9" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="I9" s="6">
+        <v>14</v>
+      </c>
       <c r="J9" s="6"/>
       <c r="K9" s="6"/>
       <c r="L9" s="6"/>
       <c r="M9" s="6"/>
-      <c r="N9" s="30"/>
+      <c r="N9" s="30" t="s">
+        <v>33</v>
+      </c>
       <c r="O9" s="45"/>
       <c r="P9" s="46"/>
     </row>
     <row r="10" spans="2:16" ht="21.2" customHeight="1">
-      <c r="B10" s="8"/>
-      <c r="C10" s="6"/>
-      <c r="D10" s="6"/>
-      <c r="E10" s="6"/>
-      <c r="F10" s="6"/>
-      <c r="G10" s="6"/>
-      <c r="H10" s="6"/>
-      <c r="I10" s="6"/>
-      <c r="J10" s="6"/>
+      <c r="B10" s="8">
+        <v>4</v>
+      </c>
+      <c r="C10" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="D10" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="E10" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="F10" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="G10" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="H10" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="I10" s="6">
+        <v>8</v>
+      </c>
+      <c r="J10" s="6">
+        <v>5</v>
+      </c>
       <c r="K10" s="6"/>
       <c r="L10" s="6"/>
       <c r="M10" s="6"/>
@@ -1936,10 +2016,16 @@
       <c r="P10" s="46"/>
     </row>
     <row r="11" spans="2:16" ht="21.2" customHeight="1">
-      <c r="B11" s="8"/>
+      <c r="B11" s="8">
+        <v>5</v>
+      </c>
       <c r="C11" s="6"/>
-      <c r="D11" s="6"/>
-      <c r="E11" s="6"/>
+      <c r="D11" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="E11" s="6" t="s">
+        <v>38</v>
+      </c>
       <c r="F11" s="6"/>
       <c r="G11" s="6"/>
       <c r="H11" s="6"/>
@@ -1953,44 +2039,92 @@
       <c r="P11" s="46"/>
     </row>
     <row r="12" spans="2:16" ht="21.2" customHeight="1">
-      <c r="B12" s="8"/>
-      <c r="C12" s="6"/>
-      <c r="D12" s="6"/>
-      <c r="E12" s="6"/>
-      <c r="F12" s="6"/>
-      <c r="G12" s="6"/>
-      <c r="H12" s="6"/>
-      <c r="I12" s="6"/>
-      <c r="J12" s="6"/>
+      <c r="B12" s="8">
+        <v>6</v>
+      </c>
+      <c r="C12" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="D12" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="E12" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="F12" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="G12" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="H12" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="I12" s="6">
+        <v>7</v>
+      </c>
+      <c r="J12" s="6">
+        <v>5</v>
+      </c>
       <c r="K12" s="6"/>
       <c r="L12" s="6"/>
       <c r="M12" s="6"/>
-      <c r="N12" s="30"/>
+      <c r="N12" s="30" t="s">
+        <v>41</v>
+      </c>
       <c r="O12" s="45"/>
       <c r="P12" s="46"/>
     </row>
     <row r="13" spans="2:16" ht="21.2" customHeight="1">
-      <c r="B13" s="8"/>
-      <c r="C13" s="6"/>
-      <c r="D13" s="6"/>
-      <c r="E13" s="6"/>
-      <c r="F13" s="6"/>
-      <c r="G13" s="6"/>
-      <c r="H13" s="6"/>
-      <c r="I13" s="6"/>
-      <c r="J13" s="6"/>
-      <c r="K13" s="6"/>
+      <c r="B13" s="8">
+        <v>7</v>
+      </c>
+      <c r="C13" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="D13" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="E13" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="F13" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="G13" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="H13" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="I13" s="6">
+        <v>10</v>
+      </c>
+      <c r="J13" s="6">
+        <v>8</v>
+      </c>
+      <c r="K13" s="6">
+        <v>20</v>
+      </c>
       <c r="L13" s="6"/>
       <c r="M13" s="6"/>
-      <c r="N13" s="30"/>
+      <c r="N13" s="30" t="s">
+        <v>45</v>
+      </c>
       <c r="O13" s="45"/>
       <c r="P13" s="46"/>
     </row>
     <row r="14" spans="2:16" ht="21.2" customHeight="1">
-      <c r="B14" s="8"/>
+      <c r="B14" s="8">
+        <v>8</v>
+      </c>
       <c r="C14" s="6"/>
-      <c r="D14" s="6"/>
-      <c r="E14" s="6"/>
+      <c r="D14" s="6" t="s">
+        <v>46</v>
+      </c>
+      <c r="E14" s="6" t="s">
+        <v>47</v>
+      </c>
       <c r="F14" s="6"/>
       <c r="G14" s="6"/>
       <c r="H14" s="6"/>
@@ -2004,7 +2138,9 @@
       <c r="P14" s="46"/>
     </row>
     <row r="15" spans="2:16" ht="21.2" customHeight="1">
-      <c r="B15" s="8"/>
+      <c r="B15" s="8">
+        <v>9</v>
+      </c>
       <c r="C15" s="6"/>
       <c r="D15" s="6"/>
       <c r="E15" s="6"/>
@@ -2021,7 +2157,9 @@
       <c r="P15" s="46"/>
     </row>
     <row r="16" spans="2:16" ht="21.2" customHeight="1">
-      <c r="B16" s="8"/>
+      <c r="B16" s="8">
+        <v>10</v>
+      </c>
       <c r="C16" s="6"/>
       <c r="D16" s="6"/>
       <c r="E16" s="6"/>
@@ -2038,7 +2176,9 @@
       <c r="P16" s="46"/>
     </row>
     <row r="17" spans="2:16" ht="21.2" customHeight="1">
-      <c r="B17" s="8"/>
+      <c r="B17" s="8">
+        <v>11</v>
+      </c>
       <c r="C17" s="6"/>
       <c r="D17" s="6"/>
       <c r="E17" s="6"/>
@@ -2055,7 +2195,9 @@
       <c r="P17" s="46"/>
     </row>
     <row r="18" spans="2:16" ht="21.2" customHeight="1">
-      <c r="B18" s="8"/>
+      <c r="B18" s="8">
+        <v>12</v>
+      </c>
       <c r="C18" s="6"/>
       <c r="D18" s="6"/>
       <c r="E18" s="6"/>
@@ -2072,7 +2214,9 @@
       <c r="P18" s="46"/>
     </row>
     <row r="19" spans="2:16" ht="21.2" customHeight="1">
-      <c r="B19" s="8"/>
+      <c r="B19" s="8">
+        <v>13</v>
+      </c>
       <c r="C19" s="6"/>
       <c r="D19" s="6"/>
       <c r="E19" s="6"/>
@@ -2089,7 +2233,9 @@
       <c r="P19" s="46"/>
     </row>
     <row r="20" spans="2:16" ht="21.2" customHeight="1">
-      <c r="B20" s="8"/>
+      <c r="B20" s="8">
+        <v>14</v>
+      </c>
       <c r="C20" s="6"/>
       <c r="D20" s="6"/>
       <c r="E20" s="6"/>
@@ -2106,7 +2252,9 @@
       <c r="P20" s="46"/>
     </row>
     <row r="21" spans="2:16" ht="21.2" customHeight="1">
-      <c r="B21" s="8"/>
+      <c r="B21" s="8">
+        <v>15</v>
+      </c>
       <c r="C21" s="6"/>
       <c r="D21" s="6"/>
       <c r="E21" s="6"/>
@@ -2123,7 +2271,9 @@
       <c r="P21" s="46"/>
     </row>
     <row r="22" spans="2:16" ht="21.2" customHeight="1">
-      <c r="B22" s="8"/>
+      <c r="B22" s="8">
+        <v>16</v>
+      </c>
       <c r="C22" s="6"/>
       <c r="D22" s="6"/>
       <c r="E22" s="6"/>
@@ -2140,7 +2290,9 @@
       <c r="P22" s="46"/>
     </row>
     <row r="23" spans="2:16" ht="21.2" customHeight="1">
-      <c r="B23" s="8"/>
+      <c r="B23" s="8">
+        <v>17</v>
+      </c>
       <c r="C23" s="6"/>
       <c r="D23" s="6"/>
       <c r="E23" s="6"/>
@@ -2157,7 +2309,9 @@
       <c r="P23" s="46"/>
     </row>
     <row r="24" spans="2:16" ht="21.2" customHeight="1">
-      <c r="B24" s="8"/>
+      <c r="B24" s="8">
+        <v>18</v>
+      </c>
       <c r="C24" s="6"/>
       <c r="D24" s="6"/>
       <c r="E24" s="6"/>
@@ -2174,7 +2328,9 @@
       <c r="P24" s="46"/>
     </row>
     <row r="25" spans="2:16" ht="21.2" customHeight="1">
-      <c r="B25" s="8"/>
+      <c r="B25" s="8">
+        <v>19</v>
+      </c>
       <c r="C25" s="6"/>
       <c r="D25" s="6"/>
       <c r="E25" s="6"/>
@@ -2191,7 +2347,9 @@
       <c r="P25" s="46"/>
     </row>
     <row r="26" spans="2:16" ht="21.2" customHeight="1">
-      <c r="B26" s="8"/>
+      <c r="B26" s="8">
+        <v>20</v>
+      </c>
       <c r="C26" s="6"/>
       <c r="D26" s="6"/>
       <c r="E26" s="6"/>
@@ -2208,7 +2366,9 @@
       <c r="P26" s="46"/>
     </row>
     <row r="27" spans="2:16" ht="21.2" customHeight="1" thickBot="1">
-      <c r="B27" s="9"/>
+      <c r="B27" s="9">
+        <v>21</v>
+      </c>
       <c r="C27" s="10"/>
       <c r="D27" s="10"/>
       <c r="E27" s="10"/>
@@ -2324,211 +2484,355 @@
       </c>
     </row>
     <row r="32" spans="2:16" ht="21.2" customHeight="1">
-      <c r="B32" s="8"/>
-      <c r="C32" s="6"/>
-      <c r="D32" s="6"/>
-      <c r="E32" s="24"/>
-      <c r="G32" s="8"/>
+      <c r="B32" s="8">
+        <v>1</v>
+      </c>
+      <c r="C32" s="6" t="s">
+        <v>55</v>
+      </c>
+      <c r="D32" s="6" t="s">
+        <v>56</v>
+      </c>
+      <c r="E32" s="24">
+        <v>33</v>
+      </c>
+      <c r="G32" s="8">
+        <v>1</v>
+      </c>
       <c r="H32" s="6"/>
       <c r="I32" s="6"/>
       <c r="J32" s="21"/>
-      <c r="L32" s="8"/>
+      <c r="L32" s="8">
+        <v>1</v>
+      </c>
       <c r="M32" s="6"/>
       <c r="N32" s="11"/>
       <c r="O32" s="21"/>
     </row>
     <row r="33" spans="2:16" ht="21.2" customHeight="1">
-      <c r="B33" s="8"/>
-      <c r="C33" s="6"/>
-      <c r="D33" s="6"/>
-      <c r="E33" s="24"/>
-      <c r="G33" s="8"/>
+      <c r="B33" s="8">
+        <v>2</v>
+      </c>
+      <c r="C33" s="6" t="s">
+        <v>57</v>
+      </c>
+      <c r="D33" s="6" t="s">
+        <v>58</v>
+      </c>
+      <c r="E33" s="24">
+        <v>83</v>
+      </c>
+      <c r="G33" s="8">
+        <v>2</v>
+      </c>
       <c r="H33" s="6"/>
       <c r="I33" s="6"/>
       <c r="J33" s="21"/>
-      <c r="L33" s="8"/>
+      <c r="L33" s="8">
+        <v>2</v>
+      </c>
       <c r="M33" s="6"/>
       <c r="N33" s="11"/>
       <c r="O33" s="21"/>
     </row>
     <row r="34" spans="2:16" ht="21.2" customHeight="1">
-      <c r="B34" s="8"/>
-      <c r="C34" s="6"/>
-      <c r="D34" s="6"/>
-      <c r="E34" s="24"/>
-      <c r="G34" s="8"/>
+      <c r="B34" s="8">
+        <v>3</v>
+      </c>
+      <c r="C34" s="6" t="s">
+        <v>59</v>
+      </c>
+      <c r="D34" s="6" t="s">
+        <v>60</v>
+      </c>
+      <c r="E34" s="24">
+        <v>81</v>
+      </c>
+      <c r="G34" s="8">
+        <v>3</v>
+      </c>
       <c r="H34" s="6"/>
       <c r="I34" s="6"/>
       <c r="J34" s="21"/>
-      <c r="L34" s="8"/>
+      <c r="L34" s="8">
+        <v>3</v>
+      </c>
       <c r="M34" s="6"/>
       <c r="N34" s="11"/>
       <c r="O34" s="21"/>
     </row>
     <row r="35" spans="2:16" ht="21.2" customHeight="1">
-      <c r="B35" s="8"/>
-      <c r="C35" s="6"/>
-      <c r="D35" s="6"/>
-      <c r="E35" s="24"/>
-      <c r="G35" s="8"/>
+      <c r="B35" s="8">
+        <v>4</v>
+      </c>
+      <c r="C35" s="6" t="s">
+        <v>61</v>
+      </c>
+      <c r="D35" s="6" t="s">
+        <v>62</v>
+      </c>
+      <c r="E35" s="24">
+        <v>28</v>
+      </c>
+      <c r="G35" s="8">
+        <v>4</v>
+      </c>
       <c r="H35" s="6"/>
       <c r="I35" s="6"/>
       <c r="J35" s="21"/>
-      <c r="L35" s="8"/>
+      <c r="L35" s="8">
+        <v>4</v>
+      </c>
       <c r="M35" s="6"/>
       <c r="N35" s="11"/>
       <c r="O35" s="21"/>
     </row>
     <row r="36" spans="2:16" ht="21.2" customHeight="1">
-      <c r="B36" s="8"/>
-      <c r="C36" s="6"/>
-      <c r="D36" s="6"/>
-      <c r="E36" s="24"/>
-      <c r="G36" s="8"/>
+      <c r="B36" s="8">
+        <v>5</v>
+      </c>
+      <c r="C36" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="D36" s="6" t="s">
+        <v>64</v>
+      </c>
+      <c r="E36" s="24">
+        <v>23</v>
+      </c>
+      <c r="G36" s="8">
+        <v>5</v>
+      </c>
       <c r="H36" s="6"/>
       <c r="I36" s="6"/>
       <c r="J36" s="21"/>
-      <c r="L36" s="8"/>
+      <c r="L36" s="8">
+        <v>5</v>
+      </c>
       <c r="M36" s="6"/>
       <c r="N36" s="11"/>
       <c r="O36" s="21"/>
     </row>
     <row r="37" spans="2:16" ht="21.2" customHeight="1">
-      <c r="B37" s="8"/>
-      <c r="C37" s="6"/>
-      <c r="D37" s="6"/>
-      <c r="E37" s="24"/>
-      <c r="G37" s="8"/>
+      <c r="B37" s="8">
+        <v>6</v>
+      </c>
+      <c r="C37" s="6" t="s">
+        <v>65</v>
+      </c>
+      <c r="D37" s="6" t="s">
+        <v>66</v>
+      </c>
+      <c r="E37" s="24">
+        <v>21</v>
+      </c>
+      <c r="G37" s="8">
+        <v>6</v>
+      </c>
       <c r="H37" s="6"/>
       <c r="I37" s="6"/>
       <c r="J37" s="21"/>
-      <c r="L37" s="8"/>
+      <c r="L37" s="8">
+        <v>6</v>
+      </c>
       <c r="M37" s="6"/>
       <c r="N37" s="11"/>
       <c r="O37" s="21"/>
     </row>
     <row r="38" spans="2:16" ht="21.2" customHeight="1">
-      <c r="B38" s="8"/>
-      <c r="C38" s="6"/>
-      <c r="D38" s="6"/>
-      <c r="E38" s="24"/>
-      <c r="G38" s="8"/>
+      <c r="B38" s="8">
+        <v>7</v>
+      </c>
+      <c r="C38" s="6" t="s">
+        <v>67</v>
+      </c>
+      <c r="D38" s="6" t="s">
+        <v>68</v>
+      </c>
+      <c r="E38" s="24">
+        <v>45</v>
+      </c>
+      <c r="G38" s="8">
+        <v>7</v>
+      </c>
       <c r="H38" s="6"/>
       <c r="I38" s="6"/>
       <c r="J38" s="21"/>
-      <c r="L38" s="8"/>
+      <c r="L38" s="8">
+        <v>7</v>
+      </c>
       <c r="M38" s="6"/>
       <c r="N38" s="11"/>
       <c r="O38" s="21"/>
     </row>
     <row r="39" spans="2:16" ht="21.2" customHeight="1">
-      <c r="B39" s="8"/>
-      <c r="C39" s="6"/>
-      <c r="D39" s="6"/>
-      <c r="E39" s="24"/>
-      <c r="G39" s="8"/>
+      <c r="B39" s="8">
+        <v>8</v>
+      </c>
+      <c r="C39" s="6" t="s">
+        <v>69</v>
+      </c>
+      <c r="D39" s="6" t="s">
+        <v>70</v>
+      </c>
+      <c r="E39" s="24">
+        <v>117</v>
+      </c>
+      <c r="G39" s="8">
+        <v>8</v>
+      </c>
       <c r="H39" s="6"/>
       <c r="I39" s="6"/>
       <c r="J39" s="21"/>
-      <c r="L39" s="8"/>
+      <c r="L39" s="8">
+        <v>8</v>
+      </c>
       <c r="M39" s="6"/>
       <c r="N39" s="11"/>
       <c r="O39" s="21"/>
     </row>
     <row r="40" spans="2:16" ht="21.2" customHeight="1">
-      <c r="B40" s="8"/>
-      <c r="C40" s="6"/>
-      <c r="D40" s="6"/>
-      <c r="E40" s="24"/>
-      <c r="G40" s="8"/>
+      <c r="B40" s="8">
+        <v>9</v>
+      </c>
+      <c r="C40" s="6" t="s">
+        <v>71</v>
+      </c>
+      <c r="D40" s="6" t="s">
+        <v>72</v>
+      </c>
+      <c r="E40" s="24">
+        <v>14</v>
+      </c>
+      <c r="G40" s="8">
+        <v>9</v>
+      </c>
       <c r="H40" s="6"/>
       <c r="I40" s="6"/>
       <c r="J40" s="21"/>
-      <c r="L40" s="8"/>
+      <c r="L40" s="8">
+        <v>9</v>
+      </c>
       <c r="M40" s="6"/>
       <c r="N40" s="11"/>
       <c r="O40" s="21"/>
     </row>
     <row r="41" spans="2:16" ht="21.2" customHeight="1">
-      <c r="B41" s="8"/>
+      <c r="B41" s="8">
+        <v>10</v>
+      </c>
       <c r="C41" s="6"/>
       <c r="D41" s="6"/>
       <c r="E41" s="21"/>
-      <c r="G41" s="8"/>
+      <c r="G41" s="8">
+        <v>10</v>
+      </c>
       <c r="H41" s="6"/>
       <c r="I41" s="6"/>
       <c r="J41" s="21"/>
-      <c r="L41" s="8"/>
+      <c r="L41" s="8">
+        <v>10</v>
+      </c>
       <c r="M41" s="6"/>
       <c r="N41" s="11"/>
       <c r="O41" s="21"/>
     </row>
     <row r="42" spans="2:16" ht="21.2" customHeight="1">
-      <c r="B42" s="8"/>
+      <c r="B42" s="8">
+        <v>11</v>
+      </c>
       <c r="C42" s="6"/>
       <c r="D42" s="6"/>
       <c r="E42" s="21"/>
-      <c r="G42" s="8"/>
+      <c r="G42" s="8">
+        <v>11</v>
+      </c>
       <c r="H42" s="6"/>
       <c r="I42" s="6"/>
       <c r="J42" s="21"/>
-      <c r="L42" s="8"/>
+      <c r="L42" s="8">
+        <v>11</v>
+      </c>
       <c r="M42" s="6"/>
       <c r="N42" s="11"/>
       <c r="O42" s="21"/>
     </row>
     <row r="43" spans="2:16" ht="21.2" customHeight="1">
-      <c r="B43" s="8"/>
+      <c r="B43" s="8">
+        <v>12</v>
+      </c>
       <c r="C43" s="6"/>
       <c r="D43" s="6"/>
       <c r="E43" s="21"/>
-      <c r="G43" s="8"/>
+      <c r="G43" s="8">
+        <v>12</v>
+      </c>
       <c r="H43" s="6"/>
       <c r="I43" s="6"/>
       <c r="J43" s="21"/>
-      <c r="L43" s="8"/>
+      <c r="L43" s="8">
+        <v>12</v>
+      </c>
       <c r="M43" s="6"/>
       <c r="N43" s="11"/>
       <c r="O43" s="21"/>
     </row>
     <row r="44" spans="2:16" ht="21.2" customHeight="1">
-      <c r="B44" s="8"/>
+      <c r="B44" s="8">
+        <v>13</v>
+      </c>
       <c r="C44" s="6"/>
       <c r="D44" s="6"/>
       <c r="E44" s="21"/>
-      <c r="G44" s="8"/>
+      <c r="G44" s="8">
+        <v>13</v>
+      </c>
       <c r="H44" s="6"/>
       <c r="I44" s="6"/>
       <c r="J44" s="21"/>
-      <c r="L44" s="8"/>
+      <c r="L44" s="8">
+        <v>13</v>
+      </c>
       <c r="M44" s="6"/>
       <c r="N44" s="11"/>
       <c r="O44" s="21"/>
     </row>
     <row r="45" spans="2:16" ht="21.2" customHeight="1">
-      <c r="B45" s="8"/>
+      <c r="B45" s="8">
+        <v>14</v>
+      </c>
       <c r="C45" s="6"/>
       <c r="D45" s="6"/>
       <c r="E45" s="21"/>
-      <c r="G45" s="8"/>
+      <c r="G45" s="8">
+        <v>14</v>
+      </c>
       <c r="H45" s="6"/>
       <c r="I45" s="6"/>
       <c r="J45" s="21"/>
-      <c r="L45" s="8"/>
+      <c r="L45" s="8">
+        <v>14</v>
+      </c>
       <c r="M45" s="6"/>
       <c r="N45" s="11"/>
       <c r="O45" s="21"/>
     </row>
     <row r="46" spans="2:16" ht="21.2" customHeight="1" thickBot="1">
-      <c r="B46" s="9"/>
+      <c r="B46" s="9">
+        <v>15</v>
+      </c>
       <c r="C46" s="10"/>
       <c r="D46" s="10"/>
       <c r="E46" s="22"/>
-      <c r="G46" s="9"/>
+      <c r="G46" s="9">
+        <v>15</v>
+      </c>
       <c r="H46" s="10"/>
       <c r="I46" s="10"/>
       <c r="J46" s="22"/>
-      <c r="L46" s="9"/>
+      <c r="L46" s="9">
+        <v>15</v>
+      </c>
       <c r="M46" s="10"/>
       <c r="N46" s="12"/>
       <c r="O46" s="22"/>
@@ -2653,7 +2957,9 @@
         <v>0</v>
       </c>
       <c r="C3" s="39"/>
-      <c r="D3" s="34"/>
+      <c r="D3" s="34" t="s">
+        <v>1</v>
+      </c>
       <c r="E3" s="40"/>
       <c r="F3" s="40"/>
       <c r="G3" s="40"/>
@@ -2661,7 +2967,9 @@
       <c r="I3" s="23" t="s">
         <v>2</v>
       </c>
-      <c r="J3" s="34"/>
+      <c r="J3" s="34" t="s">
+        <v>3</v>
+      </c>
       <c r="K3" s="40"/>
       <c r="L3" s="40"/>
       <c r="M3" s="40"/>
@@ -2669,7 +2977,9 @@
       <c r="O3" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="P3" s="2"/>
+      <c r="P3" s="2" t="s">
+        <v>73</v>
+      </c>
     </row>
     <row r="4" spans="2:16" ht="15" customHeight="1" thickBot="1">
       <c r="B4" s="5"/>
@@ -2751,10 +3061,16 @@
       <c r="P6" s="44"/>
     </row>
     <row r="7" spans="2:16" ht="21.2" customHeight="1">
-      <c r="B7" s="8"/>
+      <c r="B7" s="8">
+        <v>1</v>
+      </c>
       <c r="C7" s="6"/>
-      <c r="D7" s="6"/>
-      <c r="E7" s="35"/>
+      <c r="D7" s="6" t="s">
+        <v>74</v>
+      </c>
+      <c r="E7" s="35" t="s">
+        <v>75</v>
+      </c>
       <c r="F7" s="45"/>
       <c r="G7" s="45"/>
       <c r="H7" s="45"/>
@@ -2768,16 +3084,34 @@
       <c r="P7" s="46"/>
     </row>
     <row r="8" spans="2:16" ht="21.2" customHeight="1">
-      <c r="B8" s="8"/>
-      <c r="C8" s="6"/>
-      <c r="D8" s="6"/>
-      <c r="E8" s="6"/>
-      <c r="F8" s="6"/>
-      <c r="G8" s="6"/>
-      <c r="H8" s="6"/>
-      <c r="I8" s="6"/>
+      <c r="B8" s="8">
+        <v>2</v>
+      </c>
+      <c r="C8" s="6" t="s">
+        <v>76</v>
+      </c>
+      <c r="D8" s="6" t="s">
+        <v>77</v>
+      </c>
+      <c r="E8" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="F8" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="G8" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="H8" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="I8" s="6">
+        <v>7</v>
+      </c>
       <c r="J8" s="6"/>
-      <c r="K8" s="6"/>
+      <c r="K8" s="6">
+        <v>38</v>
+      </c>
       <c r="L8" s="6"/>
       <c r="M8" s="6"/>
       <c r="N8" s="30"/>
@@ -2785,27 +3119,55 @@
       <c r="P8" s="46"/>
     </row>
     <row r="9" spans="2:16" ht="21.2" customHeight="1">
-      <c r="B9" s="8"/>
-      <c r="C9" s="6"/>
-      <c r="D9" s="6"/>
-      <c r="E9" s="6"/>
-      <c r="F9" s="6"/>
-      <c r="G9" s="6"/>
-      <c r="H9" s="6"/>
-      <c r="I9" s="6"/>
-      <c r="J9" s="6"/>
-      <c r="K9" s="6"/>
+      <c r="B9" s="8">
+        <v>3</v>
+      </c>
+      <c r="C9" s="6" t="s">
+        <v>78</v>
+      </c>
+      <c r="D9" s="6" t="s">
+        <v>79</v>
+      </c>
+      <c r="E9" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="F9" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="G9" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="H9" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="I9" s="6">
+        <v>10</v>
+      </c>
+      <c r="J9" s="6">
+        <v>8</v>
+      </c>
+      <c r="K9" s="6">
+        <v>19</v>
+      </c>
       <c r="L9" s="6"/>
       <c r="M9" s="6"/>
-      <c r="N9" s="30"/>
+      <c r="N9" s="30" t="s">
+        <v>80</v>
+      </c>
       <c r="O9" s="45"/>
       <c r="P9" s="46"/>
     </row>
     <row r="10" spans="2:16" ht="21.2" customHeight="1">
-      <c r="B10" s="8"/>
+      <c r="B10" s="8">
+        <v>4</v>
+      </c>
       <c r="C10" s="6"/>
-      <c r="D10" s="6"/>
-      <c r="E10" s="6"/>
+      <c r="D10" s="6" t="s">
+        <v>81</v>
+      </c>
+      <c r="E10" s="6" t="s">
+        <v>82</v>
+      </c>
       <c r="F10" s="6"/>
       <c r="G10" s="6"/>
       <c r="H10" s="6"/>
@@ -2819,16 +3181,32 @@
       <c r="P10" s="46"/>
     </row>
     <row r="11" spans="2:16" ht="21.2" customHeight="1">
-      <c r="B11" s="8"/>
-      <c r="C11" s="6"/>
-      <c r="D11" s="6"/>
-      <c r="E11" s="6"/>
-      <c r="F11" s="6"/>
-      <c r="G11" s="6"/>
-      <c r="H11" s="6"/>
+      <c r="B11" s="8">
+        <v>5</v>
+      </c>
+      <c r="C11" s="6" t="s">
+        <v>57</v>
+      </c>
+      <c r="D11" s="6" t="s">
+        <v>83</v>
+      </c>
+      <c r="E11" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="F11" s="6" t="s">
+        <v>84</v>
+      </c>
+      <c r="G11" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="H11" s="6" t="s">
+        <v>25</v>
+      </c>
       <c r="I11" s="6"/>
       <c r="J11" s="6"/>
-      <c r="K11" s="6"/>
+      <c r="K11" s="6">
+        <v>42</v>
+      </c>
       <c r="L11" s="6"/>
       <c r="M11" s="6"/>
       <c r="N11" s="30"/>
@@ -2836,30 +3214,62 @@
       <c r="P11" s="46"/>
     </row>
     <row r="12" spans="2:16" ht="21.2" customHeight="1">
-      <c r="B12" s="8"/>
-      <c r="C12" s="6"/>
-      <c r="D12" s="6"/>
-      <c r="E12" s="6"/>
-      <c r="F12" s="6"/>
-      <c r="G12" s="6"/>
-      <c r="H12" s="6"/>
+      <c r="B12" s="8">
+        <v>6</v>
+      </c>
+      <c r="C12" s="6" t="s">
+        <v>71</v>
+      </c>
+      <c r="D12" s="6" t="s">
+        <v>85</v>
+      </c>
+      <c r="E12" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="F12" s="6" t="s">
+        <v>84</v>
+      </c>
+      <c r="G12" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="H12" s="6" t="s">
+        <v>25</v>
+      </c>
       <c r="I12" s="6"/>
       <c r="J12" s="6"/>
-      <c r="K12" s="6"/>
+      <c r="K12" s="6">
+        <v>23</v>
+      </c>
       <c r="L12" s="6"/>
       <c r="M12" s="6"/>
-      <c r="N12" s="30"/>
+      <c r="N12" s="30" t="s">
+        <v>86</v>
+      </c>
       <c r="O12" s="45"/>
       <c r="P12" s="46"/>
     </row>
     <row r="13" spans="2:16" ht="21.2" customHeight="1">
-      <c r="B13" s="8"/>
-      <c r="C13" s="6"/>
-      <c r="D13" s="6"/>
-      <c r="E13" s="6"/>
-      <c r="F13" s="6"/>
-      <c r="G13" s="6"/>
-      <c r="H13" s="6"/>
+      <c r="B13" s="8">
+        <v>7</v>
+      </c>
+      <c r="C13" s="6" t="s">
+        <v>87</v>
+      </c>
+      <c r="D13" s="6" t="s">
+        <v>88</v>
+      </c>
+      <c r="E13" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="F13" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="G13" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="H13" s="6" t="s">
+        <v>25</v>
+      </c>
       <c r="I13" s="6"/>
       <c r="J13" s="6"/>
       <c r="K13" s="6"/>
@@ -2870,16 +3280,34 @@
       <c r="P13" s="46"/>
     </row>
     <row r="14" spans="2:16" ht="21.2" customHeight="1">
-      <c r="B14" s="8"/>
-      <c r="C14" s="6"/>
-      <c r="D14" s="6"/>
-      <c r="E14" s="6"/>
-      <c r="F14" s="6"/>
-      <c r="G14" s="6"/>
-      <c r="H14" s="6"/>
-      <c r="I14" s="6"/>
+      <c r="B14" s="8">
+        <v>8</v>
+      </c>
+      <c r="C14" s="6" t="s">
+        <v>87</v>
+      </c>
+      <c r="D14" s="6" t="s">
+        <v>89</v>
+      </c>
+      <c r="E14" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="F14" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="G14" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="H14" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="I14" s="6">
+        <v>11</v>
+      </c>
       <c r="J14" s="6"/>
-      <c r="K14" s="6"/>
+      <c r="K14" s="6">
+        <v>35</v>
+      </c>
       <c r="L14" s="6"/>
       <c r="M14" s="6"/>
       <c r="N14" s="30"/>
@@ -2887,44 +3315,92 @@
       <c r="P14" s="46"/>
     </row>
     <row r="15" spans="2:16" ht="21.2" customHeight="1">
-      <c r="B15" s="8"/>
-      <c r="C15" s="6"/>
-      <c r="D15" s="6"/>
-      <c r="E15" s="6"/>
-      <c r="F15" s="6"/>
-      <c r="G15" s="6"/>
-      <c r="H15" s="6"/>
-      <c r="I15" s="6"/>
-      <c r="J15" s="6"/>
-      <c r="K15" s="6"/>
+      <c r="B15" s="8">
+        <v>9</v>
+      </c>
+      <c r="C15" s="6" t="s">
+        <v>90</v>
+      </c>
+      <c r="D15" s="6" t="s">
+        <v>91</v>
+      </c>
+      <c r="E15" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="F15" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="G15" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="H15" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="I15" s="6">
+        <v>11</v>
+      </c>
+      <c r="J15" s="6">
+        <v>11</v>
+      </c>
+      <c r="K15" s="6">
+        <v>39</v>
+      </c>
       <c r="L15" s="6"/>
       <c r="M15" s="6"/>
-      <c r="N15" s="30"/>
+      <c r="N15" s="30" t="s">
+        <v>92</v>
+      </c>
       <c r="O15" s="45"/>
       <c r="P15" s="46"/>
     </row>
     <row r="16" spans="2:16" ht="21.2" customHeight="1">
-      <c r="B16" s="8"/>
-      <c r="C16" s="6"/>
-      <c r="D16" s="6"/>
-      <c r="E16" s="6"/>
-      <c r="F16" s="6"/>
-      <c r="G16" s="6"/>
-      <c r="H16" s="6"/>
-      <c r="I16" s="6"/>
+      <c r="B16" s="8">
+        <v>10</v>
+      </c>
+      <c r="C16" s="6" t="s">
+        <v>55</v>
+      </c>
+      <c r="D16" s="6" t="s">
+        <v>93</v>
+      </c>
+      <c r="E16" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="F16" s="6" t="s">
+        <v>84</v>
+      </c>
+      <c r="G16" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="H16" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="I16" s="6">
+        <v>3</v>
+      </c>
       <c r="J16" s="6"/>
-      <c r="K16" s="6"/>
+      <c r="K16" s="6">
+        <v>32</v>
+      </c>
       <c r="L16" s="6"/>
       <c r="M16" s="6"/>
-      <c r="N16" s="30"/>
+      <c r="N16" s="30" t="s">
+        <v>94</v>
+      </c>
       <c r="O16" s="45"/>
       <c r="P16" s="46"/>
     </row>
     <row r="17" spans="2:16" ht="21.2" customHeight="1">
-      <c r="B17" s="8"/>
+      <c r="B17" s="8">
+        <v>11</v>
+      </c>
       <c r="C17" s="6"/>
-      <c r="D17" s="6"/>
-      <c r="E17" s="6"/>
+      <c r="D17" s="6" t="s">
+        <v>95</v>
+      </c>
+      <c r="E17" s="6" t="s">
+        <v>96</v>
+      </c>
       <c r="F17" s="6"/>
       <c r="G17" s="6"/>
       <c r="H17" s="6"/>
@@ -2938,31 +3414,69 @@
       <c r="P17" s="46"/>
     </row>
     <row r="18" spans="2:16" ht="21.2" customHeight="1">
-      <c r="B18" s="8"/>
-      <c r="C18" s="6"/>
-      <c r="D18" s="6"/>
-      <c r="E18" s="6"/>
-      <c r="F18" s="6"/>
-      <c r="G18" s="6"/>
-      <c r="H18" s="6"/>
-      <c r="I18" s="6"/>
-      <c r="J18" s="6"/>
-      <c r="K18" s="6"/>
+      <c r="B18" s="8">
+        <v>12</v>
+      </c>
+      <c r="C18" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="D18" s="6" t="s">
+        <v>97</v>
+      </c>
+      <c r="E18" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="F18" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="G18" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="H18" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="I18" s="6">
+        <v>10</v>
+      </c>
+      <c r="J18" s="6">
+        <v>8</v>
+      </c>
+      <c r="K18" s="6">
+        <v>19</v>
+      </c>
       <c r="L18" s="6"/>
       <c r="M18" s="6"/>
-      <c r="N18" s="30"/>
+      <c r="N18" s="30" t="s">
+        <v>98</v>
+      </c>
       <c r="O18" s="45"/>
       <c r="P18" s="46"/>
     </row>
     <row r="19" spans="2:16" ht="21.2" customHeight="1">
-      <c r="B19" s="8"/>
-      <c r="C19" s="6"/>
-      <c r="D19" s="6"/>
-      <c r="E19" s="6"/>
-      <c r="F19" s="6"/>
-      <c r="G19" s="6"/>
-      <c r="H19" s="6"/>
-      <c r="I19" s="6"/>
+      <c r="B19" s="8">
+        <v>13</v>
+      </c>
+      <c r="C19" s="6" t="s">
+        <v>59</v>
+      </c>
+      <c r="D19" s="6" t="s">
+        <v>99</v>
+      </c>
+      <c r="E19" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="F19" s="6" t="s">
+        <v>84</v>
+      </c>
+      <c r="G19" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="H19" s="6" t="s">
+        <v>100</v>
+      </c>
+      <c r="I19" s="6">
+        <v>3.5</v>
+      </c>
       <c r="J19" s="6"/>
       <c r="K19" s="6"/>
       <c r="L19" s="6"/>
@@ -2972,7 +3486,9 @@
       <c r="P19" s="46"/>
     </row>
     <row r="20" spans="2:16" ht="21.2" customHeight="1">
-      <c r="B20" s="8"/>
+      <c r="B20" s="8">
+        <v>14</v>
+      </c>
       <c r="C20" s="6"/>
       <c r="D20" s="6"/>
       <c r="E20" s="6"/>
@@ -2989,7 +3505,9 @@
       <c r="P20" s="46"/>
     </row>
     <row r="21" spans="2:16" ht="21.2" customHeight="1">
-      <c r="B21" s="8"/>
+      <c r="B21" s="8">
+        <v>15</v>
+      </c>
       <c r="C21" s="6"/>
       <c r="D21" s="6"/>
       <c r="E21" s="6"/>
@@ -3006,7 +3524,9 @@
       <c r="P21" s="46"/>
     </row>
     <row r="22" spans="2:16" ht="21.2" customHeight="1">
-      <c r="B22" s="8"/>
+      <c r="B22" s="8">
+        <v>16</v>
+      </c>
       <c r="C22" s="6"/>
       <c r="D22" s="6"/>
       <c r="E22" s="6"/>
@@ -3023,7 +3543,9 @@
       <c r="P22" s="46"/>
     </row>
     <row r="23" spans="2:16" ht="21.2" customHeight="1">
-      <c r="B23" s="8"/>
+      <c r="B23" s="8">
+        <v>17</v>
+      </c>
       <c r="C23" s="6"/>
       <c r="D23" s="6"/>
       <c r="E23" s="6"/>
@@ -3040,7 +3562,9 @@
       <c r="P23" s="46"/>
     </row>
     <row r="24" spans="2:16" ht="21.2" customHeight="1">
-      <c r="B24" s="8"/>
+      <c r="B24" s="8">
+        <v>18</v>
+      </c>
       <c r="C24" s="6"/>
       <c r="D24" s="6"/>
       <c r="E24" s="6"/>
@@ -3057,7 +3581,9 @@
       <c r="P24" s="46"/>
     </row>
     <row r="25" spans="2:16" ht="21.2" customHeight="1">
-      <c r="B25" s="8"/>
+      <c r="B25" s="8">
+        <v>19</v>
+      </c>
       <c r="C25" s="6"/>
       <c r="D25" s="6"/>
       <c r="E25" s="6"/>
@@ -3074,7 +3600,9 @@
       <c r="P25" s="46"/>
     </row>
     <row r="26" spans="2:16" ht="21.2" customHeight="1">
-      <c r="B26" s="8"/>
+      <c r="B26" s="8">
+        <v>20</v>
+      </c>
       <c r="C26" s="6"/>
       <c r="D26" s="6"/>
       <c r="E26" s="6"/>
@@ -3091,7 +3619,9 @@
       <c r="P26" s="46"/>
     </row>
     <row r="27" spans="2:16" ht="21.2" customHeight="1" thickBot="1">
-      <c r="B27" s="9"/>
+      <c r="B27" s="9">
+        <v>21</v>
+      </c>
       <c r="C27" s="10"/>
       <c r="D27" s="10"/>
       <c r="E27" s="10"/>
@@ -3207,211 +3737,385 @@
       </c>
     </row>
     <row r="32" spans="2:16" ht="21.2" customHeight="1">
-      <c r="B32" s="8"/>
-      <c r="C32" s="6"/>
-      <c r="D32" s="6"/>
-      <c r="E32" s="24"/>
-      <c r="G32" s="8"/>
-      <c r="H32" s="6"/>
-      <c r="I32" s="6"/>
-      <c r="J32" s="24"/>
-      <c r="L32" s="8"/>
+      <c r="B32" s="8">
+        <v>1</v>
+      </c>
+      <c r="C32" s="6" t="s">
+        <v>55</v>
+      </c>
+      <c r="D32" s="6" t="s">
+        <v>101</v>
+      </c>
+      <c r="E32" s="24">
+        <v>13</v>
+      </c>
+      <c r="G32" s="8">
+        <v>1</v>
+      </c>
+      <c r="H32" s="6" t="s">
+        <v>57</v>
+      </c>
+      <c r="I32" s="6" t="s">
+        <v>83</v>
+      </c>
+      <c r="J32" s="24">
+        <v>142</v>
+      </c>
+      <c r="L32" s="8">
+        <v>1</v>
+      </c>
       <c r="M32" s="6"/>
       <c r="N32" s="11"/>
       <c r="O32" s="21"/>
     </row>
     <row r="33" spans="2:16" ht="21.2" customHeight="1">
-      <c r="B33" s="8"/>
-      <c r="C33" s="6"/>
-      <c r="D33" s="6"/>
-      <c r="E33" s="24"/>
-      <c r="G33" s="8"/>
-      <c r="H33" s="6"/>
-      <c r="I33" s="6"/>
-      <c r="J33" s="24"/>
-      <c r="L33" s="8"/>
+      <c r="B33" s="8">
+        <v>2</v>
+      </c>
+      <c r="C33" s="6" t="s">
+        <v>69</v>
+      </c>
+      <c r="D33" s="6" t="s">
+        <v>102</v>
+      </c>
+      <c r="E33" s="24">
+        <v>109</v>
+      </c>
+      <c r="G33" s="8">
+        <v>2</v>
+      </c>
+      <c r="H33" s="6" t="s">
+        <v>71</v>
+      </c>
+      <c r="I33" s="6" t="s">
+        <v>85</v>
+      </c>
+      <c r="J33" s="24">
+        <v>42</v>
+      </c>
+      <c r="L33" s="8">
+        <v>2</v>
+      </c>
       <c r="M33" s="6"/>
       <c r="N33" s="11"/>
       <c r="O33" s="21"/>
     </row>
     <row r="34" spans="2:16" ht="21.2" customHeight="1">
-      <c r="B34" s="8"/>
-      <c r="C34" s="6"/>
-      <c r="D34" s="6"/>
-      <c r="E34" s="24"/>
-      <c r="G34" s="8"/>
-      <c r="H34" s="6"/>
-      <c r="I34" s="6"/>
-      <c r="J34" s="24"/>
-      <c r="L34" s="8"/>
+      <c r="B34" s="8">
+        <v>3</v>
+      </c>
+      <c r="C34" s="6" t="s">
+        <v>67</v>
+      </c>
+      <c r="D34" s="6" t="s">
+        <v>103</v>
+      </c>
+      <c r="E34" s="24">
+        <v>57</v>
+      </c>
+      <c r="G34" s="8">
+        <v>3</v>
+      </c>
+      <c r="H34" s="6" t="s">
+        <v>55</v>
+      </c>
+      <c r="I34" s="6" t="s">
+        <v>93</v>
+      </c>
+      <c r="J34" s="24">
+        <v>37</v>
+      </c>
+      <c r="L34" s="8">
+        <v>3</v>
+      </c>
       <c r="M34" s="6"/>
       <c r="N34" s="11"/>
       <c r="O34" s="21"/>
     </row>
     <row r="35" spans="2:16" ht="21.2" customHeight="1">
-      <c r="B35" s="8"/>
-      <c r="C35" s="6"/>
-      <c r="D35" s="6"/>
-      <c r="E35" s="24"/>
-      <c r="G35" s="8"/>
-      <c r="H35" s="6"/>
-      <c r="I35" s="6"/>
-      <c r="J35" s="24"/>
-      <c r="L35" s="8"/>
+      <c r="B35" s="8">
+        <v>4</v>
+      </c>
+      <c r="C35" s="6" t="s">
+        <v>104</v>
+      </c>
+      <c r="D35" s="6" t="s">
+        <v>105</v>
+      </c>
+      <c r="E35" s="24">
+        <v>40</v>
+      </c>
+      <c r="G35" s="8">
+        <v>4</v>
+      </c>
+      <c r="H35" s="6" t="s">
+        <v>59</v>
+      </c>
+      <c r="I35" s="6" t="s">
+        <v>99</v>
+      </c>
+      <c r="J35" s="24">
+        <v>119</v>
+      </c>
+      <c r="L35" s="8">
+        <v>4</v>
+      </c>
       <c r="M35" s="6"/>
       <c r="N35" s="11"/>
       <c r="O35" s="21"/>
     </row>
     <row r="36" spans="2:16" ht="21.2" customHeight="1">
-      <c r="B36" s="8"/>
-      <c r="C36" s="6"/>
-      <c r="D36" s="6"/>
-      <c r="E36" s="24"/>
-      <c r="G36" s="8"/>
+      <c r="B36" s="8">
+        <v>5</v>
+      </c>
+      <c r="C36" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="D36" s="6" t="s">
+        <v>106</v>
+      </c>
+      <c r="E36" s="24">
+        <v>35</v>
+      </c>
+      <c r="G36" s="8">
+        <v>5</v>
+      </c>
       <c r="H36" s="6"/>
       <c r="I36" s="6"/>
       <c r="J36" s="24"/>
-      <c r="L36" s="8"/>
+      <c r="L36" s="8">
+        <v>5</v>
+      </c>
       <c r="M36" s="6"/>
       <c r="N36" s="11"/>
       <c r="O36" s="21"/>
     </row>
     <row r="37" spans="2:16" ht="21.2" customHeight="1">
-      <c r="B37" s="8"/>
-      <c r="C37" s="6"/>
-      <c r="D37" s="6"/>
-      <c r="E37" s="24"/>
-      <c r="G37" s="8"/>
+      <c r="B37" s="8">
+        <v>6</v>
+      </c>
+      <c r="C37" s="6" t="s">
+        <v>65</v>
+      </c>
+      <c r="D37" s="6" t="s">
+        <v>107</v>
+      </c>
+      <c r="E37" s="24">
+        <v>86</v>
+      </c>
+      <c r="G37" s="8">
+        <v>6</v>
+      </c>
       <c r="H37" s="6"/>
       <c r="I37" s="6"/>
       <c r="J37" s="21"/>
-      <c r="L37" s="8"/>
+      <c r="L37" s="8">
+        <v>6</v>
+      </c>
       <c r="M37" s="6"/>
       <c r="N37" s="11"/>
       <c r="O37" s="21"/>
     </row>
     <row r="38" spans="2:16" ht="21.2" customHeight="1">
-      <c r="B38" s="8"/>
-      <c r="C38" s="6"/>
-      <c r="D38" s="6"/>
-      <c r="E38" s="24"/>
-      <c r="G38" s="8"/>
+      <c r="B38" s="8">
+        <v>7</v>
+      </c>
+      <c r="C38" s="6" t="s">
+        <v>61</v>
+      </c>
+      <c r="D38" s="6" t="s">
+        <v>108</v>
+      </c>
+      <c r="E38" s="24">
+        <v>86</v>
+      </c>
+      <c r="G38" s="8">
+        <v>7</v>
+      </c>
       <c r="H38" s="6"/>
       <c r="I38" s="6"/>
       <c r="J38" s="21"/>
-      <c r="L38" s="8"/>
+      <c r="L38" s="8">
+        <v>7</v>
+      </c>
       <c r="M38" s="6"/>
       <c r="N38" s="11"/>
       <c r="O38" s="21"/>
     </row>
     <row r="39" spans="2:16" ht="21.2" customHeight="1">
-      <c r="B39" s="8"/>
-      <c r="C39" s="6"/>
-      <c r="D39" s="6"/>
-      <c r="E39" s="24"/>
-      <c r="G39" s="8"/>
+      <c r="B39" s="8">
+        <v>8</v>
+      </c>
+      <c r="C39" s="6" t="s">
+        <v>59</v>
+      </c>
+      <c r="D39" s="6" t="s">
+        <v>109</v>
+      </c>
+      <c r="E39" s="24">
+        <v>97</v>
+      </c>
+      <c r="G39" s="8">
+        <v>8</v>
+      </c>
       <c r="H39" s="6"/>
       <c r="I39" s="6"/>
       <c r="J39" s="21"/>
-      <c r="L39" s="8"/>
+      <c r="L39" s="8">
+        <v>8</v>
+      </c>
       <c r="M39" s="6"/>
       <c r="N39" s="11"/>
       <c r="O39" s="21"/>
     </row>
     <row r="40" spans="2:16" ht="21.2" customHeight="1">
-      <c r="B40" s="8"/>
-      <c r="C40" s="6"/>
-      <c r="D40" s="6"/>
-      <c r="E40" s="24"/>
-      <c r="G40" s="8"/>
+      <c r="B40" s="8">
+        <v>9</v>
+      </c>
+      <c r="C40" s="6" t="s">
+        <v>57</v>
+      </c>
+      <c r="D40" s="6" t="s">
+        <v>110</v>
+      </c>
+      <c r="E40" s="24">
+        <v>96</v>
+      </c>
+      <c r="G40" s="8">
+        <v>9</v>
+      </c>
       <c r="H40" s="6"/>
       <c r="I40" s="6"/>
       <c r="J40" s="21"/>
-      <c r="L40" s="8"/>
+      <c r="L40" s="8">
+        <v>9</v>
+      </c>
       <c r="M40" s="6"/>
       <c r="N40" s="11"/>
       <c r="O40" s="21"/>
     </row>
     <row r="41" spans="2:16" ht="21.2" customHeight="1">
-      <c r="B41" s="8"/>
-      <c r="C41" s="6"/>
-      <c r="D41" s="6"/>
-      <c r="E41" s="24"/>
-      <c r="G41" s="8"/>
+      <c r="B41" s="8">
+        <v>10</v>
+      </c>
+      <c r="C41" s="6" t="s">
+        <v>71</v>
+      </c>
+      <c r="D41" s="6" t="s">
+        <v>111</v>
+      </c>
+      <c r="E41" s="24">
+        <v>40</v>
+      </c>
+      <c r="G41" s="8">
+        <v>10</v>
+      </c>
       <c r="H41" s="6"/>
       <c r="I41" s="6"/>
       <c r="J41" s="21"/>
-      <c r="L41" s="8"/>
+      <c r="L41" s="8">
+        <v>10</v>
+      </c>
       <c r="M41" s="6"/>
       <c r="N41" s="11"/>
       <c r="O41" s="21"/>
     </row>
     <row r="42" spans="2:16" ht="21.2" customHeight="1">
-      <c r="B42" s="8"/>
+      <c r="B42" s="8">
+        <v>11</v>
+      </c>
       <c r="C42" s="6"/>
       <c r="D42" s="6"/>
       <c r="E42" s="21"/>
-      <c r="G42" s="8"/>
+      <c r="G42" s="8">
+        <v>11</v>
+      </c>
       <c r="H42" s="6"/>
       <c r="I42" s="6"/>
       <c r="J42" s="21"/>
-      <c r="L42" s="8"/>
+      <c r="L42" s="8">
+        <v>11</v>
+      </c>
       <c r="M42" s="6"/>
       <c r="N42" s="11"/>
       <c r="O42" s="21"/>
     </row>
     <row r="43" spans="2:16" ht="21.2" customHeight="1">
-      <c r="B43" s="8"/>
+      <c r="B43" s="8">
+        <v>12</v>
+      </c>
       <c r="C43" s="6"/>
       <c r="D43" s="6"/>
       <c r="E43" s="21"/>
-      <c r="G43" s="8"/>
+      <c r="G43" s="8">
+        <v>12</v>
+      </c>
       <c r="H43" s="6"/>
       <c r="I43" s="6"/>
       <c r="J43" s="21"/>
-      <c r="L43" s="8"/>
+      <c r="L43" s="8">
+        <v>12</v>
+      </c>
       <c r="M43" s="6"/>
       <c r="N43" s="11"/>
       <c r="O43" s="21"/>
     </row>
     <row r="44" spans="2:16" ht="21.2" customHeight="1">
-      <c r="B44" s="8"/>
+      <c r="B44" s="8">
+        <v>13</v>
+      </c>
       <c r="C44" s="6"/>
       <c r="D44" s="6"/>
       <c r="E44" s="21"/>
-      <c r="G44" s="8"/>
+      <c r="G44" s="8">
+        <v>13</v>
+      </c>
       <c r="H44" s="6"/>
       <c r="I44" s="6"/>
       <c r="J44" s="21"/>
-      <c r="L44" s="8"/>
+      <c r="L44" s="8">
+        <v>13</v>
+      </c>
       <c r="M44" s="6"/>
       <c r="N44" s="11"/>
       <c r="O44" s="21"/>
     </row>
     <row r="45" spans="2:16" ht="21.2" customHeight="1">
-      <c r="B45" s="8"/>
+      <c r="B45" s="8">
+        <v>14</v>
+      </c>
       <c r="C45" s="6"/>
       <c r="D45" s="6"/>
       <c r="E45" s="21"/>
-      <c r="G45" s="8"/>
+      <c r="G45" s="8">
+        <v>14</v>
+      </c>
       <c r="H45" s="6"/>
       <c r="I45" s="6"/>
       <c r="J45" s="21"/>
-      <c r="L45" s="8"/>
+      <c r="L45" s="8">
+        <v>14</v>
+      </c>
       <c r="M45" s="6"/>
       <c r="N45" s="11"/>
       <c r="O45" s="21"/>
     </row>
     <row r="46" spans="2:16" ht="21.2" customHeight="1" thickBot="1">
-      <c r="B46" s="9"/>
+      <c r="B46" s="9">
+        <v>15</v>
+      </c>
       <c r="C46" s="10"/>
       <c r="D46" s="10"/>
       <c r="E46" s="22"/>
-      <c r="G46" s="9"/>
+      <c r="G46" s="9">
+        <v>15</v>
+      </c>
       <c r="H46" s="10"/>
       <c r="I46" s="10"/>
       <c r="J46" s="22"/>
-      <c r="L46" s="9"/>
+      <c r="L46" s="9">
+        <v>15</v>
+      </c>
       <c r="M46" s="10"/>
       <c r="N46" s="12"/>
       <c r="O46" s="22"/>
@@ -3534,7 +4238,9 @@
         <v>0</v>
       </c>
       <c r="C3" s="39"/>
-      <c r="D3" s="34"/>
+      <c r="D3" s="34" t="s">
+        <v>1</v>
+      </c>
       <c r="E3" s="40"/>
       <c r="F3" s="40"/>
       <c r="G3" s="40"/>
@@ -3542,7 +4248,9 @@
       <c r="I3" s="23" t="s">
         <v>2</v>
       </c>
-      <c r="J3" s="34"/>
+      <c r="J3" s="34" t="s">
+        <v>3</v>
+      </c>
       <c r="K3" s="40"/>
       <c r="L3" s="40"/>
       <c r="M3" s="40"/>
@@ -3550,7 +4258,9 @@
       <c r="O3" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="P3" s="2"/>
+      <c r="P3" s="2" t="s">
+        <v>112</v>
+      </c>
     </row>
     <row r="4" spans="2:16" ht="15" customHeight="1" thickBot="1">
       <c r="B4" s="5"/>
@@ -3632,10 +4342,16 @@
       <c r="P6" s="44"/>
     </row>
     <row r="7" spans="2:16" ht="21.2" customHeight="1">
-      <c r="B7" s="8"/>
+      <c r="B7" s="8">
+        <v>1</v>
+      </c>
       <c r="C7" s="6"/>
-      <c r="D7" s="6"/>
-      <c r="E7" s="6"/>
+      <c r="D7" s="6" t="s">
+        <v>113</v>
+      </c>
+      <c r="E7" s="6" t="s">
+        <v>114</v>
+      </c>
       <c r="F7" s="6"/>
       <c r="G7" s="6"/>
       <c r="H7" s="6"/>
@@ -3649,44 +4365,90 @@
       <c r="P7" s="46"/>
     </row>
     <row r="8" spans="2:16" ht="21.2" customHeight="1">
-      <c r="B8" s="8"/>
-      <c r="C8" s="6"/>
-      <c r="D8" s="6"/>
-      <c r="E8" s="6"/>
-      <c r="F8" s="6"/>
-      <c r="G8" s="6"/>
-      <c r="H8" s="6"/>
-      <c r="I8" s="6"/>
+      <c r="B8" s="8">
+        <v>2</v>
+      </c>
+      <c r="C8" s="6" t="s">
+        <v>59</v>
+      </c>
+      <c r="D8" s="6" t="s">
+        <v>115</v>
+      </c>
+      <c r="E8" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="F8" s="6" t="s">
+        <v>84</v>
+      </c>
+      <c r="G8" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="H8" s="6" t="s">
+        <v>100</v>
+      </c>
+      <c r="I8" s="6">
+        <v>3</v>
+      </c>
       <c r="J8" s="6"/>
       <c r="K8" s="6"/>
       <c r="L8" s="6"/>
       <c r="M8" s="6"/>
-      <c r="N8" s="30"/>
+      <c r="N8" s="30" t="s">
+        <v>116</v>
+      </c>
       <c r="O8" s="45"/>
       <c r="P8" s="46"/>
     </row>
     <row r="9" spans="2:16" ht="21.2" customHeight="1">
-      <c r="B9" s="8"/>
-      <c r="C9" s="6"/>
-      <c r="D9" s="6"/>
-      <c r="E9" s="6"/>
-      <c r="F9" s="6"/>
-      <c r="G9" s="6"/>
-      <c r="H9" s="6"/>
-      <c r="I9" s="6"/>
-      <c r="J9" s="6"/>
-      <c r="K9" s="6"/>
+      <c r="B9" s="8">
+        <v>3</v>
+      </c>
+      <c r="C9" s="6" t="s">
+        <v>78</v>
+      </c>
+      <c r="D9" s="6" t="s">
+        <v>117</v>
+      </c>
+      <c r="E9" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="F9" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="G9" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="H9" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="I9" s="6">
+        <v>10</v>
+      </c>
+      <c r="J9" s="6">
+        <v>8</v>
+      </c>
+      <c r="K9" s="6">
+        <v>19</v>
+      </c>
       <c r="L9" s="6"/>
       <c r="M9" s="6"/>
-      <c r="N9" s="30"/>
+      <c r="N9" s="30" t="s">
+        <v>118</v>
+      </c>
       <c r="O9" s="45"/>
       <c r="P9" s="46"/>
     </row>
     <row r="10" spans="2:16" ht="21.2" customHeight="1">
-      <c r="B10" s="8"/>
+      <c r="B10" s="8">
+        <v>4</v>
+      </c>
       <c r="C10" s="6"/>
-      <c r="D10" s="6"/>
-      <c r="E10" s="6"/>
+      <c r="D10" s="6" t="s">
+        <v>119</v>
+      </c>
+      <c r="E10" s="6" t="s">
+        <v>120</v>
+      </c>
       <c r="F10" s="6"/>
       <c r="G10" s="6"/>
       <c r="H10" s="6"/>
@@ -3700,10 +4462,16 @@
       <c r="P10" s="46"/>
     </row>
     <row r="11" spans="2:16" ht="21.2" customHeight="1">
-      <c r="B11" s="8"/>
+      <c r="B11" s="8">
+        <v>5</v>
+      </c>
       <c r="C11" s="6"/>
-      <c r="D11" s="6"/>
-      <c r="E11" s="6"/>
+      <c r="D11" s="6" t="s">
+        <v>121</v>
+      </c>
+      <c r="E11" s="6" t="s">
+        <v>122</v>
+      </c>
       <c r="F11" s="6"/>
       <c r="G11" s="6"/>
       <c r="H11" s="6"/>
@@ -3717,61 +4485,129 @@
       <c r="P11" s="46"/>
     </row>
     <row r="12" spans="2:16" ht="21.2" customHeight="1">
-      <c r="B12" s="8"/>
-      <c r="C12" s="6"/>
-      <c r="D12" s="6"/>
-      <c r="E12" s="6"/>
-      <c r="F12" s="6"/>
-      <c r="G12" s="6"/>
-      <c r="H12" s="6"/>
-      <c r="I12" s="6"/>
+      <c r="B12" s="8">
+        <v>6</v>
+      </c>
+      <c r="C12" s="6" t="s">
+        <v>55</v>
+      </c>
+      <c r="D12" s="6" t="s">
+        <v>123</v>
+      </c>
+      <c r="E12" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="F12" s="6" t="s">
+        <v>84</v>
+      </c>
+      <c r="G12" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="H12" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="I12" s="6">
+        <v>3</v>
+      </c>
       <c r="J12" s="6"/>
-      <c r="K12" s="6"/>
+      <c r="K12" s="6">
+        <v>31</v>
+      </c>
       <c r="L12" s="6"/>
       <c r="M12" s="6"/>
-      <c r="N12" s="30"/>
+      <c r="N12" s="30" t="s">
+        <v>124</v>
+      </c>
       <c r="O12" s="45"/>
       <c r="P12" s="46"/>
     </row>
     <row r="13" spans="2:16" ht="21.2" customHeight="1">
-      <c r="B13" s="8"/>
-      <c r="C13" s="6"/>
-      <c r="D13" s="6"/>
-      <c r="E13" s="6"/>
-      <c r="F13" s="6"/>
-      <c r="G13" s="6"/>
-      <c r="H13" s="6"/>
-      <c r="I13" s="6"/>
+      <c r="B13" s="8">
+        <v>7</v>
+      </c>
+      <c r="C13" s="6" t="s">
+        <v>87</v>
+      </c>
+      <c r="D13" s="6" t="s">
+        <v>125</v>
+      </c>
+      <c r="E13" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="F13" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="G13" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="H13" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="I13" s="6">
+        <v>8</v>
+      </c>
       <c r="J13" s="6"/>
-      <c r="K13" s="6"/>
+      <c r="K13" s="6">
+        <v>32</v>
+      </c>
       <c r="L13" s="6"/>
       <c r="M13" s="6"/>
-      <c r="N13" s="30"/>
+      <c r="N13" s="30" t="s">
+        <v>126</v>
+      </c>
       <c r="O13" s="45"/>
       <c r="P13" s="46"/>
     </row>
     <row r="14" spans="2:16" ht="21.2" customHeight="1">
-      <c r="B14" s="8"/>
-      <c r="C14" s="6"/>
-      <c r="D14" s="6"/>
-      <c r="E14" s="6"/>
-      <c r="F14" s="6"/>
-      <c r="G14" s="6"/>
-      <c r="H14" s="6"/>
-      <c r="I14" s="6"/>
-      <c r="J14" s="6"/>
-      <c r="K14" s="6"/>
+      <c r="B14" s="8">
+        <v>8</v>
+      </c>
+      <c r="C14" s="6" t="s">
+        <v>127</v>
+      </c>
+      <c r="D14" s="6" t="s">
+        <v>128</v>
+      </c>
+      <c r="E14" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="F14" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="G14" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="H14" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="I14" s="6">
+        <v>5</v>
+      </c>
+      <c r="J14" s="6">
+        <v>5</v>
+      </c>
+      <c r="K14" s="6">
+        <v>42</v>
+      </c>
       <c r="L14" s="6"/>
       <c r="M14" s="6"/>
-      <c r="N14" s="30"/>
+      <c r="N14" s="30" t="s">
+        <v>129</v>
+      </c>
       <c r="O14" s="45"/>
       <c r="P14" s="46"/>
     </row>
     <row r="15" spans="2:16" ht="21.2" customHeight="1">
-      <c r="B15" s="8"/>
+      <c r="B15" s="8">
+        <v>9</v>
+      </c>
       <c r="C15" s="6"/>
-      <c r="D15" s="6"/>
-      <c r="E15" s="6"/>
+      <c r="D15" s="6" t="s">
+        <v>130</v>
+      </c>
+      <c r="E15" s="6" t="s">
+        <v>131</v>
+      </c>
       <c r="F15" s="6"/>
       <c r="G15" s="6"/>
       <c r="H15" s="6"/>
@@ -3785,10 +4621,16 @@
       <c r="P15" s="46"/>
     </row>
     <row r="16" spans="2:16" ht="21.2" customHeight="1">
-      <c r="B16" s="8"/>
+      <c r="B16" s="8">
+        <v>10</v>
+      </c>
       <c r="C16" s="6"/>
-      <c r="D16" s="6"/>
-      <c r="E16" s="6"/>
+      <c r="D16" s="6" t="s">
+        <v>132</v>
+      </c>
+      <c r="E16" s="6" t="s">
+        <v>133</v>
+      </c>
       <c r="F16" s="6"/>
       <c r="G16" s="6"/>
       <c r="H16" s="6"/>
@@ -3802,10 +4644,16 @@
       <c r="P16" s="46"/>
     </row>
     <row r="17" spans="2:16" ht="21.2" customHeight="1">
-      <c r="B17" s="8"/>
+      <c r="B17" s="8">
+        <v>11</v>
+      </c>
       <c r="C17" s="6"/>
-      <c r="D17" s="6"/>
-      <c r="E17" s="6"/>
+      <c r="D17" s="6" t="s">
+        <v>134</v>
+      </c>
+      <c r="E17" s="6" t="s">
+        <v>135</v>
+      </c>
       <c r="F17" s="6"/>
       <c r="G17" s="6"/>
       <c r="H17" s="6"/>
@@ -3819,16 +4667,34 @@
       <c r="P17" s="46"/>
     </row>
     <row r="18" spans="2:16" ht="21.2" customHeight="1">
-      <c r="B18" s="8"/>
-      <c r="C18" s="6"/>
-      <c r="D18" s="6"/>
-      <c r="E18" s="6"/>
-      <c r="F18" s="6"/>
-      <c r="G18" s="6"/>
-      <c r="H18" s="6"/>
-      <c r="I18" s="6"/>
+      <c r="B18" s="8">
+        <v>12</v>
+      </c>
+      <c r="C18" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="D18" s="6" t="s">
+        <v>136</v>
+      </c>
+      <c r="E18" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="F18" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="G18" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="H18" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="I18" s="6">
+        <v>7</v>
+      </c>
       <c r="J18" s="6"/>
-      <c r="K18" s="6"/>
+      <c r="K18" s="6">
+        <v>25</v>
+      </c>
       <c r="L18" s="6"/>
       <c r="M18" s="6"/>
       <c r="N18" s="30"/>
@@ -3836,32 +4702,68 @@
       <c r="P18" s="46"/>
     </row>
     <row r="19" spans="2:16" ht="21.2" customHeight="1">
-      <c r="B19" s="8"/>
-      <c r="C19" s="6"/>
-      <c r="D19" s="6"/>
-      <c r="E19" s="6"/>
-      <c r="F19" s="6"/>
-      <c r="G19" s="6"/>
-      <c r="H19" s="6"/>
-      <c r="I19" s="6"/>
+      <c r="B19" s="8">
+        <v>13</v>
+      </c>
+      <c r="C19" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="D19" s="6" t="s">
+        <v>137</v>
+      </c>
+      <c r="E19" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="F19" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="G19" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="H19" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="I19" s="6">
+        <v>6</v>
+      </c>
       <c r="J19" s="6"/>
       <c r="K19" s="6"/>
       <c r="L19" s="6"/>
       <c r="M19" s="6"/>
-      <c r="N19" s="30"/>
+      <c r="N19" s="30" t="s">
+        <v>138</v>
+      </c>
       <c r="O19" s="45"/>
       <c r="P19" s="46"/>
     </row>
     <row r="20" spans="2:16" ht="21.2" customHeight="1">
-      <c r="B20" s="8"/>
-      <c r="C20" s="6"/>
-      <c r="D20" s="6"/>
-      <c r="E20" s="6"/>
-      <c r="F20" s="6"/>
-      <c r="G20" s="6"/>
-      <c r="H20" s="6"/>
-      <c r="I20" s="6"/>
-      <c r="J20" s="6"/>
+      <c r="B20" s="8">
+        <v>14</v>
+      </c>
+      <c r="C20" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="D20" s="6" t="s">
+        <v>139</v>
+      </c>
+      <c r="E20" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="F20" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="G20" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="H20" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="I20" s="6">
+        <v>8</v>
+      </c>
+      <c r="J20" s="6">
+        <v>5</v>
+      </c>
       <c r="K20" s="6"/>
       <c r="L20" s="6"/>
       <c r="M20" s="6"/>
@@ -3870,15 +4772,33 @@
       <c r="P20" s="46"/>
     </row>
     <row r="21" spans="2:16" ht="21.2" customHeight="1">
-      <c r="B21" s="8"/>
-      <c r="C21" s="6"/>
-      <c r="D21" s="6"/>
-      <c r="E21" s="6"/>
-      <c r="F21" s="6"/>
-      <c r="G21" s="6"/>
-      <c r="H21" s="6"/>
-      <c r="I21" s="6"/>
-      <c r="J21" s="6"/>
+      <c r="B21" s="8">
+        <v>15</v>
+      </c>
+      <c r="C21" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="D21" s="6" t="s">
+        <v>140</v>
+      </c>
+      <c r="E21" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="F21" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="G21" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="H21" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="I21" s="6">
+        <v>6</v>
+      </c>
+      <c r="J21" s="6">
+        <v>4</v>
+      </c>
       <c r="K21" s="6"/>
       <c r="L21" s="6"/>
       <c r="M21" s="6"/>
@@ -3887,10 +4807,16 @@
       <c r="P21" s="46"/>
     </row>
     <row r="22" spans="2:16" ht="21.2" customHeight="1">
-      <c r="B22" s="8"/>
+      <c r="B22" s="8">
+        <v>16</v>
+      </c>
       <c r="C22" s="6"/>
-      <c r="D22" s="6"/>
-      <c r="E22" s="6"/>
+      <c r="D22" s="6" t="s">
+        <v>141</v>
+      </c>
+      <c r="E22" s="6" t="s">
+        <v>142</v>
+      </c>
       <c r="F22" s="6"/>
       <c r="G22" s="6"/>
       <c r="H22" s="6"/>
@@ -3904,27 +4830,55 @@
       <c r="P22" s="46"/>
     </row>
     <row r="23" spans="2:16" ht="21.2" customHeight="1">
-      <c r="B23" s="8"/>
-      <c r="C23" s="6"/>
-      <c r="D23" s="6"/>
-      <c r="E23" s="6"/>
-      <c r="F23" s="6"/>
-      <c r="G23" s="6"/>
-      <c r="H23" s="6"/>
-      <c r="I23" s="6"/>
-      <c r="J23" s="6"/>
-      <c r="K23" s="6"/>
+      <c r="B23" s="8">
+        <v>17</v>
+      </c>
+      <c r="C23" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="D23" s="6" t="s">
+        <v>143</v>
+      </c>
+      <c r="E23" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="F23" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="G23" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="H23" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="I23" s="6">
+        <v>9</v>
+      </c>
+      <c r="J23" s="6">
+        <v>7</v>
+      </c>
+      <c r="K23" s="6">
+        <v>20</v>
+      </c>
       <c r="L23" s="6"/>
       <c r="M23" s="6"/>
-      <c r="N23" s="30"/>
+      <c r="N23" s="30" t="s">
+        <v>144</v>
+      </c>
       <c r="O23" s="45"/>
       <c r="P23" s="46"/>
     </row>
     <row r="24" spans="2:16" ht="21.2" customHeight="1">
-      <c r="B24" s="8"/>
+      <c r="B24" s="8">
+        <v>18</v>
+      </c>
       <c r="C24" s="6"/>
-      <c r="D24" s="6"/>
-      <c r="E24" s="6"/>
+      <c r="D24" s="6" t="s">
+        <v>145</v>
+      </c>
+      <c r="E24" s="6" t="s">
+        <v>146</v>
+      </c>
       <c r="F24" s="6"/>
       <c r="G24" s="6"/>
       <c r="H24" s="6"/>
@@ -3938,10 +4892,16 @@
       <c r="P24" s="46"/>
     </row>
     <row r="25" spans="2:16" ht="21.2" customHeight="1">
-      <c r="B25" s="8"/>
+      <c r="B25" s="8">
+        <v>19</v>
+      </c>
       <c r="C25" s="6"/>
-      <c r="D25" s="6"/>
-      <c r="E25" s="6"/>
+      <c r="D25" s="6" t="s">
+        <v>147</v>
+      </c>
+      <c r="E25" s="6" t="s">
+        <v>148</v>
+      </c>
       <c r="F25" s="6"/>
       <c r="G25" s="6"/>
       <c r="H25" s="6"/>
@@ -3955,7 +4915,9 @@
       <c r="P25" s="46"/>
     </row>
     <row r="26" spans="2:16" ht="21.2" customHeight="1">
-      <c r="B26" s="8"/>
+      <c r="B26" s="8">
+        <v>20</v>
+      </c>
       <c r="C26" s="6"/>
       <c r="D26" s="6"/>
       <c r="E26" s="6"/>
@@ -3972,7 +4934,9 @@
       <c r="P26" s="46"/>
     </row>
     <row r="27" spans="2:16" ht="21.2" customHeight="1" thickBot="1">
-      <c r="B27" s="9"/>
+      <c r="B27" s="9">
+        <v>21</v>
+      </c>
       <c r="C27" s="10"/>
       <c r="D27" s="10"/>
       <c r="E27" s="10"/>
@@ -4088,211 +5052,379 @@
       </c>
     </row>
     <row r="32" spans="2:16" ht="21.2" customHeight="1">
-      <c r="B32" s="8"/>
-      <c r="C32" s="6"/>
-      <c r="D32" s="6"/>
-      <c r="E32" s="24"/>
-      <c r="G32" s="8"/>
-      <c r="H32" s="6"/>
-      <c r="I32" s="6"/>
-      <c r="J32" s="24"/>
-      <c r="L32" s="8"/>
+      <c r="B32" s="8">
+        <v>1</v>
+      </c>
+      <c r="C32" s="6" t="s">
+        <v>69</v>
+      </c>
+      <c r="D32" s="6" t="s">
+        <v>149</v>
+      </c>
+      <c r="E32" s="24">
+        <v>103</v>
+      </c>
+      <c r="G32" s="8">
+        <v>1</v>
+      </c>
+      <c r="H32" s="6" t="s">
+        <v>59</v>
+      </c>
+      <c r="I32" s="6" t="s">
+        <v>115</v>
+      </c>
+      <c r="J32" s="24">
+        <v>100</v>
+      </c>
+      <c r="L32" s="8">
+        <v>1</v>
+      </c>
       <c r="M32" s="6"/>
       <c r="N32" s="11"/>
       <c r="O32" s="21"/>
     </row>
     <row r="33" spans="2:16" ht="21.2" customHeight="1">
-      <c r="B33" s="8"/>
-      <c r="C33" s="6"/>
-      <c r="D33" s="6"/>
-      <c r="E33" s="24"/>
-      <c r="G33" s="8"/>
-      <c r="H33" s="6"/>
-      <c r="I33" s="6"/>
-      <c r="J33" s="24"/>
-      <c r="L33" s="8"/>
+      <c r="B33" s="8">
+        <v>2</v>
+      </c>
+      <c r="C33" s="6" t="s">
+        <v>67</v>
+      </c>
+      <c r="D33" s="6" t="s">
+        <v>150</v>
+      </c>
+      <c r="E33" s="24">
+        <v>56</v>
+      </c>
+      <c r="G33" s="8">
+        <v>2</v>
+      </c>
+      <c r="H33" s="6" t="s">
+        <v>55</v>
+      </c>
+      <c r="I33" s="6" t="s">
+        <v>123</v>
+      </c>
+      <c r="J33" s="24">
+        <v>38</v>
+      </c>
+      <c r="L33" s="8">
+        <v>2</v>
+      </c>
       <c r="M33" s="6"/>
       <c r="N33" s="11"/>
       <c r="O33" s="21"/>
     </row>
     <row r="34" spans="2:16" ht="21.2" customHeight="1">
-      <c r="B34" s="8"/>
-      <c r="C34" s="6"/>
-      <c r="D34" s="6"/>
-      <c r="E34" s="24"/>
-      <c r="G34" s="8"/>
+      <c r="B34" s="8">
+        <v>3</v>
+      </c>
+      <c r="C34" s="6" t="s">
+        <v>104</v>
+      </c>
+      <c r="D34" s="6" t="s">
+        <v>151</v>
+      </c>
+      <c r="E34" s="24">
+        <v>61</v>
+      </c>
+      <c r="G34" s="8">
+        <v>3</v>
+      </c>
       <c r="H34" s="6"/>
       <c r="I34" s="6"/>
       <c r="J34" s="21"/>
-      <c r="L34" s="8"/>
+      <c r="L34" s="8">
+        <v>3</v>
+      </c>
       <c r="M34" s="6"/>
       <c r="N34" s="11"/>
       <c r="O34" s="21"/>
     </row>
     <row r="35" spans="2:16" ht="21.2" customHeight="1">
-      <c r="B35" s="8"/>
-      <c r="C35" s="6"/>
-      <c r="D35" s="6"/>
-      <c r="E35" s="24"/>
-      <c r="G35" s="8"/>
+      <c r="B35" s="8">
+        <v>4</v>
+      </c>
+      <c r="C35" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="D35" s="6" t="s">
+        <v>152</v>
+      </c>
+      <c r="E35" s="24">
+        <v>32</v>
+      </c>
+      <c r="G35" s="8">
+        <v>4</v>
+      </c>
       <c r="H35" s="6"/>
       <c r="I35" s="6"/>
       <c r="J35" s="21"/>
-      <c r="L35" s="8"/>
+      <c r="L35" s="8">
+        <v>4</v>
+      </c>
       <c r="M35" s="6"/>
       <c r="N35" s="11"/>
       <c r="O35" s="21"/>
     </row>
     <row r="36" spans="2:16" ht="21.2" customHeight="1">
-      <c r="B36" s="8"/>
-      <c r="C36" s="6"/>
-      <c r="D36" s="6"/>
-      <c r="E36" s="24"/>
-      <c r="G36" s="8"/>
+      <c r="B36" s="8">
+        <v>5</v>
+      </c>
+      <c r="C36" s="6" t="s">
+        <v>65</v>
+      </c>
+      <c r="D36" s="6" t="s">
+        <v>153</v>
+      </c>
+      <c r="E36" s="24">
+        <v>87</v>
+      </c>
+      <c r="G36" s="8">
+        <v>5</v>
+      </c>
       <c r="H36" s="6"/>
       <c r="I36" s="6"/>
       <c r="J36" s="21"/>
-      <c r="L36" s="8"/>
+      <c r="L36" s="8">
+        <v>5</v>
+      </c>
       <c r="M36" s="6"/>
       <c r="N36" s="11"/>
       <c r="O36" s="21"/>
     </row>
     <row r="37" spans="2:16" ht="21.2" customHeight="1">
-      <c r="B37" s="8"/>
-      <c r="C37" s="6"/>
-      <c r="D37" s="6"/>
-      <c r="E37" s="24"/>
-      <c r="G37" s="8"/>
+      <c r="B37" s="8">
+        <v>6</v>
+      </c>
+      <c r="C37" s="6" t="s">
+        <v>154</v>
+      </c>
+      <c r="D37" s="6" t="s">
+        <v>155</v>
+      </c>
+      <c r="E37" s="24">
+        <v>10</v>
+      </c>
+      <c r="G37" s="8">
+        <v>6</v>
+      </c>
       <c r="H37" s="6"/>
       <c r="I37" s="6"/>
       <c r="J37" s="21"/>
-      <c r="L37" s="8"/>
+      <c r="L37" s="8">
+        <v>6</v>
+      </c>
       <c r="M37" s="6"/>
       <c r="N37" s="11"/>
       <c r="O37" s="21"/>
     </row>
     <row r="38" spans="2:16" ht="21.2" customHeight="1">
-      <c r="B38" s="8"/>
-      <c r="C38" s="6"/>
-      <c r="D38" s="6"/>
-      <c r="E38" s="24"/>
-      <c r="G38" s="8"/>
+      <c r="B38" s="8">
+        <v>7</v>
+      </c>
+      <c r="C38" s="6" t="s">
+        <v>61</v>
+      </c>
+      <c r="D38" s="6" t="s">
+        <v>156</v>
+      </c>
+      <c r="E38" s="24">
+        <v>50</v>
+      </c>
+      <c r="G38" s="8">
+        <v>7</v>
+      </c>
       <c r="H38" s="6"/>
       <c r="I38" s="6"/>
       <c r="J38" s="21"/>
-      <c r="L38" s="8"/>
+      <c r="L38" s="8">
+        <v>7</v>
+      </c>
       <c r="M38" s="6"/>
       <c r="N38" s="11"/>
       <c r="O38" s="21"/>
     </row>
     <row r="39" spans="2:16" ht="21.2" customHeight="1">
-      <c r="B39" s="8"/>
-      <c r="C39" s="6"/>
-      <c r="D39" s="6"/>
-      <c r="E39" s="24"/>
-      <c r="G39" s="8"/>
+      <c r="B39" s="8">
+        <v>8</v>
+      </c>
+      <c r="C39" s="6" t="s">
+        <v>59</v>
+      </c>
+      <c r="D39" s="6" t="s">
+        <v>157</v>
+      </c>
+      <c r="E39" s="24">
+        <v>38</v>
+      </c>
+      <c r="G39" s="8">
+        <v>8</v>
+      </c>
       <c r="H39" s="6"/>
       <c r="I39" s="6"/>
       <c r="J39" s="21"/>
-      <c r="L39" s="8"/>
+      <c r="L39" s="8">
+        <v>8</v>
+      </c>
       <c r="M39" s="6"/>
       <c r="N39" s="11"/>
       <c r="O39" s="21"/>
     </row>
     <row r="40" spans="2:16" ht="21.2" customHeight="1">
-      <c r="B40" s="8"/>
-      <c r="C40" s="6"/>
-      <c r="D40" s="6"/>
-      <c r="E40" s="24"/>
-      <c r="G40" s="8"/>
+      <c r="B40" s="8">
+        <v>9</v>
+      </c>
+      <c r="C40" s="6" t="s">
+        <v>55</v>
+      </c>
+      <c r="D40" s="6" t="s">
+        <v>158</v>
+      </c>
+      <c r="E40" s="24">
+        <v>75</v>
+      </c>
+      <c r="G40" s="8">
+        <v>9</v>
+      </c>
       <c r="H40" s="6"/>
       <c r="I40" s="6"/>
       <c r="J40" s="21"/>
-      <c r="L40" s="8"/>
+      <c r="L40" s="8">
+        <v>9</v>
+      </c>
       <c r="M40" s="6"/>
       <c r="N40" s="11"/>
       <c r="O40" s="21"/>
     </row>
     <row r="41" spans="2:16" ht="21.2" customHeight="1">
-      <c r="B41" s="8"/>
-      <c r="C41" s="6"/>
-      <c r="D41" s="6"/>
-      <c r="E41" s="24"/>
-      <c r="G41" s="8"/>
+      <c r="B41" s="8">
+        <v>10</v>
+      </c>
+      <c r="C41" s="6" t="s">
+        <v>57</v>
+      </c>
+      <c r="D41" s="6" t="s">
+        <v>159</v>
+      </c>
+      <c r="E41" s="24">
+        <v>126</v>
+      </c>
+      <c r="G41" s="8">
+        <v>10</v>
+      </c>
       <c r="H41" s="6"/>
       <c r="I41" s="6"/>
       <c r="J41" s="21"/>
-      <c r="L41" s="8"/>
+      <c r="L41" s="8">
+        <v>10</v>
+      </c>
       <c r="M41" s="6"/>
       <c r="N41" s="11"/>
       <c r="O41" s="21"/>
     </row>
     <row r="42" spans="2:16" ht="21.2" customHeight="1">
-      <c r="B42" s="8"/>
-      <c r="C42" s="6"/>
-      <c r="D42" s="6"/>
-      <c r="E42" s="24"/>
-      <c r="G42" s="8"/>
+      <c r="B42" s="8">
+        <v>11</v>
+      </c>
+      <c r="C42" s="6" t="s">
+        <v>160</v>
+      </c>
+      <c r="D42" s="6" t="s">
+        <v>161</v>
+      </c>
+      <c r="E42" s="24">
+        <v>63</v>
+      </c>
+      <c r="G42" s="8">
+        <v>11</v>
+      </c>
       <c r="H42" s="6"/>
       <c r="I42" s="6"/>
       <c r="J42" s="21"/>
-      <c r="L42" s="8"/>
+      <c r="L42" s="8">
+        <v>11</v>
+      </c>
       <c r="M42" s="6"/>
       <c r="N42" s="11"/>
       <c r="O42" s="21"/>
     </row>
     <row r="43" spans="2:16" ht="21.2" customHeight="1">
-      <c r="B43" s="8"/>
+      <c r="B43" s="8">
+        <v>12</v>
+      </c>
       <c r="C43" s="6"/>
       <c r="D43" s="6"/>
       <c r="E43" s="21"/>
-      <c r="G43" s="8"/>
+      <c r="G43" s="8">
+        <v>12</v>
+      </c>
       <c r="H43" s="6"/>
       <c r="I43" s="6"/>
       <c r="J43" s="21"/>
-      <c r="L43" s="8"/>
+      <c r="L43" s="8">
+        <v>12</v>
+      </c>
       <c r="M43" s="6"/>
       <c r="N43" s="11"/>
       <c r="O43" s="21"/>
     </row>
     <row r="44" spans="2:16" ht="21.2" customHeight="1">
-      <c r="B44" s="8"/>
+      <c r="B44" s="8">
+        <v>13</v>
+      </c>
       <c r="C44" s="6"/>
       <c r="D44" s="6"/>
       <c r="E44" s="21"/>
-      <c r="G44" s="8"/>
+      <c r="G44" s="8">
+        <v>13</v>
+      </c>
       <c r="H44" s="6"/>
       <c r="I44" s="6"/>
       <c r="J44" s="21"/>
-      <c r="L44" s="8"/>
+      <c r="L44" s="8">
+        <v>13</v>
+      </c>
       <c r="M44" s="6"/>
       <c r="N44" s="11"/>
       <c r="O44" s="21"/>
     </row>
     <row r="45" spans="2:16" ht="21.2" customHeight="1">
-      <c r="B45" s="8"/>
+      <c r="B45" s="8">
+        <v>14</v>
+      </c>
       <c r="C45" s="6"/>
       <c r="D45" s="6"/>
       <c r="E45" s="21"/>
-      <c r="G45" s="8"/>
+      <c r="G45" s="8">
+        <v>14</v>
+      </c>
       <c r="H45" s="6"/>
       <c r="I45" s="6"/>
       <c r="J45" s="21"/>
-      <c r="L45" s="8"/>
+      <c r="L45" s="8">
+        <v>14</v>
+      </c>
       <c r="M45" s="6"/>
       <c r="N45" s="11"/>
       <c r="O45" s="21"/>
     </row>
     <row r="46" spans="2:16" ht="21.2" customHeight="1" thickBot="1">
-      <c r="B46" s="9"/>
+      <c r="B46" s="9">
+        <v>15</v>
+      </c>
       <c r="C46" s="10"/>
       <c r="D46" s="10"/>
       <c r="E46" s="22"/>
-      <c r="G46" s="9"/>
+      <c r="G46" s="9">
+        <v>15</v>
+      </c>
       <c r="H46" s="10"/>
       <c r="I46" s="10"/>
       <c r="J46" s="22"/>
-      <c r="L46" s="9"/>
+      <c r="L46" s="9">
+        <v>15</v>
+      </c>
       <c r="M46" s="10"/>
       <c r="N46" s="12"/>
       <c r="O46" s="22"/>
@@ -4414,7 +5546,9 @@
         <v>0</v>
       </c>
       <c r="C3" s="39"/>
-      <c r="D3" s="34"/>
+      <c r="D3" s="34" t="s">
+        <v>1</v>
+      </c>
       <c r="E3" s="40"/>
       <c r="F3" s="40"/>
       <c r="G3" s="40"/>
@@ -4422,7 +5556,9 @@
       <c r="I3" s="23" t="s">
         <v>2</v>
       </c>
-      <c r="J3" s="34"/>
+      <c r="J3" s="34" t="s">
+        <v>3</v>
+      </c>
       <c r="K3" s="40"/>
       <c r="L3" s="40"/>
       <c r="M3" s="40"/>
@@ -4430,7 +5566,9 @@
       <c r="O3" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="P3" s="2"/>
+      <c r="P3" s="2" t="s">
+        <v>162</v>
+      </c>
     </row>
     <row r="4" spans="2:16" ht="15" customHeight="1" thickBot="1">
       <c r="B4" s="5"/>
@@ -4512,10 +5650,16 @@
       <c r="P6" s="44"/>
     </row>
     <row r="7" spans="2:16" ht="21.2" customHeight="1">
-      <c r="B7" s="8"/>
+      <c r="B7" s="8">
+        <v>1</v>
+      </c>
       <c r="C7" s="6"/>
-      <c r="D7" s="6"/>
-      <c r="E7" s="6"/>
+      <c r="D7" s="6" t="s">
+        <v>163</v>
+      </c>
+      <c r="E7" s="6" t="s">
+        <v>164</v>
+      </c>
       <c r="F7" s="6"/>
       <c r="G7" s="6"/>
       <c r="H7" s="6"/>
@@ -4529,31 +5673,67 @@
       <c r="P7" s="46"/>
     </row>
     <row r="8" spans="2:16" ht="21.2" customHeight="1">
-      <c r="B8" s="8"/>
-      <c r="C8" s="6"/>
-      <c r="D8" s="6"/>
-      <c r="E8" s="6"/>
-      <c r="F8" s="6"/>
-      <c r="G8" s="6"/>
-      <c r="H8" s="6"/>
-      <c r="I8" s="6"/>
+      <c r="B8" s="8">
+        <v>2</v>
+      </c>
+      <c r="C8" s="6" t="s">
+        <v>55</v>
+      </c>
+      <c r="D8" s="6" t="s">
+        <v>165</v>
+      </c>
+      <c r="E8" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="F8" s="6" t="s">
+        <v>84</v>
+      </c>
+      <c r="G8" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="H8" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="I8" s="6">
+        <v>2</v>
+      </c>
       <c r="J8" s="6"/>
-      <c r="K8" s="6"/>
+      <c r="K8" s="6">
+        <v>28</v>
+      </c>
       <c r="L8" s="6"/>
       <c r="M8" s="6"/>
-      <c r="N8" s="30"/>
+      <c r="N8" s="30" t="s">
+        <v>166</v>
+      </c>
       <c r="O8" s="45"/>
       <c r="P8" s="46"/>
     </row>
     <row r="9" spans="2:16" ht="21.2" customHeight="1">
-      <c r="B9" s="8"/>
-      <c r="C9" s="6"/>
-      <c r="D9" s="6"/>
-      <c r="E9" s="6"/>
-      <c r="F9" s="6"/>
-      <c r="G9" s="6"/>
-      <c r="H9" s="6"/>
-      <c r="I9" s="6"/>
+      <c r="B9" s="8">
+        <v>3</v>
+      </c>
+      <c r="C9" s="6" t="s">
+        <v>59</v>
+      </c>
+      <c r="D9" s="6" t="s">
+        <v>167</v>
+      </c>
+      <c r="E9" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="F9" s="6" t="s">
+        <v>84</v>
+      </c>
+      <c r="G9" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="H9" s="6" t="s">
+        <v>100</v>
+      </c>
+      <c r="I9" s="6">
+        <v>2</v>
+      </c>
       <c r="J9" s="6"/>
       <c r="K9" s="6"/>
       <c r="L9" s="6"/>
@@ -4563,16 +5743,34 @@
       <c r="P9" s="46"/>
     </row>
     <row r="10" spans="2:16" ht="21.2" customHeight="1">
-      <c r="B10" s="8"/>
-      <c r="C10" s="6"/>
-      <c r="D10" s="6"/>
-      <c r="E10" s="6"/>
-      <c r="F10" s="6"/>
-      <c r="G10" s="6"/>
-      <c r="H10" s="6"/>
-      <c r="I10" s="6"/>
+      <c r="B10" s="8">
+        <v>4</v>
+      </c>
+      <c r="C10" s="6" t="s">
+        <v>57</v>
+      </c>
+      <c r="D10" s="6" t="s">
+        <v>168</v>
+      </c>
+      <c r="E10" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="F10" s="6" t="s">
+        <v>84</v>
+      </c>
+      <c r="G10" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="H10" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="I10" s="6">
+        <v>4</v>
+      </c>
       <c r="J10" s="6"/>
-      <c r="K10" s="6"/>
+      <c r="K10" s="6">
+        <v>42</v>
+      </c>
       <c r="L10" s="6"/>
       <c r="M10" s="6"/>
       <c r="N10" s="30"/>
@@ -4580,16 +5778,34 @@
       <c r="P10" s="46"/>
     </row>
     <row r="11" spans="2:16" ht="21.2" customHeight="1">
-      <c r="B11" s="8"/>
-      <c r="C11" s="6"/>
-      <c r="D11" s="6"/>
-      <c r="E11" s="6"/>
-      <c r="F11" s="6"/>
-      <c r="G11" s="6"/>
-      <c r="H11" s="6"/>
-      <c r="I11" s="6"/>
+      <c r="B11" s="8">
+        <v>5</v>
+      </c>
+      <c r="C11" s="6" t="s">
+        <v>87</v>
+      </c>
+      <c r="D11" s="6" t="s">
+        <v>169</v>
+      </c>
+      <c r="E11" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="F11" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="G11" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="H11" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="I11" s="6">
+        <v>4</v>
+      </c>
       <c r="J11" s="6"/>
-      <c r="K11" s="6"/>
+      <c r="K11" s="6">
+        <v>31</v>
+      </c>
       <c r="L11" s="6"/>
       <c r="M11" s="6"/>
       <c r="N11" s="30"/>
@@ -4597,33 +5813,73 @@
       <c r="P11" s="46"/>
     </row>
     <row r="12" spans="2:16" ht="21.2" customHeight="1">
-      <c r="B12" s="8"/>
-      <c r="C12" s="6"/>
-      <c r="D12" s="6"/>
-      <c r="E12" s="6"/>
-      <c r="F12" s="6"/>
-      <c r="G12" s="6"/>
-      <c r="H12" s="6"/>
-      <c r="I12" s="6"/>
-      <c r="J12" s="6"/>
-      <c r="K12" s="6"/>
+      <c r="B12" s="8">
+        <v>6</v>
+      </c>
+      <c r="C12" s="6" t="s">
+        <v>127</v>
+      </c>
+      <c r="D12" s="6" t="s">
+        <v>170</v>
+      </c>
+      <c r="E12" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="F12" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="G12" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="H12" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="I12" s="6">
+        <v>20</v>
+      </c>
+      <c r="J12" s="6">
+        <v>14</v>
+      </c>
+      <c r="K12" s="6">
+        <v>46</v>
+      </c>
       <c r="L12" s="6"/>
       <c r="M12" s="6"/>
-      <c r="N12" s="30"/>
+      <c r="N12" s="30" t="s">
+        <v>126</v>
+      </c>
       <c r="O12" s="45"/>
       <c r="P12" s="46"/>
     </row>
     <row r="13" spans="2:16" ht="21.2" customHeight="1">
-      <c r="B13" s="8"/>
-      <c r="C13" s="6"/>
-      <c r="D13" s="6"/>
-      <c r="E13" s="6"/>
-      <c r="F13" s="6"/>
-      <c r="G13" s="6"/>
-      <c r="H13" s="6"/>
-      <c r="I13" s="6"/>
+      <c r="B13" s="8">
+        <v>7</v>
+      </c>
+      <c r="C13" s="6" t="s">
+        <v>76</v>
+      </c>
+      <c r="D13" s="6" t="s">
+        <v>171</v>
+      </c>
+      <c r="E13" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="F13" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="G13" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="H13" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="I13" s="6">
+        <v>9</v>
+      </c>
       <c r="J13" s="6"/>
-      <c r="K13" s="6"/>
+      <c r="K13" s="6">
+        <v>38</v>
+      </c>
       <c r="L13" s="6"/>
       <c r="M13" s="6"/>
       <c r="N13" s="30"/>
@@ -4631,27 +5887,55 @@
       <c r="P13" s="46"/>
     </row>
     <row r="14" spans="2:16" ht="21.2" customHeight="1">
-      <c r="B14" s="8"/>
-      <c r="C14" s="6"/>
-      <c r="D14" s="6"/>
-      <c r="E14" s="6"/>
-      <c r="F14" s="6"/>
-      <c r="G14" s="6"/>
-      <c r="H14" s="6"/>
-      <c r="I14" s="6"/>
-      <c r="J14" s="6"/>
-      <c r="K14" s="6"/>
+      <c r="B14" s="8">
+        <v>8</v>
+      </c>
+      <c r="C14" s="6" t="s">
+        <v>78</v>
+      </c>
+      <c r="D14" s="6" t="s">
+        <v>172</v>
+      </c>
+      <c r="E14" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="F14" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="G14" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="H14" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="I14" s="6">
+        <v>9</v>
+      </c>
+      <c r="J14" s="6">
+        <v>7</v>
+      </c>
+      <c r="K14" s="6">
+        <v>19</v>
+      </c>
       <c r="L14" s="6"/>
       <c r="M14" s="6"/>
-      <c r="N14" s="30"/>
+      <c r="N14" s="30" t="s">
+        <v>173</v>
+      </c>
       <c r="O14" s="45"/>
       <c r="P14" s="46"/>
     </row>
     <row r="15" spans="2:16" ht="21.2" customHeight="1">
-      <c r="B15" s="8"/>
+      <c r="B15" s="8">
+        <v>9</v>
+      </c>
       <c r="C15" s="6"/>
-      <c r="D15" s="6"/>
-      <c r="E15" s="6"/>
+      <c r="D15" s="6" t="s">
+        <v>174</v>
+      </c>
+      <c r="E15" s="6" t="s">
+        <v>175</v>
+      </c>
       <c r="F15" s="6"/>
       <c r="G15" s="6"/>
       <c r="H15" s="6"/>
@@ -4665,50 +5949,108 @@
       <c r="P15" s="46"/>
     </row>
     <row r="16" spans="2:16" ht="21.2" customHeight="1">
-      <c r="B16" s="8"/>
-      <c r="C16" s="6"/>
-      <c r="D16" s="6"/>
-      <c r="E16" s="6"/>
-      <c r="F16" s="6"/>
-      <c r="G16" s="6"/>
-      <c r="H16" s="6"/>
-      <c r="I16" s="6"/>
+      <c r="B16" s="8">
+        <v>10</v>
+      </c>
+      <c r="C16" s="6" t="s">
+        <v>160</v>
+      </c>
+      <c r="D16" s="6" t="s">
+        <v>176</v>
+      </c>
+      <c r="E16" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="F16" s="6" t="s">
+        <v>84</v>
+      </c>
+      <c r="G16" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="H16" s="6" t="s">
+        <v>177</v>
+      </c>
+      <c r="I16" s="6">
+        <v>1</v>
+      </c>
       <c r="J16" s="6"/>
       <c r="K16" s="6"/>
       <c r="L16" s="6"/>
       <c r="M16" s="6"/>
-      <c r="N16" s="30"/>
+      <c r="N16" s="30" t="s">
+        <v>178</v>
+      </c>
       <c r="O16" s="45"/>
       <c r="P16" s="46"/>
     </row>
     <row r="17" spans="2:16" ht="21.2" customHeight="1">
-      <c r="B17" s="8"/>
-      <c r="C17" s="6"/>
-      <c r="D17" s="6"/>
-      <c r="E17" s="6"/>
-      <c r="F17" s="6"/>
-      <c r="G17" s="6"/>
-      <c r="H17" s="6"/>
-      <c r="I17" s="6"/>
-      <c r="J17" s="6"/>
-      <c r="K17" s="6"/>
+      <c r="B17" s="8">
+        <v>11</v>
+      </c>
+      <c r="C17" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="D17" s="6" t="s">
+        <v>179</v>
+      </c>
+      <c r="E17" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="F17" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="G17" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="H17" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="I17" s="6">
+        <v>8</v>
+      </c>
+      <c r="J17" s="6">
+        <v>8</v>
+      </c>
+      <c r="K17" s="6">
+        <v>44</v>
+      </c>
       <c r="L17" s="6"/>
       <c r="M17" s="6"/>
-      <c r="N17" s="30"/>
+      <c r="N17" s="30" t="s">
+        <v>180</v>
+      </c>
       <c r="O17" s="45"/>
       <c r="P17" s="46"/>
     </row>
     <row r="18" spans="2:16" ht="21.2" customHeight="1">
-      <c r="B18" s="8"/>
-      <c r="C18" s="6"/>
-      <c r="D18" s="6"/>
-      <c r="E18" s="6"/>
-      <c r="F18" s="6"/>
-      <c r="G18" s="6"/>
-      <c r="H18" s="6"/>
-      <c r="I18" s="6"/>
+      <c r="B18" s="8">
+        <v>12</v>
+      </c>
+      <c r="C18" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="D18" s="6" t="s">
+        <v>181</v>
+      </c>
+      <c r="E18" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="F18" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="G18" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="H18" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="I18" s="6">
+        <v>9</v>
+      </c>
       <c r="J18" s="6"/>
-      <c r="K18" s="6"/>
+      <c r="K18" s="6">
+        <v>28</v>
+      </c>
       <c r="L18" s="6"/>
       <c r="M18" s="6"/>
       <c r="N18" s="30"/>
@@ -4716,15 +6058,33 @@
       <c r="P18" s="46"/>
     </row>
     <row r="19" spans="2:16" ht="21.2" customHeight="1">
-      <c r="B19" s="8"/>
-      <c r="C19" s="6"/>
-      <c r="D19" s="6"/>
-      <c r="E19" s="6"/>
-      <c r="F19" s="6"/>
-      <c r="G19" s="6"/>
-      <c r="H19" s="6"/>
-      <c r="I19" s="6"/>
-      <c r="J19" s="6"/>
+      <c r="B19" s="8">
+        <v>13</v>
+      </c>
+      <c r="C19" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="D19" s="6" t="s">
+        <v>182</v>
+      </c>
+      <c r="E19" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="F19" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="G19" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="H19" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="I19" s="6">
+        <v>8</v>
+      </c>
+      <c r="J19" s="6">
+        <v>5</v>
+      </c>
       <c r="K19" s="6"/>
       <c r="L19" s="6"/>
       <c r="M19" s="6"/>
@@ -4733,10 +6093,16 @@
       <c r="P19" s="46"/>
     </row>
     <row r="20" spans="2:16" ht="21.2" customHeight="1">
-      <c r="B20" s="8"/>
+      <c r="B20" s="8">
+        <v>14</v>
+      </c>
       <c r="C20" s="6"/>
-      <c r="D20" s="6"/>
-      <c r="E20" s="6"/>
+      <c r="D20" s="6" t="s">
+        <v>183</v>
+      </c>
+      <c r="E20" s="6" t="s">
+        <v>142</v>
+      </c>
       <c r="F20" s="6"/>
       <c r="G20" s="6"/>
       <c r="H20" s="6"/>
@@ -4750,24 +6116,48 @@
       <c r="P20" s="46"/>
     </row>
     <row r="21" spans="2:16" ht="21.2" customHeight="1">
-      <c r="B21" s="8"/>
-      <c r="C21" s="6"/>
-      <c r="D21" s="6"/>
-      <c r="E21" s="6"/>
-      <c r="F21" s="6"/>
-      <c r="G21" s="6"/>
-      <c r="H21" s="6"/>
-      <c r="I21" s="6"/>
-      <c r="J21" s="6"/>
-      <c r="K21" s="6"/>
+      <c r="B21" s="8">
+        <v>15</v>
+      </c>
+      <c r="C21" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="D21" s="6" t="s">
+        <v>184</v>
+      </c>
+      <c r="E21" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="F21" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="G21" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="H21" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="I21" s="6">
+        <v>9</v>
+      </c>
+      <c r="J21" s="6">
+        <v>7</v>
+      </c>
+      <c r="K21" s="6">
+        <v>21</v>
+      </c>
       <c r="L21" s="6"/>
       <c r="M21" s="6"/>
-      <c r="N21" s="30"/>
+      <c r="N21" s="30" t="s">
+        <v>185</v>
+      </c>
       <c r="O21" s="45"/>
       <c r="P21" s="46"/>
     </row>
     <row r="22" spans="2:16" ht="21.2" customHeight="1">
-      <c r="B22" s="8"/>
+      <c r="B22" s="8">
+        <v>16</v>
+      </c>
       <c r="C22" s="6"/>
       <c r="D22" s="6"/>
       <c r="E22" s="6"/>
@@ -4784,7 +6174,9 @@
       <c r="P22" s="46"/>
     </row>
     <row r="23" spans="2:16" ht="21.2" customHeight="1">
-      <c r="B23" s="8"/>
+      <c r="B23" s="8">
+        <v>17</v>
+      </c>
       <c r="C23" s="6"/>
       <c r="D23" s="6"/>
       <c r="E23" s="6"/>
@@ -4801,7 +6193,9 @@
       <c r="P23" s="46"/>
     </row>
     <row r="24" spans="2:16" ht="21.2" customHeight="1">
-      <c r="B24" s="8"/>
+      <c r="B24" s="8">
+        <v>18</v>
+      </c>
       <c r="C24" s="6"/>
       <c r="D24" s="6"/>
       <c r="E24" s="6"/>
@@ -4818,7 +6212,9 @@
       <c r="P24" s="46"/>
     </row>
     <row r="25" spans="2:16" ht="21.2" customHeight="1">
-      <c r="B25" s="8"/>
+      <c r="B25" s="8">
+        <v>19</v>
+      </c>
       <c r="C25" s="6"/>
       <c r="D25" s="6"/>
       <c r="E25" s="6"/>
@@ -4835,7 +6231,9 @@
       <c r="P25" s="46"/>
     </row>
     <row r="26" spans="2:16" ht="21.2" customHeight="1">
-      <c r="B26" s="8"/>
+      <c r="B26" s="8">
+        <v>20</v>
+      </c>
       <c r="C26" s="6"/>
       <c r="D26" s="6"/>
       <c r="E26" s="6"/>
@@ -4852,7 +6250,9 @@
       <c r="P26" s="46"/>
     </row>
     <row r="27" spans="2:16" ht="21.2" customHeight="1" thickBot="1">
-      <c r="B27" s="9"/>
+      <c r="B27" s="9">
+        <v>21</v>
+      </c>
       <c r="C27" s="10"/>
       <c r="D27" s="10"/>
       <c r="E27" s="10"/>
@@ -4968,211 +6368,385 @@
       </c>
     </row>
     <row r="32" spans="2:16" ht="21.2" customHeight="1">
-      <c r="B32" s="8"/>
-      <c r="C32" s="6"/>
-      <c r="D32" s="6"/>
-      <c r="E32" s="24"/>
-      <c r="G32" s="8"/>
-      <c r="H32" s="6"/>
-      <c r="I32" s="6"/>
-      <c r="J32" s="24"/>
-      <c r="L32" s="8"/>
+      <c r="B32" s="8">
+        <v>1</v>
+      </c>
+      <c r="C32" s="6" t="s">
+        <v>104</v>
+      </c>
+      <c r="D32" s="6" t="s">
+        <v>186</v>
+      </c>
+      <c r="E32" s="24">
+        <v>62</v>
+      </c>
+      <c r="G32" s="8">
+        <v>1</v>
+      </c>
+      <c r="H32" s="6" t="s">
+        <v>55</v>
+      </c>
+      <c r="I32" s="6" t="s">
+        <v>165</v>
+      </c>
+      <c r="J32" s="24">
+        <v>40</v>
+      </c>
+      <c r="L32" s="8">
+        <v>1</v>
+      </c>
       <c r="M32" s="6"/>
       <c r="N32" s="11"/>
       <c r="O32" s="21"/>
     </row>
     <row r="33" spans="2:16" ht="21.2" customHeight="1">
-      <c r="B33" s="8"/>
-      <c r="C33" s="6"/>
-      <c r="D33" s="6"/>
-      <c r="E33" s="24"/>
-      <c r="G33" s="8"/>
-      <c r="H33" s="6"/>
-      <c r="I33" s="6"/>
-      <c r="J33" s="24"/>
-      <c r="L33" s="8"/>
+      <c r="B33" s="8">
+        <v>2</v>
+      </c>
+      <c r="C33" s="6" t="s">
+        <v>65</v>
+      </c>
+      <c r="D33" s="6" t="s">
+        <v>187</v>
+      </c>
+      <c r="E33" s="24">
+        <v>50</v>
+      </c>
+      <c r="G33" s="8">
+        <v>2</v>
+      </c>
+      <c r="H33" s="6" t="s">
+        <v>59</v>
+      </c>
+      <c r="I33" s="6" t="s">
+        <v>167</v>
+      </c>
+      <c r="J33" s="24">
+        <v>190</v>
+      </c>
+      <c r="L33" s="8">
+        <v>2</v>
+      </c>
       <c r="M33" s="6"/>
       <c r="N33" s="11"/>
       <c r="O33" s="21"/>
     </row>
     <row r="34" spans="2:16" ht="21.2" customHeight="1">
-      <c r="B34" s="8"/>
-      <c r="C34" s="6"/>
-      <c r="D34" s="6"/>
-      <c r="E34" s="24"/>
-      <c r="G34" s="8"/>
-      <c r="H34" s="6"/>
-      <c r="I34" s="6"/>
-      <c r="J34" s="24"/>
-      <c r="L34" s="8"/>
+      <c r="B34" s="8">
+        <v>3</v>
+      </c>
+      <c r="C34" s="6" t="s">
+        <v>61</v>
+      </c>
+      <c r="D34" s="6" t="s">
+        <v>188</v>
+      </c>
+      <c r="E34" s="24">
+        <v>112</v>
+      </c>
+      <c r="G34" s="8">
+        <v>3</v>
+      </c>
+      <c r="H34" s="6" t="s">
+        <v>57</v>
+      </c>
+      <c r="I34" s="6" t="s">
+        <v>168</v>
+      </c>
+      <c r="J34" s="24">
+        <v>130</v>
+      </c>
+      <c r="L34" s="8">
+        <v>3</v>
+      </c>
       <c r="M34" s="6"/>
       <c r="N34" s="11"/>
       <c r="O34" s="21"/>
     </row>
     <row r="35" spans="2:16" ht="21.2" customHeight="1">
-      <c r="B35" s="8"/>
-      <c r="C35" s="6"/>
-      <c r="D35" s="6"/>
-      <c r="E35" s="24"/>
-      <c r="G35" s="8"/>
-      <c r="H35" s="6"/>
-      <c r="I35" s="6"/>
-      <c r="J35" s="24"/>
-      <c r="L35" s="8"/>
+      <c r="B35" s="8">
+        <v>4</v>
+      </c>
+      <c r="C35" s="6" t="s">
+        <v>59</v>
+      </c>
+      <c r="D35" s="6" t="s">
+        <v>189</v>
+      </c>
+      <c r="E35" s="24">
+        <v>147</v>
+      </c>
+      <c r="G35" s="8">
+        <v>4</v>
+      </c>
+      <c r="H35" s="6" t="s">
+        <v>160</v>
+      </c>
+      <c r="I35" s="6" t="s">
+        <v>176</v>
+      </c>
+      <c r="J35" s="24">
+        <v>36</v>
+      </c>
+      <c r="L35" s="8">
+        <v>4</v>
+      </c>
       <c r="M35" s="6"/>
       <c r="N35" s="11"/>
       <c r="O35" s="21"/>
     </row>
     <row r="36" spans="2:16" ht="21.2" customHeight="1">
-      <c r="B36" s="8"/>
-      <c r="C36" s="6"/>
-      <c r="D36" s="6"/>
-      <c r="E36" s="24"/>
-      <c r="G36" s="8"/>
+      <c r="B36" s="8">
+        <v>5</v>
+      </c>
+      <c r="C36" s="6" t="s">
+        <v>57</v>
+      </c>
+      <c r="D36" s="6" t="s">
+        <v>190</v>
+      </c>
+      <c r="E36" s="24">
+        <v>50</v>
+      </c>
+      <c r="G36" s="8">
+        <v>5</v>
+      </c>
       <c r="H36" s="6"/>
       <c r="I36" s="6"/>
       <c r="J36" s="21"/>
-      <c r="L36" s="8"/>
+      <c r="L36" s="8">
+        <v>5</v>
+      </c>
       <c r="M36" s="6"/>
       <c r="N36" s="11"/>
       <c r="O36" s="21"/>
     </row>
     <row r="37" spans="2:16" ht="21.2" customHeight="1">
-      <c r="B37" s="8"/>
-      <c r="C37" s="6"/>
-      <c r="D37" s="6"/>
-      <c r="E37" s="24"/>
-      <c r="G37" s="8"/>
+      <c r="B37" s="8">
+        <v>6</v>
+      </c>
+      <c r="C37" s="6" t="s">
+        <v>160</v>
+      </c>
+      <c r="D37" s="6" t="s">
+        <v>191</v>
+      </c>
+      <c r="E37" s="24">
+        <v>11</v>
+      </c>
+      <c r="G37" s="8">
+        <v>6</v>
+      </c>
       <c r="H37" s="6"/>
       <c r="I37" s="6"/>
       <c r="J37" s="21"/>
-      <c r="L37" s="8"/>
+      <c r="L37" s="8">
+        <v>6</v>
+      </c>
       <c r="M37" s="6"/>
       <c r="N37" s="11"/>
       <c r="O37" s="21"/>
     </row>
     <row r="38" spans="2:16" ht="21.2" customHeight="1">
-      <c r="B38" s="8"/>
-      <c r="C38" s="6"/>
-      <c r="D38" s="6"/>
-      <c r="E38" s="24"/>
-      <c r="G38" s="8"/>
+      <c r="B38" s="8">
+        <v>7</v>
+      </c>
+      <c r="C38" s="6" t="s">
+        <v>69</v>
+      </c>
+      <c r="D38" s="6" t="s">
+        <v>192</v>
+      </c>
+      <c r="E38" s="24">
+        <v>87</v>
+      </c>
+      <c r="G38" s="8">
+        <v>7</v>
+      </c>
       <c r="H38" s="6"/>
       <c r="I38" s="6"/>
       <c r="J38" s="21"/>
-      <c r="L38" s="8"/>
+      <c r="L38" s="8">
+        <v>7</v>
+      </c>
       <c r="M38" s="6"/>
       <c r="N38" s="11"/>
       <c r="O38" s="21"/>
     </row>
     <row r="39" spans="2:16" ht="21.2" customHeight="1">
-      <c r="B39" s="8"/>
-      <c r="C39" s="6"/>
-      <c r="D39" s="6"/>
-      <c r="E39" s="24"/>
-      <c r="G39" s="8"/>
+      <c r="B39" s="8">
+        <v>8</v>
+      </c>
+      <c r="C39" s="6" t="s">
+        <v>67</v>
+      </c>
+      <c r="D39" s="6" t="s">
+        <v>193</v>
+      </c>
+      <c r="E39" s="24">
+        <v>60</v>
+      </c>
+      <c r="G39" s="8">
+        <v>8</v>
+      </c>
       <c r="H39" s="6"/>
       <c r="I39" s="6"/>
       <c r="J39" s="21"/>
-      <c r="L39" s="8"/>
+      <c r="L39" s="8">
+        <v>8</v>
+      </c>
       <c r="M39" s="6"/>
       <c r="N39" s="11"/>
       <c r="O39" s="21"/>
     </row>
     <row r="40" spans="2:16" ht="21.2" customHeight="1">
-      <c r="B40" s="8"/>
-      <c r="C40" s="6"/>
-      <c r="D40" s="6"/>
-      <c r="E40" s="24"/>
-      <c r="G40" s="8"/>
+      <c r="B40" s="8">
+        <v>9</v>
+      </c>
+      <c r="C40" s="6" t="s">
+        <v>55</v>
+      </c>
+      <c r="D40" s="6" t="s">
+        <v>194</v>
+      </c>
+      <c r="E40" s="24">
+        <v>35</v>
+      </c>
+      <c r="G40" s="8">
+        <v>9</v>
+      </c>
       <c r="H40" s="6"/>
       <c r="I40" s="6"/>
       <c r="J40" s="21"/>
-      <c r="L40" s="8"/>
+      <c r="L40" s="8">
+        <v>9</v>
+      </c>
       <c r="M40" s="6"/>
       <c r="N40" s="11"/>
       <c r="O40" s="21"/>
     </row>
     <row r="41" spans="2:16" ht="21.2" customHeight="1">
-      <c r="B41" s="8"/>
-      <c r="C41" s="6"/>
-      <c r="D41" s="6"/>
-      <c r="E41" s="24"/>
-      <c r="G41" s="8"/>
+      <c r="B41" s="8">
+        <v>10</v>
+      </c>
+      <c r="C41" s="6" t="s">
+        <v>160</v>
+      </c>
+      <c r="D41" s="6" t="s">
+        <v>195</v>
+      </c>
+      <c r="E41" s="24">
+        <v>39</v>
+      </c>
+      <c r="G41" s="8">
+        <v>10</v>
+      </c>
       <c r="H41" s="6"/>
       <c r="I41" s="6"/>
       <c r="J41" s="21"/>
-      <c r="L41" s="8"/>
+      <c r="L41" s="8">
+        <v>10</v>
+      </c>
       <c r="M41" s="6"/>
       <c r="N41" s="11"/>
       <c r="O41" s="21"/>
     </row>
     <row r="42" spans="2:16" ht="21.2" customHeight="1">
-      <c r="B42" s="8"/>
+      <c r="B42" s="8">
+        <v>11</v>
+      </c>
       <c r="C42" s="6"/>
       <c r="D42" s="6"/>
       <c r="E42" s="21"/>
-      <c r="G42" s="8"/>
+      <c r="G42" s="8">
+        <v>11</v>
+      </c>
       <c r="H42" s="6"/>
       <c r="I42" s="6"/>
       <c r="J42" s="21"/>
-      <c r="L42" s="8"/>
+      <c r="L42" s="8">
+        <v>11</v>
+      </c>
       <c r="M42" s="6"/>
       <c r="N42" s="11"/>
       <c r="O42" s="21"/>
     </row>
     <row r="43" spans="2:16" ht="21.2" customHeight="1">
-      <c r="B43" s="8"/>
+      <c r="B43" s="8">
+        <v>12</v>
+      </c>
       <c r="C43" s="6"/>
       <c r="D43" s="6"/>
       <c r="E43" s="21"/>
-      <c r="G43" s="8"/>
+      <c r="G43" s="8">
+        <v>12</v>
+      </c>
       <c r="H43" s="6"/>
       <c r="I43" s="6"/>
       <c r="J43" s="21"/>
-      <c r="L43" s="8"/>
+      <c r="L43" s="8">
+        <v>12</v>
+      </c>
       <c r="M43" s="6"/>
       <c r="N43" s="11"/>
       <c r="O43" s="21"/>
     </row>
     <row r="44" spans="2:16" ht="21.2" customHeight="1">
-      <c r="B44" s="8"/>
+      <c r="B44" s="8">
+        <v>13</v>
+      </c>
       <c r="C44" s="6"/>
       <c r="D44" s="6"/>
       <c r="E44" s="21"/>
-      <c r="G44" s="8"/>
+      <c r="G44" s="8">
+        <v>13</v>
+      </c>
       <c r="H44" s="6"/>
       <c r="I44" s="6"/>
       <c r="J44" s="21"/>
-      <c r="L44" s="8"/>
+      <c r="L44" s="8">
+        <v>13</v>
+      </c>
       <c r="M44" s="6"/>
       <c r="N44" s="11"/>
       <c r="O44" s="21"/>
     </row>
     <row r="45" spans="2:16" ht="21.2" customHeight="1">
-      <c r="B45" s="8"/>
+      <c r="B45" s="8">
+        <v>14</v>
+      </c>
       <c r="C45" s="6"/>
       <c r="D45" s="6"/>
       <c r="E45" s="21"/>
-      <c r="G45" s="8"/>
+      <c r="G45" s="8">
+        <v>14</v>
+      </c>
       <c r="H45" s="6"/>
       <c r="I45" s="6"/>
       <c r="J45" s="21"/>
-      <c r="L45" s="8"/>
+      <c r="L45" s="8">
+        <v>14</v>
+      </c>
       <c r="M45" s="6"/>
       <c r="N45" s="11"/>
       <c r="O45" s="21"/>
     </row>
     <row r="46" spans="2:16" ht="21.2" customHeight="1" thickBot="1">
-      <c r="B46" s="9"/>
+      <c r="B46" s="9">
+        <v>15</v>
+      </c>
       <c r="C46" s="10"/>
       <c r="D46" s="10"/>
       <c r="E46" s="22"/>
-      <c r="G46" s="9"/>
+      <c r="G46" s="9">
+        <v>15</v>
+      </c>
       <c r="H46" s="10"/>
       <c r="I46" s="10"/>
       <c r="J46" s="22"/>
-      <c r="L46" s="9"/>
+      <c r="L46" s="9">
+        <v>15</v>
+      </c>
       <c r="M46" s="10"/>
       <c r="N46" s="12"/>
       <c r="O46" s="22"/>
@@ -5294,7 +6868,9 @@
         <v>0</v>
       </c>
       <c r="C3" s="39"/>
-      <c r="D3" s="34"/>
+      <c r="D3" s="34" t="s">
+        <v>1</v>
+      </c>
       <c r="E3" s="40"/>
       <c r="F3" s="40"/>
       <c r="G3" s="40"/>
@@ -5302,7 +6878,9 @@
       <c r="I3" s="23" t="s">
         <v>2</v>
       </c>
-      <c r="J3" s="34"/>
+      <c r="J3" s="34" t="s">
+        <v>3</v>
+      </c>
       <c r="K3" s="40"/>
       <c r="L3" s="40"/>
       <c r="M3" s="40"/>
@@ -5310,7 +6888,9 @@
       <c r="O3" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="P3" s="2"/>
+      <c r="P3" s="2" t="s">
+        <v>196</v>
+      </c>
     </row>
     <row r="4" spans="2:16" ht="15" customHeight="1" thickBot="1">
       <c r="B4" s="5"/>
@@ -5392,10 +6972,18 @@
       <c r="P6" s="44"/>
     </row>
     <row r="7" spans="2:16" ht="21.2" customHeight="1">
-      <c r="B7" s="8"/>
-      <c r="C7" s="6"/>
-      <c r="D7" s="6"/>
-      <c r="E7" s="36"/>
+      <c r="B7" s="8">
+        <v>1</v>
+      </c>
+      <c r="C7" s="6" t="s">
+        <v>160</v>
+      </c>
+      <c r="D7" s="6" t="s">
+        <v>197</v>
+      </c>
+      <c r="E7" s="36" t="s">
+        <v>198</v>
+      </c>
       <c r="F7" s="37"/>
       <c r="G7" s="37"/>
       <c r="H7" s="37"/>
@@ -5409,78 +6997,162 @@
       <c r="P7" s="46"/>
     </row>
     <row r="8" spans="2:16" ht="21.2" customHeight="1">
-      <c r="B8" s="8"/>
-      <c r="C8" s="6"/>
-      <c r="D8" s="6"/>
-      <c r="E8" s="6"/>
-      <c r="F8" s="6"/>
-      <c r="G8" s="6"/>
-      <c r="H8" s="6"/>
-      <c r="I8" s="6"/>
+      <c r="B8" s="8">
+        <v>2</v>
+      </c>
+      <c r="C8" s="6" t="s">
+        <v>57</v>
+      </c>
+      <c r="D8" s="6" t="s">
+        <v>199</v>
+      </c>
+      <c r="E8" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="F8" s="6" t="s">
+        <v>84</v>
+      </c>
+      <c r="G8" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="H8" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="I8" s="6">
+        <v>4</v>
+      </c>
       <c r="J8" s="6"/>
-      <c r="K8" s="6"/>
+      <c r="K8" s="6">
+        <v>42</v>
+      </c>
       <c r="L8" s="6"/>
       <c r="M8" s="6"/>
-      <c r="N8" s="30"/>
+      <c r="N8" s="30" t="s">
+        <v>200</v>
+      </c>
       <c r="O8" s="45"/>
       <c r="P8" s="46"/>
     </row>
     <row r="9" spans="2:16" ht="21.2" customHeight="1">
-      <c r="B9" s="8"/>
-      <c r="C9" s="6"/>
-      <c r="D9" s="6"/>
-      <c r="E9" s="6"/>
-      <c r="F9" s="6"/>
-      <c r="G9" s="6"/>
-      <c r="H9" s="6"/>
-      <c r="I9" s="6"/>
+      <c r="B9" s="8">
+        <v>3</v>
+      </c>
+      <c r="C9" s="6" t="s">
+        <v>87</v>
+      </c>
+      <c r="D9" s="6" t="s">
+        <v>201</v>
+      </c>
+      <c r="E9" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="F9" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="G9" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="H9" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="I9" s="6">
+        <v>4</v>
+      </c>
       <c r="J9" s="6"/>
-      <c r="K9" s="6"/>
+      <c r="K9" s="6">
+        <v>32</v>
+      </c>
       <c r="L9" s="6"/>
       <c r="M9" s="6"/>
-      <c r="N9" s="30"/>
+      <c r="N9" s="30" t="s">
+        <v>202</v>
+      </c>
       <c r="O9" s="45"/>
       <c r="P9" s="46"/>
     </row>
     <row r="10" spans="2:16" ht="21.2" customHeight="1">
-      <c r="B10" s="8"/>
-      <c r="C10" s="6"/>
-      <c r="D10" s="6"/>
-      <c r="E10" s="6"/>
-      <c r="F10" s="6"/>
-      <c r="G10" s="6"/>
-      <c r="H10" s="6"/>
-      <c r="I10" s="6"/>
+      <c r="B10" s="8">
+        <v>4</v>
+      </c>
+      <c r="C10" s="6" t="s">
+        <v>59</v>
+      </c>
+      <c r="D10" s="6" t="s">
+        <v>203</v>
+      </c>
+      <c r="E10" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="F10" s="6" t="s">
+        <v>84</v>
+      </c>
+      <c r="G10" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="H10" s="6" t="s">
+        <v>100</v>
+      </c>
+      <c r="I10" s="6">
+        <v>2</v>
+      </c>
       <c r="J10" s="6"/>
       <c r="K10" s="6"/>
       <c r="L10" s="6"/>
       <c r="M10" s="6"/>
-      <c r="N10" s="30"/>
+      <c r="N10" s="30" t="s">
+        <v>126</v>
+      </c>
       <c r="O10" s="45"/>
       <c r="P10" s="46"/>
     </row>
     <row r="11" spans="2:16" ht="21.75" customHeight="1">
-      <c r="B11" s="8"/>
-      <c r="C11" s="6"/>
-      <c r="D11" s="6"/>
-      <c r="E11" s="6"/>
-      <c r="F11" s="6"/>
-      <c r="G11" s="6"/>
-      <c r="H11" s="6"/>
-      <c r="I11" s="6"/>
+      <c r="B11" s="8">
+        <v>5</v>
+      </c>
+      <c r="C11" s="6" t="s">
+        <v>55</v>
+      </c>
+      <c r="D11" s="6" t="s">
+        <v>74</v>
+      </c>
+      <c r="E11" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="F11" s="6" t="s">
+        <v>84</v>
+      </c>
+      <c r="G11" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="H11" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="I11" s="6">
+        <v>2</v>
+      </c>
       <c r="J11" s="6"/>
-      <c r="K11" s="6"/>
+      <c r="K11" s="6">
+        <v>28</v>
+      </c>
       <c r="L11" s="6"/>
       <c r="M11" s="6"/>
-      <c r="N11" s="30"/>
+      <c r="N11" s="30" t="s">
+        <v>204</v>
+      </c>
       <c r="O11" s="45"/>
       <c r="P11" s="46"/>
     </row>
     <row r="12" spans="2:16" ht="26.25" customHeight="1">
-      <c r="B12" s="8"/>
+      <c r="B12" s="8">
+        <v>6</v>
+      </c>
       <c r="C12" s="6"/>
-      <c r="D12" s="6"/>
-      <c r="E12" s="36"/>
+      <c r="D12" s="6" t="s">
+        <v>205</v>
+      </c>
+      <c r="E12" s="36" t="s">
+        <v>206</v>
+      </c>
       <c r="F12" s="37"/>
       <c r="G12" s="37"/>
       <c r="H12" s="37"/>
@@ -5494,10 +7166,16 @@
       <c r="P12" s="46"/>
     </row>
     <row r="13" spans="2:16" ht="30" customHeight="1">
-      <c r="B13" s="8"/>
+      <c r="B13" s="8">
+        <v>7</v>
+      </c>
       <c r="C13" s="6"/>
-      <c r="D13" s="6"/>
-      <c r="E13" s="36"/>
+      <c r="D13" s="6" t="s">
+        <v>207</v>
+      </c>
+      <c r="E13" s="36" t="s">
+        <v>208</v>
+      </c>
       <c r="F13" s="37"/>
       <c r="G13" s="37"/>
       <c r="H13" s="37"/>
@@ -5511,10 +7189,16 @@
       <c r="P13" s="46"/>
     </row>
     <row r="14" spans="2:16" ht="29.25" customHeight="1">
-      <c r="B14" s="8"/>
+      <c r="B14" s="8">
+        <v>8</v>
+      </c>
       <c r="C14" s="6"/>
-      <c r="D14" s="6"/>
-      <c r="E14" s="36"/>
+      <c r="D14" s="6" t="s">
+        <v>209</v>
+      </c>
+      <c r="E14" s="36" t="s">
+        <v>210</v>
+      </c>
       <c r="F14" s="37"/>
       <c r="G14" s="37"/>
       <c r="H14" s="37"/>
@@ -5528,10 +7212,16 @@
       <c r="P14" s="46"/>
     </row>
     <row r="15" spans="2:16" ht="21.2" customHeight="1">
-      <c r="B15" s="8"/>
+      <c r="B15" s="8">
+        <v>9</v>
+      </c>
       <c r="C15" s="6"/>
-      <c r="D15" s="6"/>
-      <c r="E15" s="6"/>
+      <c r="D15" s="6" t="s">
+        <v>211</v>
+      </c>
+      <c r="E15" s="6" t="s">
+        <v>212</v>
+      </c>
       <c r="F15" s="6"/>
       <c r="G15" s="6"/>
       <c r="H15" s="6"/>
@@ -5545,7 +7235,9 @@
       <c r="P15" s="46"/>
     </row>
     <row r="16" spans="2:16" ht="21.2" customHeight="1">
-      <c r="B16" s="8"/>
+      <c r="B16" s="8">
+        <v>10</v>
+      </c>
       <c r="C16" s="6"/>
       <c r="D16" s="6"/>
       <c r="E16" s="6"/>
@@ -5562,7 +7254,9 @@
       <c r="P16" s="46"/>
     </row>
     <row r="17" spans="2:16" ht="21.2" customHeight="1">
-      <c r="B17" s="8"/>
+      <c r="B17" s="8">
+        <v>11</v>
+      </c>
       <c r="C17" s="6"/>
       <c r="D17" s="6"/>
       <c r="E17" s="6"/>
@@ -5579,7 +7273,9 @@
       <c r="P17" s="46"/>
     </row>
     <row r="18" spans="2:16" ht="21.2" customHeight="1">
-      <c r="B18" s="8"/>
+      <c r="B18" s="8">
+        <v>12</v>
+      </c>
       <c r="C18" s="6"/>
       <c r="D18" s="6"/>
       <c r="E18" s="6"/>
@@ -5596,7 +7292,9 @@
       <c r="P18" s="46"/>
     </row>
     <row r="19" spans="2:16" ht="21.2" customHeight="1">
-      <c r="B19" s="8"/>
+      <c r="B19" s="8">
+        <v>13</v>
+      </c>
       <c r="C19" s="6"/>
       <c r="D19" s="6"/>
       <c r="E19" s="6"/>
@@ -5613,7 +7311,9 @@
       <c r="P19" s="46"/>
     </row>
     <row r="20" spans="2:16" ht="21.2" customHeight="1">
-      <c r="B20" s="8"/>
+      <c r="B20" s="8">
+        <v>14</v>
+      </c>
       <c r="C20" s="6"/>
       <c r="D20" s="6"/>
       <c r="E20" s="6"/>
@@ -5630,7 +7330,9 @@
       <c r="P20" s="46"/>
     </row>
     <row r="21" spans="2:16" ht="21.2" customHeight="1">
-      <c r="B21" s="8"/>
+      <c r="B21" s="8">
+        <v>15</v>
+      </c>
       <c r="C21" s="6"/>
       <c r="D21" s="6"/>
       <c r="E21" s="6"/>
@@ -5647,7 +7349,9 @@
       <c r="P21" s="46"/>
     </row>
     <row r="22" spans="2:16" ht="21.2" customHeight="1">
-      <c r="B22" s="8"/>
+      <c r="B22" s="8">
+        <v>16</v>
+      </c>
       <c r="C22" s="6"/>
       <c r="D22" s="6"/>
       <c r="E22" s="6"/>
@@ -5664,7 +7368,9 @@
       <c r="P22" s="46"/>
     </row>
     <row r="23" spans="2:16" ht="21.2" customHeight="1">
-      <c r="B23" s="8"/>
+      <c r="B23" s="8">
+        <v>17</v>
+      </c>
       <c r="C23" s="6"/>
       <c r="D23" s="6"/>
       <c r="E23" s="6"/>
@@ -5681,7 +7387,9 @@
       <c r="P23" s="46"/>
     </row>
     <row r="24" spans="2:16" ht="21.2" customHeight="1">
-      <c r="B24" s="8"/>
+      <c r="B24" s="8">
+        <v>18</v>
+      </c>
       <c r="C24" s="6"/>
       <c r="D24" s="6"/>
       <c r="E24" s="6"/>
@@ -5698,7 +7406,9 @@
       <c r="P24" s="46"/>
     </row>
     <row r="25" spans="2:16" ht="21.2" customHeight="1">
-      <c r="B25" s="8"/>
+      <c r="B25" s="8">
+        <v>19</v>
+      </c>
       <c r="C25" s="6"/>
       <c r="D25" s="6"/>
       <c r="E25" s="6"/>
@@ -5715,7 +7425,9 @@
       <c r="P25" s="46"/>
     </row>
     <row r="26" spans="2:16" ht="21.2" customHeight="1">
-      <c r="B26" s="8"/>
+      <c r="B26" s="8">
+        <v>20</v>
+      </c>
       <c r="C26" s="6"/>
       <c r="D26" s="6"/>
       <c r="E26" s="6"/>
@@ -5732,7 +7444,9 @@
       <c r="P26" s="46"/>
     </row>
     <row r="27" spans="2:16" ht="21.2" customHeight="1" thickBot="1">
-      <c r="B27" s="9"/>
+      <c r="B27" s="9">
+        <v>21</v>
+      </c>
       <c r="C27" s="10"/>
       <c r="D27" s="10"/>
       <c r="E27" s="10"/>
@@ -5848,211 +7562,415 @@
       </c>
     </row>
     <row r="32" spans="2:16" ht="21.2" customHeight="1">
-      <c r="B32" s="8"/>
-      <c r="C32" s="6"/>
-      <c r="D32" s="6"/>
-      <c r="E32" s="24"/>
-      <c r="G32" s="8"/>
-      <c r="H32" s="6"/>
-      <c r="I32" s="6"/>
-      <c r="J32" s="24"/>
-      <c r="L32" s="8"/>
+      <c r="B32" s="8">
+        <v>1</v>
+      </c>
+      <c r="C32" s="6" t="s">
+        <v>160</v>
+      </c>
+      <c r="D32" s="6" t="s">
+        <v>213</v>
+      </c>
+      <c r="E32" s="24">
+        <v>63</v>
+      </c>
+      <c r="G32" s="8">
+        <v>1</v>
+      </c>
+      <c r="H32" s="6" t="s">
+        <v>160</v>
+      </c>
+      <c r="I32" s="6" t="s">
+        <v>197</v>
+      </c>
+      <c r="J32" s="24">
+        <v>54</v>
+      </c>
+      <c r="L32" s="8">
+        <v>1</v>
+      </c>
       <c r="M32" s="6"/>
       <c r="N32" s="11"/>
       <c r="O32" s="21"/>
     </row>
     <row r="33" spans="2:16" ht="21.2" customHeight="1">
-      <c r="B33" s="8"/>
-      <c r="C33" s="6"/>
-      <c r="D33" s="6"/>
-      <c r="E33" s="24"/>
-      <c r="G33" s="8"/>
-      <c r="H33" s="6"/>
-      <c r="I33" s="6"/>
-      <c r="J33" s="24"/>
-      <c r="L33" s="8"/>
+      <c r="B33" s="8">
+        <v>2</v>
+      </c>
+      <c r="C33" s="6" t="s">
+        <v>160</v>
+      </c>
+      <c r="D33" s="6" t="s">
+        <v>214</v>
+      </c>
+      <c r="E33" s="24">
+        <v>8</v>
+      </c>
+      <c r="G33" s="8">
+        <v>2</v>
+      </c>
+      <c r="H33" s="6" t="s">
+        <v>57</v>
+      </c>
+      <c r="I33" s="6" t="s">
+        <v>199</v>
+      </c>
+      <c r="J33" s="24">
+        <v>80</v>
+      </c>
+      <c r="L33" s="8">
+        <v>2</v>
+      </c>
       <c r="M33" s="6"/>
       <c r="N33" s="11"/>
       <c r="O33" s="21"/>
     </row>
     <row r="34" spans="2:16" ht="21.2" customHeight="1">
-      <c r="B34" s="8"/>
-      <c r="C34" s="6"/>
-      <c r="D34" s="6"/>
-      <c r="E34" s="24"/>
-      <c r="G34" s="8"/>
-      <c r="H34" s="6"/>
-      <c r="I34" s="6"/>
-      <c r="J34" s="24"/>
-      <c r="L34" s="8"/>
+      <c r="B34" s="8">
+        <v>3</v>
+      </c>
+      <c r="C34" s="6" t="s">
+        <v>160</v>
+      </c>
+      <c r="D34" s="6" t="s">
+        <v>215</v>
+      </c>
+      <c r="E34" s="24">
+        <v>31</v>
+      </c>
+      <c r="G34" s="8">
+        <v>3</v>
+      </c>
+      <c r="H34" s="6" t="s">
+        <v>59</v>
+      </c>
+      <c r="I34" s="6" t="s">
+        <v>203</v>
+      </c>
+      <c r="J34" s="24">
+        <v>137</v>
+      </c>
+      <c r="L34" s="8">
+        <v>3</v>
+      </c>
       <c r="M34" s="6"/>
       <c r="N34" s="11"/>
       <c r="O34" s="21"/>
     </row>
     <row r="35" spans="2:16" ht="21.2" customHeight="1">
-      <c r="B35" s="8"/>
-      <c r="C35" s="6"/>
-      <c r="D35" s="6"/>
-      <c r="E35" s="24"/>
-      <c r="G35" s="8"/>
-      <c r="H35" s="6"/>
-      <c r="I35" s="6"/>
-      <c r="J35" s="24"/>
-      <c r="L35" s="8"/>
+      <c r="B35" s="8">
+        <v>4</v>
+      </c>
+      <c r="C35" s="6" t="s">
+        <v>55</v>
+      </c>
+      <c r="D35" s="6" t="s">
+        <v>216</v>
+      </c>
+      <c r="E35" s="24">
+        <v>77</v>
+      </c>
+      <c r="G35" s="8">
+        <v>4</v>
+      </c>
+      <c r="H35" s="6" t="s">
+        <v>55</v>
+      </c>
+      <c r="I35" s="6" t="s">
+        <v>74</v>
+      </c>
+      <c r="J35" s="24">
+        <v>60</v>
+      </c>
+      <c r="L35" s="8">
+        <v>4</v>
+      </c>
       <c r="M35" s="6"/>
       <c r="N35" s="11"/>
       <c r="O35" s="21"/>
     </row>
     <row r="36" spans="2:16" ht="21.2" customHeight="1">
-      <c r="B36" s="8"/>
-      <c r="C36" s="6"/>
-      <c r="D36" s="6"/>
-      <c r="E36" s="24"/>
-      <c r="G36" s="8"/>
+      <c r="B36" s="8">
+        <v>5</v>
+      </c>
+      <c r="C36" s="6" t="s">
+        <v>69</v>
+      </c>
+      <c r="D36" s="6" t="s">
+        <v>217</v>
+      </c>
+      <c r="E36" s="24">
+        <v>35</v>
+      </c>
+      <c r="G36" s="8">
+        <v>5</v>
+      </c>
       <c r="H36" s="6"/>
       <c r="I36" s="6"/>
       <c r="J36" s="21"/>
-      <c r="L36" s="8"/>
+      <c r="L36" s="8">
+        <v>5</v>
+      </c>
       <c r="M36" s="6"/>
       <c r="N36" s="11"/>
       <c r="O36" s="21"/>
     </row>
     <row r="37" spans="2:16" ht="21.2" customHeight="1">
-      <c r="B37" s="8"/>
-      <c r="C37" s="6"/>
-      <c r="D37" s="6"/>
-      <c r="E37" s="24"/>
-      <c r="G37" s="8"/>
+      <c r="B37" s="8">
+        <v>6</v>
+      </c>
+      <c r="C37" s="6" t="s">
+        <v>67</v>
+      </c>
+      <c r="D37" s="6" t="s">
+        <v>218</v>
+      </c>
+      <c r="E37" s="24">
+        <v>48</v>
+      </c>
+      <c r="G37" s="8">
+        <v>6</v>
+      </c>
       <c r="H37" s="6"/>
       <c r="I37" s="6"/>
       <c r="J37" s="21"/>
-      <c r="L37" s="8"/>
+      <c r="L37" s="8">
+        <v>6</v>
+      </c>
       <c r="M37" s="6"/>
       <c r="N37" s="11"/>
       <c r="O37" s="21"/>
     </row>
     <row r="38" spans="2:16" ht="21.2" customHeight="1">
-      <c r="B38" s="8"/>
-      <c r="C38" s="6"/>
-      <c r="D38" s="6"/>
-      <c r="E38" s="24"/>
-      <c r="G38" s="8"/>
+      <c r="B38" s="8">
+        <v>7</v>
+      </c>
+      <c r="C38" s="6" t="s">
+        <v>104</v>
+      </c>
+      <c r="D38" s="6" t="s">
+        <v>219</v>
+      </c>
+      <c r="E38" s="24">
+        <v>17</v>
+      </c>
+      <c r="G38" s="8">
+        <v>7</v>
+      </c>
       <c r="H38" s="6"/>
       <c r="I38" s="6"/>
       <c r="J38" s="21"/>
-      <c r="L38" s="8"/>
+      <c r="L38" s="8">
+        <v>7</v>
+      </c>
       <c r="M38" s="6"/>
       <c r="N38" s="11"/>
       <c r="O38" s="21"/>
     </row>
     <row r="39" spans="2:16" ht="21.2" customHeight="1">
-      <c r="B39" s="8"/>
-      <c r="C39" s="6"/>
-      <c r="D39" s="6"/>
-      <c r="E39" s="24"/>
-      <c r="G39" s="8"/>
+      <c r="B39" s="8">
+        <v>8</v>
+      </c>
+      <c r="C39" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="D39" s="6" t="s">
+        <v>220</v>
+      </c>
+      <c r="E39" s="24">
+        <v>85</v>
+      </c>
+      <c r="G39" s="8">
+        <v>8</v>
+      </c>
       <c r="H39" s="6"/>
       <c r="I39" s="6"/>
       <c r="J39" s="21"/>
-      <c r="L39" s="8"/>
+      <c r="L39" s="8">
+        <v>8</v>
+      </c>
       <c r="M39" s="6"/>
       <c r="N39" s="11"/>
       <c r="O39" s="21"/>
     </row>
     <row r="40" spans="2:16" ht="21.2" customHeight="1">
-      <c r="B40" s="8"/>
-      <c r="C40" s="6"/>
-      <c r="D40" s="6"/>
-      <c r="E40" s="24"/>
-      <c r="G40" s="8"/>
+      <c r="B40" s="8">
+        <v>9</v>
+      </c>
+      <c r="C40" s="6" t="s">
+        <v>65</v>
+      </c>
+      <c r="D40" s="6" t="s">
+        <v>221</v>
+      </c>
+      <c r="E40" s="24">
+        <v>50</v>
+      </c>
+      <c r="G40" s="8">
+        <v>9</v>
+      </c>
       <c r="H40" s="6"/>
       <c r="I40" s="6"/>
       <c r="J40" s="21"/>
-      <c r="L40" s="8"/>
+      <c r="L40" s="8">
+        <v>9</v>
+      </c>
       <c r="M40" s="6"/>
       <c r="N40" s="11"/>
       <c r="O40" s="21"/>
     </row>
     <row r="41" spans="2:16" ht="21.2" customHeight="1">
-      <c r="B41" s="8"/>
-      <c r="C41" s="6"/>
-      <c r="D41" s="6"/>
-      <c r="E41" s="24"/>
-      <c r="G41" s="8"/>
+      <c r="B41" s="8">
+        <v>10</v>
+      </c>
+      <c r="C41" s="6" t="s">
+        <v>154</v>
+      </c>
+      <c r="D41" s="6" t="s">
+        <v>222</v>
+      </c>
+      <c r="E41" s="24">
+        <v>49</v>
+      </c>
+      <c r="G41" s="8">
+        <v>10</v>
+      </c>
       <c r="H41" s="6"/>
       <c r="I41" s="6"/>
       <c r="J41" s="21"/>
-      <c r="L41" s="8"/>
+      <c r="L41" s="8">
+        <v>10</v>
+      </c>
       <c r="M41" s="6"/>
       <c r="N41" s="11"/>
       <c r="O41" s="21"/>
     </row>
     <row r="42" spans="2:16" ht="21.2" customHeight="1">
-      <c r="B42" s="8"/>
-      <c r="C42" s="6"/>
-      <c r="D42" s="6"/>
-      <c r="E42" s="24"/>
-      <c r="G42" s="8"/>
+      <c r="B42" s="8">
+        <v>11</v>
+      </c>
+      <c r="C42" s="6" t="s">
+        <v>61</v>
+      </c>
+      <c r="D42" s="6" t="s">
+        <v>223</v>
+      </c>
+      <c r="E42" s="24">
+        <v>39</v>
+      </c>
+      <c r="G42" s="8">
+        <v>11</v>
+      </c>
       <c r="H42" s="6"/>
       <c r="I42" s="6"/>
       <c r="J42" s="21"/>
-      <c r="L42" s="8"/>
+      <c r="L42" s="8">
+        <v>11</v>
+      </c>
       <c r="M42" s="6"/>
       <c r="N42" s="11"/>
       <c r="O42" s="21"/>
     </row>
     <row r="43" spans="2:16" ht="21.2" customHeight="1">
-      <c r="B43" s="8"/>
-      <c r="C43" s="6"/>
-      <c r="D43" s="6"/>
-      <c r="E43" s="24"/>
-      <c r="G43" s="8"/>
+      <c r="B43" s="8">
+        <v>12</v>
+      </c>
+      <c r="C43" s="6" t="s">
+        <v>59</v>
+      </c>
+      <c r="D43" s="6" t="s">
+        <v>224</v>
+      </c>
+      <c r="E43" s="24">
+        <v>54</v>
+      </c>
+      <c r="G43" s="8">
+        <v>12</v>
+      </c>
       <c r="H43" s="6"/>
       <c r="I43" s="6"/>
       <c r="J43" s="21"/>
-      <c r="L43" s="8"/>
+      <c r="L43" s="8">
+        <v>12</v>
+      </c>
       <c r="M43" s="6"/>
       <c r="N43" s="11"/>
       <c r="O43" s="21"/>
     </row>
     <row r="44" spans="2:16" ht="21.2" customHeight="1">
-      <c r="B44" s="8"/>
-      <c r="C44" s="6"/>
-      <c r="D44" s="6"/>
-      <c r="E44" s="24"/>
-      <c r="G44" s="8"/>
+      <c r="B44" s="8">
+        <v>13</v>
+      </c>
+      <c r="C44" s="6" t="s">
+        <v>160</v>
+      </c>
+      <c r="D44" s="6" t="s">
+        <v>225</v>
+      </c>
+      <c r="E44" s="24">
+        <v>40</v>
+      </c>
+      <c r="G44" s="8">
+        <v>13</v>
+      </c>
       <c r="H44" s="6"/>
       <c r="I44" s="6"/>
       <c r="J44" s="21"/>
-      <c r="L44" s="8"/>
+      <c r="L44" s="8">
+        <v>13</v>
+      </c>
       <c r="M44" s="6"/>
       <c r="N44" s="11"/>
       <c r="O44" s="21"/>
     </row>
     <row r="45" spans="2:16" ht="21.2" customHeight="1">
-      <c r="B45" s="8"/>
-      <c r="C45" s="6"/>
-      <c r="D45" s="6"/>
-      <c r="E45" s="24"/>
-      <c r="G45" s="8"/>
+      <c r="B45" s="8">
+        <v>14</v>
+      </c>
+      <c r="C45" s="6" t="s">
+        <v>57</v>
+      </c>
+      <c r="D45" s="6" t="s">
+        <v>226</v>
+      </c>
+      <c r="E45" s="24">
+        <v>25</v>
+      </c>
+      <c r="G45" s="8">
+        <v>14</v>
+      </c>
       <c r="H45" s="6"/>
       <c r="I45" s="6"/>
       <c r="J45" s="21"/>
-      <c r="L45" s="8"/>
+      <c r="L45" s="8">
+        <v>14</v>
+      </c>
       <c r="M45" s="6"/>
       <c r="N45" s="11"/>
       <c r="O45" s="21"/>
     </row>
     <row r="46" spans="2:16" ht="21.2" customHeight="1" thickBot="1">
-      <c r="B46" s="9"/>
-      <c r="C46" s="10"/>
-      <c r="D46" s="10"/>
-      <c r="E46" s="27"/>
-      <c r="G46" s="9"/>
+      <c r="B46" s="9">
+        <v>15</v>
+      </c>
+      <c r="C46" s="10" t="s">
+        <v>160</v>
+      </c>
+      <c r="D46" s="10" t="s">
+        <v>227</v>
+      </c>
+      <c r="E46" s="27">
+        <v>53</v>
+      </c>
+      <c r="G46" s="9">
+        <v>15</v>
+      </c>
       <c r="H46" s="10"/>
       <c r="I46" s="10"/>
       <c r="J46" s="22"/>
-      <c r="L46" s="9"/>
+      <c r="L46" s="9">
+        <v>15</v>
+      </c>
       <c r="M46" s="10"/>
       <c r="N46" s="12"/>
       <c r="O46" s="22"/>
